--- a/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
+++ b/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
@@ -19,9 +19,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛查总表'!$A$1:$AE$427</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'目标测序研究'!$A$1:$AE$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据项目与样本'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$L$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$P$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'口径与字段说明'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1671,22 +1671,58 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>原初污泥及50%水稀释污泥</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>空气经扩散石2.5 mL/min，23°C</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>原泥/稀释泥分别设微曝气和厌氧对照；反应器双份</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods含样品、反应器、Chemical analyses及Statistical analyses。COD、氨、蛋白、糖类、TS/VS测定，无核酸提取、测序建库或组学重分析。</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Materials and methods；全8页定位检索并检查结果章节</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
           <t>["original_files/R00651/fulltext/fulltext__published__4a05c2b25035cc74.pdf"]</t>
@@ -1710,13 +1746,21 @@
       <c r="AB10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
+          <t>["R00651-E01", "R00651-E02"]</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:01:57.230715+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1766,22 +1810,58 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>brown water与餐厨垃圾混合物</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>前4天每日一次37.5 mL O2/L反应体积</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>微曝气预处理与全厌氧对照；不同接种时机；双份实验</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr"/>
       <c r="U11" s="2" t="inlineStr"/>
-      <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.4为底物、反应器、分析和产气计算。GC-TCD测气体，GC-FID测VFA，COD/pH/ORP/TS/VS分析；未进行核酸测序。</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>PDF p.3完整2.1–2.4；全7页定位检索及结果检查</t>
+        </is>
+      </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
           <t>["original_files/R00677/fulltext/fulltext__published__618d438d3f05b66a.pdf"]</t>
@@ -1805,13 +1885,21 @@
       <c r="AB11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr"/>
+          <t>["R00677-E01", "R00677-E02"]</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:01:57.258627+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1964,22 +2052,58 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16S定向PCR-DGGE及条带测序</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标16S序列）</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>污泥厌氧消化产生的含H2S沼气；消化液作接种物</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>纯氧与沼气混合进入10 L微好氧脱硫单元</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>水空白/消化液接种、进气位置与温度变化</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr"/>
       <c r="U13" s="2" t="inlineStr"/>
-      <c r="V13" s="2" t="inlineStr"/>
-      <c r="W13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.3完整阅读：群落DNA提取后以968-F-GC/1401-R定向PCR、DGGE分带、条带测序及BLAST/RDP分类，非shotgun。</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods；p.6群落结果及表3；全8页定位核查</t>
+        </is>
+      </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
           <t>["original_files/R00795/fulltext/fulltext__published__874efe69f8123943.pdf"]</t>
@@ -2003,13 +2127,21 @@
       <c r="AB13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr"/>
+          <t>["R00795-E01", "R00795-E02", "R00795-E03"]</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:01:57.287207+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2055,22 +2187,58 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>牛粪</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>纯氧或空气注入反应器顶空</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>4台30 L反应器，厌氧启动后比较氧气/空气不同流量</t>
+        </is>
+      </c>
       <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr"/>
-      <c r="V14" s="2" t="inlineStr"/>
-      <c r="W14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Materials and methods完整包括反应器/底物、运行条件、监测与分析；GC气体、HPLC硫酸盐/硫代硫酸盐、光度硫化物、硫元素分析及COD/VS等。无群落DNA/RNA测序或公开组学重分析。</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Materials and methods；全11页定位和章节检查</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
           <t>["original_files/R00888/fulltext/fulltext__version_unverified__fa65f300505c073a.pdf"]</t>
@@ -2094,13 +2262,21 @@
       <c r="AB14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr"/>
+          <t>["R00888-E01", "R00888-E02"]</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:02:22.916707+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -2150,22 +2326,50 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>综述不适用</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>综述不适用</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>综述；引用和讨论其他研究</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>不适用（综述）</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>原总表将其列研究类/非综述范围；原件明确综述，筛查单列；原人工分类未改写。</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr"/>
-      <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>原件首页标Research review paper，摘要明确This article reviews；目录/正文为ORP原理、代谢、酵母乙醇/梭菌丁醇及控制策略，没有本研究群落测序实验。保留原分类和原研究类字段，仅筛查状态按实际综述单列。</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.1–2首页、摘要及完整目录；pp.2–8综述章节组织/结论；全9页定位检查</t>
+        </is>
+      </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
           <t>["original_files/R00915/fulltext/fulltext__published__5c669a9f493b8a83.pdf"]</t>
@@ -2189,13 +2393,21 @@
       <c r="AB15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="inlineStr"/>
+          <t>["R00915-E01", "R00915-E02"]</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:02:22.944444+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2245,22 +2457,62 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA基因扩增子454焦磷酸测序</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标扩增子）</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>WWTP废水/活性污泥</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>SPR微好氧池DO0.5–1.0 mg/L；好氧池3.0–4.0 mg/L</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>SPRAS与AO并行；第109天SSPR、SSPO、SAOO三份群落样品</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Roche 454 GS-FLX Titanium（16S扩增子）</t>
+        </is>
+      </c>
       <c r="T16" s="2" t="inlineStr"/>
       <c r="U16" s="2" t="inlineStr"/>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>方法明确PCR、amplicons纯化、扩增混合物用于454测序；结果3.2.1明示Three 16s RNA gene libraries。OTU和SILVA分析；不是shotgun或群落RNA测序。</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>PDF p.2完整2.1–2.3及3.2.1；全5页定位检查</t>
+        </is>
+      </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01050/fulltext/fulltext__published__298873049e96fe61.pdf"]</t>
@@ -2284,13 +2536,21 @@
       <c r="AB16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr"/>
+          <t>["R01050-E01", "R01050-E02"]</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:02:22.972836+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -2443,22 +2703,58 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>不同收获期香根草地上生物量</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>35°C微好氧预发酵4天；供氧流量未报告</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>6个收获批次；接种物空白；每处理三份</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr"/>
-      <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>完整Methodology为香根草采样/粉碎/预发酵、批次产气和COD、VFA、TN/TP常规测定；未报告任何核酸提取、建库或测序。</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>PDF p.2完整2 Methodology；pp.3–4结果/结论；全4页定位检查</t>
+        </is>
+      </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01126/fulltext/fulltext__published__2c4123486329aa07.pdf"]</t>
@@ -2482,13 +2778,21 @@
       <c r="AB18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="inlineStr"/>
+          <t>["R01126-E01", "R01126-E02"]</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:02:48.011887+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2538,22 +2842,58 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>污水厂浓缩污泥</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>底部气石0.15 L/min空气，0.05 vvm</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>预曝气0.5–96 h及blank；BMP三份实验</t>
+        </is>
+      </c>
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="2" t="inlineStr"/>
-      <c r="V19" s="2" t="inlineStr"/>
-      <c r="W19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>2.1–2.3为预曝气、污泥理化和BMP。GC测气体、GC-MS测硅氧烷、离子色谱硫酸盐及COD/氮/TS/VS等，没有DNA/RNA测序。extraction-analysis指己烷提取硅氧烷，非核酸提取。</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整2 Materials and Methods（双栏方法跨页）；全8页定位检索</t>
+        </is>
+      </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01212/fulltext/fulltext__published__ef235fcb491d4749.pdf"]</t>
@@ -2577,13 +2917,21 @@
       <c r="AB19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="inlineStr"/>
+          <t>["R01212-E01", "R01212-E02"]</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:02:48.038424+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2633,22 +2981,58 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>木薯废水及木薯残渣</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>CSTR顶部间歇供氧，每2 h供5 min，1.5–6.0 mL O2/LR/d</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>无氧负荷/残渣优化后进行不同供氧比较</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr"/>
       <c r="U20" s="2" t="inlineStr"/>
-      <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.3完整阅读：GC-TCD气体、排水计气、COD比色、VFA蒸馏滴定及GC-FID有机酸、DO仪；无群落核酸测序。</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整2 Materials and methods；全6页定位和结果章节检查</t>
+        </is>
+      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01238/fulltext/fulltext__published__61aa93be627c8612.pdf"]</t>
@@ -2672,13 +3056,21 @@
       <c r="AB20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="inlineStr"/>
+          <t>["R01238-E01", "R01238-E02"]</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:02:48.064723+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2728,22 +3120,58 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>显微镜/染色及理化分析；未报告测序</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>浓缩剩余活性污泥，补加硫酸钠</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>空气连续泵入反应器底部，0.3–1.6 L/d</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>两台10 L反应器，微好氧R1与厌氧R2并行300天</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>完整方法含产气/污泥组成、泡沫、显微镜和CST。群落观察采用湿片、Gram/Neisser染色及形态鉴定；元素组成是XRF，未开展核酸测序。</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Material and methods；全7页定位检查</t>
+        </is>
+      </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01297/fulltext/fulltext__published__de7ffcf910e42cc3.pdf"]</t>
@@ -2767,13 +3195,21 @@
       <c r="AB21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr"/>
+          <t>["R01297-E01", "R01297-E02"]</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:03:29.871808+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2823,22 +3259,58 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>合成啤酒废水；加硫酸盐</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>空气泵入UMSB出水回流，1 L/d</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>UMSB与不曝气UASB并行；SMA活性瓶试验三份</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr"/>
-      <c r="V22" s="2" t="inlineStr"/>
-      <c r="W22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.4为反应器、配方、specific methanogenic activity和理化分析；SMA为产气活性实验，GC测产气、COD/VSS/TSS/硫化物及元素/XRF分析，无测序。</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods 2.1–2.4；全6页定位检查</t>
+        </is>
+      </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01347/fulltext/fulltext__published__45f836aff9088c2e.pdf"]</t>
@@ -2862,13 +3334,21 @@
       <c r="AB22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="inlineStr"/>
+          <t>["R01347-E01", "R01347-E02"]</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:03:29.898138+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2918,22 +3398,58 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>市政污水厂混合污泥</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>纯氧质量流量控制器，顶空或回流注入</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>200 L R1/R2，S1按H2S反馈PID、S2按产气量调氧；A/M/C运行期</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr"/>
-      <c r="V23" s="2" t="inlineStr"/>
-      <c r="W23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>完整Methods 2.1–2.4：反应器、GC气体和常规污泥指标、PID控制器设计、运行阶段。Excel宏用于控制算法，非组学数据分析；无核酸提取/建库/测序或公开数据重分析。</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Materials and methods；全9页定位检查</t>
+        </is>
+      </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01349/fulltext/fulltext__published__e04b312bae2991a3.pdf"]</t>
@@ -2957,13 +3473,21 @@
       <c r="AB23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="inlineStr"/>
+          <t>["R01349-E01", "R01349-E02"]</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:03:29.926741+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -3013,22 +3537,58 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>细菌/古菌16S PCR-DGGE；古菌条带测序</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标16S序列）</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>市政污泥</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>氧气浓缩器92–98%，间歇供入顶空、沼气回流或液相</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>5 m3工业中试；P1/P5厌氧、其余微好氧；S1–S4取P1–P4</t>
+        </is>
+      </c>
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr"/>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.4明确细菌16S V6–V8、古菌V2–V3定向PCR及DGGE；切取古菌DGGE条带、16S序列RDP/BLAST和嵌合体检查，非群落shotgun。</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整2 Methods（p.3图/表）；pp.6–8群落结果；全9页定位检查</t>
+        </is>
+      </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01350/fulltext/fulltext__published__a2d149d39c1e69ee.pdf"]</t>
@@ -3052,13 +3612,21 @@
       <c r="AB24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="inlineStr"/>
+          <t>["R01350-E01", "R01350-E02", "R01350-E03"]</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:04:24.269546+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -3108,22 +3676,58 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA基因克隆库/RFLP筛选后测序</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标16S序列）</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>brown water和餐厨垃圾</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>每天进料后1–2 h以3 mL/min加氧，MA1/MA2不同供氧量</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>3 L产酸反应器AN（1–6周）、MA1（7–13周）、MA2（14–20周）</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr"/>
-      <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.3用total-community DNA但8F/1490R专门扩增16S；TOPO TA克隆、M13 PCR和RFLP筛选，再测代表性16S克隆。不是shotgun；接近全长16S不等于全基因组。</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods；p.5系统树和结果；全7页定位核查</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01362/fulltext/fulltext__published__01950ce99dba212c.pdf"]</t>
@@ -3147,13 +3751,21 @@
       <c r="AB25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" s="2" t="inlineStr"/>
+          <t>["R01362-E01", "R01362-E02", "R01362-E03"]</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:04:24.297373+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -3203,22 +3815,58 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>合成餐厨垃圾，木屑作填料</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>LBR底部空气1 L/min，每次12 min；不同间隔</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>LBR-6h/3h/2h与不曝气LBR-AN；各双份</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr"/>
-      <c r="V26" s="2" t="inlineStr"/>
-      <c r="W26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.3完整为两阶段LBR-UASB系统、曝气频率及产气/TS/VS/TOC/TKN/COD/VFA等常规分析，无核酸测序。</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>PDF p.2完整2 Materials and methods；全7页定位和结果检查</t>
+        </is>
+      </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01410/fulltext/fulltext__published__a750f0e05f2cd4ac.pdf"]</t>
@@ -3242,13 +3890,21 @@
       <c r="AB26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" s="2" t="inlineStr"/>
+          <t>["R01410-E01", "R01410-E02"]</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:04:24.325273+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -3298,22 +3954,58 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>初沉污泥；启动阶段加硫酸镁</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>氧气经底部陶瓷扩散器0.14 mL/s注入，ORP −310至−290mV反馈开闭</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>两台50 L消化器：Digester1厌氧对照、Digester2供氧</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr"/>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>2.1–2.4为反应器、监测、运行和ORP供氧控制；无核酸测序。已读题名匹配DOCX补充表，内容仅气体组成和装置照片。</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods；全5页定位；DOCX全部段落/表格</t>
+        </is>
+      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01414/fulltext/fulltext__published__f3fdd6d92cc6ded3.pdf"]</t>
@@ -3337,13 +4029,21 @@
       <c r="AB27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>已核对supplementary__0b2884c05d320076.docx题名及作者，检查图S1、Table S1全表，无测序内容。</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" s="2" t="inlineStr"/>
+          <t>["R01414-E01", "R01414-E02", "R01414-E03"]</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:05:13.129266+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -3393,22 +4093,58 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>16S PCR-DGGE及条带测序</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标16S序列）</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>污水污泥</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>纯氧经质量流量控制器单点注入顶空</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>200 L R1/R2顶空不同位置A–F取样；清理前后运行比较</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr"/>
-      <c r="V28" s="2" t="inlineStr"/>
-      <c r="W28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.4提取genomic DNA后PCR-DGGE，切条带测序和RDP/BLAST分类；图5明确16S rRNA amplicons，非shotgun。</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Methods；p.6图5明确16S扩增子；pp.7–10条带表/系统树；全11页定位核查</t>
+        </is>
+      </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01505/fulltext/fulltext__published__cd661b225d80e30c.pdf"]</t>
@@ -3432,13 +4168,21 @@
       <c r="AB28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE28" s="2" t="inlineStr"/>
+          <t>["R01505-E01", "R01505-E02", "R01505-E03"]</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:05:13.156557+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -3488,22 +4232,58 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>市政混合污泥</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>纯氧注入进料和污泥回流汇合处</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>266 L反应器，25 L顶空与&lt;0.3 L顶空；A1/A2厌氧及M1–M4微好氧</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr"/>
-      <c r="V29" s="2" t="inlineStr"/>
-      <c r="W29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>完整Methods 2.1–2.3为反应器、GC气体及COD/TS/VS/VFA/氮/硫组分分析、顶空变化实验；生物作用来自运行和沉积现象讨论，无核酸测序。</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Methods；全7页定位和章节检查</t>
+        </is>
+      </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01556/fulltext/fulltext__published__2f7462391b5df844.pdf"]</t>
@@ -3527,13 +4307,21 @@
       <c r="AB29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" s="2" t="inlineStr"/>
+          <t>["R01556-E01", "R01556-E02"]</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:05:13.183276+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -3583,22 +4371,58 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>L-胱氨酸工业生产废生物质</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>微曝气处理硫化物抑制；与稀释、Fe2+沉淀比较</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>三台1.4 L悬浮生长反应器，BMP/长期运行抑制干预</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr"/>
-      <c r="V30" s="2" t="inlineStr"/>
-      <c r="W30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Methods and techniques含原料、反应器及Analytical methods。元素分析仪Vario Macro Cube测C/N/S，水质用ISO/滴定/重量法，红外气体仪测气体；Macro为仪器名称，不是宏基因组；没有核酸提取/建库/测序。</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods and techniques；全8页定位及结果检查</t>
+        </is>
+      </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01654/fulltext/fulltext__published__07361dc13d0f4990.pdf"]</t>
@@ -3622,13 +4446,21 @@
       <c r="AB30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE30" s="2" t="inlineStr"/>
+          <t>["R01654-E01", "R01654-E02"]</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:06:27.869539+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -3773,22 +4605,58 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>甘蔗渣</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>注射器一次供氧5/10/20 mL/g VSsubstrate，高温55°C预处理</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>TMP1/2/3、NaOH碱预处理AP及未处理WP；双份</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>出版版Methods 2.1–2.6完整为底物、微好氧/碱处理、批次AD、FTIR/XRD结构分析、GC气体及TS/VS。原登记补充PDF经题名/作者匹配确认为同文接受稿，方法pp.7–9与出版版一致，未使用目标测序。</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>出版版PDF p.2完整Materials and methods，全6页定位；原登记补充PDF pp.1–2身份、7–9方法，全部25页定位</t>
+        </is>
+      </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01727/fulltext/fulltext__published__cf60070671c880d0.pdf"]</t>
@@ -3801,7 +4669,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>已取得1件原格式补充材料；其中1件唯一关联待核实；完整性未确认</t>
+          <t>原清单1件补充PDF经本轮核实为同文接受稿；未确认独立SI原件</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -3810,15 +4678,23 @@
         </is>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>supplementary__2b717bb2226270b6.pdf实际为25页接受稿（含封面）；唯一关联已核实为本文章版本，不是新增SI。原文件/原角色保留，筛查层注明实际角色。</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE32" s="2" t="inlineStr"/>
+          <t>["R01727-E01", "R01727-E02", "R01727-E03"]</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:06:27.910019+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -3868,22 +4744,58 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>技术经济建模与敏感性分析；未使用目标测序</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>处理污水污泥的全规模消化系统经济情景</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>情景比较纯氧、PSA浓缩氧、空气；向顶空供给（经济模型假设）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>FeCl3基线、三种微好氧方案、接种硫细菌铁海绵过滤方案</t>
+        </is>
+      </c>
       <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr"/>
-      <c r="V33" s="2" t="inlineStr"/>
-      <c r="W33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>完整Methods 2.1–2.4为污水厂描述、处理情景、现金流/NPV/IRR及敏感性分析；复用的是既有工程性能和成本数据，不是公共宏基因组或宏转录组数据。未开展核酸测序。</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Methods；全7页定位/章节检查；顺延纳入以补足20篇实际研究</t>
+        </is>
+      </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01785/fulltext/fulltext__published__1045800466e6b5e7.pdf"]</t>
@@ -3907,13 +4819,21 @@
       <c r="AB33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE33" s="2" t="inlineStr"/>
+          <t>["R01785-E01", "R01785-E02"]</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:06:27.938296+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -42131,7 +43051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -43074,8 +43994,2600 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>R00651-E01</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>R00651</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sludge from batch reactors was sampled weekly to measure the total COD (tCOD), sCOD, NH3, protein, carbohydrate, TS and VS concentrations in duplicate.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>同段列总/溶解COD、NH3、蛋白、糖类、TS/VS；下一页为标准法及统计，无核酸测序。</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00651/fulltext/fulltext__published__4a05c2b25035cc74.pdf</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4a05c2b25035cc748d825411e9d9b8040b0a26b78944f9cce4aa9e77525e1462</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Chemical analyses</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>R00651-E02</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>R00651</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>All measurements were carried out in duplicate for each duplicate reactor. The data points in the figures show the average and the error bars show one standard deviation.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>完整方法止于统计分析，未出现目标测序建库或生物信息分析。</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00651/fulltext/fulltext__published__4a05c2b25035cc74.pdf</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4a05c2b25035cc748d825411e9d9b8040b0a26b78944f9cce4aa9e77525e1462</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Statistical analyses</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>R00677-E01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>R00677</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>The extracted hydrolysate/digestate was measured for its pH, oxidation–reduction potential (ORP), VFA and chemical oxygen demand (COD).</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>后文明确pH、ORP、VFA、COD及TS/VS，气体和VFA用GC；未使用群落组学。</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00677/fulltext/fulltext__published__618d438d3f05b66a.pdf</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>618d438d3f05b66a514a87a1e5ffc0b50fcaced539905c09fc1631c799dc9c30</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical procedures</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>R00677-E02</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>R00677</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>All experiments were conducted in duplicates. 2.3. Analytical procedures Biogas production and its composition were measured once every 2–4 days for the first 15 days and subsequently once every 5–8 days for the rest of the batch study to allow accumulation of biogas sufficient for the analysis of biogas composition using the GC–TCD.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>微曝气与厌氧对照是产气/水解比较，不是测序样本设计。</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00677/fulltext/fulltext__published__618d438d3f05b66a.pdf</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>618d438d3f05b66a514a87a1e5ffc0b50fcaced539905c09fc1631c799dc9c30</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Batch reactors</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>R00795-E01</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>R00795</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>The universal bacterial primers 968-F-GC and 1401-R were used for the PCR amplification procedure (Sigma–Aldrich, St. Louis, MO, USA).</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>16S引物PCR-DGGE；DNA提取并不等同宏基因组测序。</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00795/fulltext/fulltext__published__874efe69f8123943.pdf</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>874efe69f8123943fc02f6af88d183a26de385e827d7e6016d1efbc719f35d1e</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Microbiological analysis</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>R00795-E02</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>R00795</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>some DGGE bands were excised according to Lebrero et al. (2011). The closest matches to each sequenced band within a confidence level of 50%, and its respective taxonomic position were obtained by the Blast search tool at the National Centre for Biotechnology Information (McGinnis and Madden, 2004), and the Ribosomal Database Project (RDP) classifier tool […]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>切取DGGE条带后测序，BLAST/RDP分类；不是混合群落shotgun文库。</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00795/fulltext/fulltext__published__874efe69f8123943.pdf</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>874efe69f8123943fc02f6af88d183a26de385e827d7e6016d1efbc719f35d1e</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Microbiological analysis</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>R00795-E03</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>R00795</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>非目标序列编号声明</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>under accession numbers KC306914 to KC306931.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>本研究条带核酸序列编号，非目标宏基因组项目。</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00795/fulltext/fulltext__published__874efe69f8123943.pdf</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>874efe69f8123943fc02f6af88d183a26de385e827d7e6016d1efbc719f35d1e</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Microbiological analysis</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>R00888-E01</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>R00888</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Digestion performance was evaluated weekly by conventional parameters such as COD, VS, BG productivity and composition, pH, DO and total sulphide concentrations, according to standard methods [22].</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>同段明确为COD、VS、沼气产量/组成、pH、DO及总硫化物的常规分析。</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00888/fulltext/fulltext__version_unverified__fa65f300505c073a.pdf</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>fa65f300505c073a011466bf5d4e8b124903b552c3b918800f68a2e6d291e6f4</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Monitoring and experimental analysis</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>R00888-E02</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>R00888</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>The amount of methane, nitrogen, carbon dioxide and hydrogen sulphide in the biogas were measured by a gas chromatograph (Shimadzu, GC14B, Japan) equipped with a thermal conductivity detector.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>该段用GC测甲烷/氮/CO2/H2S；完整节无核酸测序方法。</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00888/fulltext/fulltext__version_unverified__fa65f300505c073a.pdf</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>fa65f300505c073a011466bf5d4e8b124903b552c3b918800f68a2e6d291e6f4</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Monitoring and experimental analysis</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>R00915-E01</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>R00915</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>文献类型核对</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Research review paper Redox potential control and applications in microaerobic and anaerobic fermentations Chen-Guang Liu a, Chuang Xue a, Yen-Han Lin c,⁎, Feng-Wu Bai a,b,⁎⁎ a School of Life Sciences and Biotechnology, Dalian University of Technology, Dalian 116023, China b School of Life Sciences and Biotechnology, Shanghai Jiao Tong University, Shanghai […]</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>原件明确文献类型为综述。</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00915/fulltext/fulltext__published__5c669a9f493b8a83.pdf</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>5c669a9f493b8a83e0fffcdf3d5c2e0c2fe6ac287e15c1cfb14999fd50aa9191</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Article type</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>R00915-E02</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>R00915</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>综述不适用依据</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>This article reviews updated progress in the impact of redox potentials on gene expression, protein biosynthesis and metabolism as well as redox potential control strategies for more efficient production of fermentation products, taking ethanol fermentation by the yeast Saccharomyces under microaerobic conditions and butanol production by the bacterium […]</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>本文综述ORP对基因表达、蛋白合成和代谢的影响；不能把引用研究当作自身测序。</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00915/fulltext/fulltext__published__5c669a9f493b8a83.pdf</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5c669a9f493b8a83e0fffcdf3d5c2e0c2fe6ac287e15c1cfb14999fd50aa9191</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>R01050-E01</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>R01050</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>A mixture of amplification was used for pyrosequencing on a Roche massively parallel 454 GS-FLX Titanium sequencer (Roche 454 Life Sciences, Branford, USA) according to standard protocols.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>文库模板为PCR扩增混合物；高通量和454平台不能当宏基因组证据。</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01050/fulltext/fulltext__published__298873049e96fe61.pdf</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>298873049e96fe61afba7fc6e9deeacb187d9a753e0da86d1bcf05b15a1f69ef</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Microbial community analysis</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>R01050-E02</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>R01050</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Three 16s RNA gene libraries were constructed from pyrosequencing of SSPR, SSPO and SAOO communities with 10,643, 10,606 and 10,002 high quality sequence tags, which were clustered into different phylogenetic bacterial communities with 2866/2500, 2701/2320 and 2383/2053 OTUs at a of 3%/5% (Table 1), indicating that SPRAS exhibited greater microbial richness […]</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>原文拼写16s RNA gene，结合前述DNA提取/PCR可判定16S基因扩增子；不是群落RNA-seq。</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01050/fulltext/fulltext__published__298873049e96fe61.pdf</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>298873049e96fe61afba7fc6e9deeacb187d9a753e0da86d1bcf05b15a1f69ef</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3.2.1 Richness and diversity of bacteria phylotypes</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>R01126-E01</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>R01126</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>The biogas slurry was sampled on the first day, the third day, and then every other 7 days until the end of the experiment. Chemical Oxygen Demand (COD) was analyzed according to the manual of Lovibond COD instrument (Germany).</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>随后明确检测COD、VFA、TN、TP；没有核酸或组学方法。</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01126/fulltext/fulltext__published__2c4123486329aa07.pdf</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2c4123486329aa078e3b1db35f4b069383f4ae72a4541abcf6a9709eb4e7375c</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2 Methodology</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>R01126-E02</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>R01126</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Each treatment was performed in triplicates. Assays with inoculum alone were used as blank controls. The pretreated substrate was diluted with tap water (adjusted pH to 7.0) to 2.25 L before feeding.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>三份是产气实验重复；不能当测序样本数。</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01126/fulltext/fulltext__published__2c4123486329aa07.pdf</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2c4123486329aa078e3b1db35f4b069383f4ae72a4541abcf6a9709eb4e7375c</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2 Methodology</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>R01212-E01</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>R01212</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>A combined extraction-analysis method was performed for determining hexamethyldisiloxane (L2), octamethyltrisiloxane (L3), decamethyltetrasiloxane (L4), dodecamethylpentasiloxane (L5), hexamethylcyclotrisiloxane (D3), octamethylcyclotetrasiloxane (D4), decamethylcyclopentasiloxane (D5), dodecamethylcyclohexasiloxane (D6) in the sewage sludge.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>上下文明确目标为硅氧烷L2–L5/D3–D6，己烷提取和GC-MS；不可误当DNA/RNA提取。</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01212/fulltext/fulltext__published__ef235fcb491d4749.pdf</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ef235fcb491d474970838cf59cfd36efaf9a37c84ddd225c06788beb77d497e3</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical Methods</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>R01212-E02</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>R01212</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>A biochemical methane potential (BMP) test was conducted to assess the cumulative methane yield for the treated sewage sludge. The BMP test was performed in triplicate by the procedure described in Shelton and Tiedje [17].</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>BMP及GC分析为完整方法结尾，无测序建库。</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01212/fulltext/fulltext__published__ef235fcb491d4749.pdf</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ef235fcb491d474970838cf59cfd36efaf9a37c84ddd225c06788beb77d497e3</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical Methods（续）</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>R01238-E01</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>R01238</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>The gas composition of the produced gas was determined by the GC (AutoSystem GC, Perkin-Elmer) equipped with a thermal conductivity detector (TCD).</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>GC-TCD测气体；完整节其余为COD/VFA/有机酸/DO理化分析。</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01238/fulltext/fulltext__published__61aa93be627c8612.pdf</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>61aa93be627c8612528bcb7fb5b9223e98e7ce0f3f8fd7e4e52c8b5a8068aced</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Measurement and analytical methods</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>R01238-E02</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>R01238</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>The samples obtained from the steam distillation were also taken for the determination of organic acid compositions by using another gas chromatograph (PR 2100, Perichrom) equipped with a flame ionization detector (FID).</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>蒸汽蒸馏样品用于有机酸GC-FID，非测序样本处理。</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01238/fulltext/fulltext__published__61aa93be627c8612.pdf</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>61aa93be627c8612528bcb7fb5b9223e98e7ce0f3f8fd7e4e52c8b5a8068aced</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Measurement and analytical methods</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>R01297-E01</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>R01297</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Microscopic analysis of the sludge samples was performed in accordance with Jenkins et al. (). The microscopic examination in wet mounts (Olympus BH2-RFCA – ×125, ×250 magnification and phase contrast ×1250 magnification) was aimed at examining basic biomass characteristics 804 P.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>群落信息来自显微镜形态；次页明确Gram和Neisser染色，非测序。</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01297/fulltext/fulltext__published__de7ffcf910e42cc3.pdf</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>de7ffcf910e42cc340bb9d8ffd472e072ad5ec764323e88912c01b40f23d7b62</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>R01297-E02</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>R01297</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Gram and Neisser staining procedures were applied to determine the abundance of filamentous microorganisms and to identify them. CST Capillary suction time (CST) is a simple parameter and a method used for the characterization of sludge dewaterability.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>染色判断丝状微生物丰度/身份，不属于宏基因组或宏转录组。</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01297/fulltext/fulltext__published__de7ffcf910e42cc3.pdf</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>de7ffcf910e42cc340bb9d8ffd472e072ad5ec764323e88912c01b40f23d7b62</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Microscopy（续）</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>R01347-E01</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>R01347</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>The assessment of specific methanogenic activity (SMA) was carried out at mesophilic conditions in serum bottles (total volume of 120 mL) without mixing in triplicates according to the guidelines proposed by Angelidaki et al.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>活性瓶测定不是宏转录或宏基因组方法。</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01347/fulltext/fulltext__published__45f836aff9088c2e.pdf</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>45f836aff9088c2e3dc90eb655f9edb76d87059f04bc6d28a96ad562dd988523</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2.3 The assessment of specific methanogenic activity</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>R01347-E02</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>R01347</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Granular sludge was sampled and analyzed for TSS, VSS and elemental composition. Analysis of CODCr, VSS and TSS were done according to the Standard Methods (American Public Health Association, 1997) as well as the determination of total sulfide, dissolved sulfide and hydrogen sulfide by iodometric titration.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>该句后为TSS/VSS及元素组成；完整节列GC和XRF，无核酸测序。</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01347/fulltext/fulltext__published__45f836aff9088c2e.pdf</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>45f836aff9088c2e3dc90eb655f9edb76d87059f04bc6d28a96ad562dd988523</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>R01349-E01</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>R01349</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>its composition was determined by a CP-4900 Micro-GC [12]. The detection limit (DL) for hydrogen sulphide was 0.001%v/v. The feed and the digested sludge were sampled weekly for total and soluble chemical oxygen demand, total solids, volatile solids 304 I.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>气相色谱测气体，污泥用标准理化指标；没有测序实验。</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01349/fulltext/fulltext__published__e04b312bae2991a3.pdf</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>e04b312bae2991a34789627d36e39976c7a69fd76928426f3c54a1432b95cac9</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Monitoring and experimental analysis</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>R01349-E02</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>R01349</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>It was implemented using macros in Microsoft Office Excel.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>此处macros是Excel控制程序，不是macro-omics或测序分析。</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01349/fulltext/fulltext__published__e04b312bae2991a3.pdf</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>e04b312bae2991a34789627d36e39976c7a69fd76928426f3c54a1432b95cac9</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Design of the feedback PID controller</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>R01350-E01</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>R01350</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>archaeal 16S rRNA genes were amplified by polymerase chain reaction (PCR) using the universal bacterial primers 968-F-GC and 1401-R, and A 109(T)-F and 515-GC-R (Sigma–Aldrich, St.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>细菌和古菌16S分别采用968-F-GC/1401-R与A109(T)-F/515-GC-R；非宏转录组。</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01350/fulltext/fulltext__published__a2d149d39c1e69ee.pdf</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>a2d149d39c1e69ee44975485bce10a90c0b95435c72a517f785c76d6a20afa86</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>R01350-E02</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>R01350</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Individual bands were excised from the archaeal DGGE gel. Both DNA extraction and purification of PCR products were carried out according to Rodríguez et al.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>序列来自古菌16S条带，不是宏基因组文库。</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01350/fulltext/fulltext__published__a2d149d39c1e69ee.pdf</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>a2d149d39c1e69ee44975485bce10a90c0b95435c72a517f785c76d6a20afa86</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>R01350-E03</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>R01350</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>非目标序列编号声明</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>accession numbers KJ402278–KJ402293.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>16S序列记录，非目标组学项目。</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01350/fulltext/fulltext__published__a2d149d39c1e69ee.pdf</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>a2d149d39c1e69ee44975485bce10a90c0b95435c72a517f785c76d6a20afa86</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>R01362-E01</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>R01362</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Primer set 8F (50-AGAGTTTGATYMTGGCTC-30) and 1490R (50-GGTT ACCTTGTTACGACTT-30) was used to amplify Bacterial 16S rRNA gene from the total-community DNA.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>该句上文8F/1490R扩增Bacterial 16S rRNA gene；群落DNA提取不能单独作为宏基因组证据。</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01362/fulltext/fulltext__published__01950ce99dba212c.pdf</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>01950ce99dba212c6924e9f4f31ef6db8082a5154717386014a40821ef0e1b6b</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>R01362-E02</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>R01362</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>The 16S rRNA gene of the representative clones with different RFLP patterns were sequenced, by Axil Scientific Sequencing (Singapore), to determine their phylogenetic affiliation.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>代表性16S克隆经RFLP去冗余后测序和系统发育分析，非宏转录组/宏基因组。</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01362/fulltext/fulltext__published__01950ce99dba212c.pdf</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>01950ce99dba212c6924e9f4f31ef6db8082a5154717386014a40821ef0e1b6b</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>R01362-E03</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>R01362</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>非目标序列编号声明</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>numbers: KJ907449–KJ907466.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>文中明确细菌16S部分序列；非目标项目。</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01362/fulltext/fulltext__published__01950ce99dba212c.pdf</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>01950ce99dba212c6924e9f4f31ef6db8082a5154717386014a40821ef0e1b6b</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>R01410-E01</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>R01410</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>The volume of biogas produced from the UASB reactor was measured using a wet gas flow meter (BSD-0.5, Shanghai, China) and concentration of methane in the biogas generated was determined using a gas chromatograph (GC-HP7890) equipped with a thermal conductivity detector.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>方法以计气/GC及底物、渗滤液化学分析为主，无建库或生物信息分析。</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01410/fulltext/fulltext__published__a750f0e05f2cd4ac.pdf</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>a750f0e05f2cd4ac62532b353981015de33925a7a5b20c329283eae7a1f7b14e</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>R01410-E02</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>R01410</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>The sum of acetic acid, propionic acid, n-butyric acid, iso-butyric acid, n-valeric acid and iso-valeric acid concentrations are reported as total VFAs (tVFA).</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>VFA由GC-FID直接测定，非功能预测也非宏组学。</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01410/fulltext/fulltext__published__a750f0e05f2cd4ac.pdf</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>a750f0e05f2cd4ac62532b353981015de33925a7a5b20c329283eae7a1f7b14e</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>R01414-E01</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>R01414</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Biogas flow rate, digester temperature, ORP, and pressure were monitored in real time and recorded by the SCADA system. Biogas composition (CH4, CO2, H2S, and O2) was measured daily using a portable biogas analyser (Biogas 5000, Geotech, UK).</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>SCADA记录气体/运行参数，随后为便携气体仪及TS/VS/COD/碱度，无核酸测序。</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01414/fulltext/fulltext__published__f3fdd6d92cc6ded3.pdf</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>f3fdd6d92cc6ded33ae5b190818c70cdb20d56973ad5b57700da51736e3179da</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Monitoring and measurement</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>R01414-E02</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>R01414</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>The oxygen entered the digester through a ceramic diffuser (6 cm [U+0004] 10 cm) placed at the base of the reactor. The discharge pressure of the oxygen bottle was controlled using a flow regulator set to 150 kPa.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>供氧受ORP控制，完整实验方法无组学建库。</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01414/fulltext/fulltext__published__f3fdd6d92cc6ded3.pdf</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>f3fdd6d92cc6ded33ae5b190818c70cdb20d56973ad5b57700da51736e3179da</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Micro-oxygen injection</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>R01414-E03</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>R01414</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Table S1: Biogas composition of the two digesters during the experiment.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>附件题名/作者与正文匹配，内容为装置照片和CH4/CO2/H2S/O2表，无测序方法或项目号。</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01414/supplementary/supplementary__0b2884c05d320076.docx</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0b2884c05d320076b34c119eee0262250395b30a4ae5bde7806b3fe21e173267</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>DOCX word/document.xml 段落1–12（含表内段落统一计数）；Table S1</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>R01505-E01</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>R01505</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>The desired bands were excised from the gels according to the procedure described by Lebrero et al. (2011). The taxonomic position of the sequenced DGGE bands was obtained by the RDP classifier tool at a confidence level of 50% (Wang et al., 2007).</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>条带切取后测序及分类，非宏基因组文库。</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01505/fulltext/fulltext__published__cd661b225d80e30c.pdf</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>cd661b225d80e30ccb3aaa4cd9ae50c21071f26bbf31dfe4b1fb013483710b66</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Bacterial analysis</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>R01505-E02</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>R01505</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Bacterial DGGE profiles of the 16S rRNA amplicons of the samples retrieved from the HS of R1 (a) and R2 (b) at t = 15 with their respective diversity indices.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>明确为16S扩增子DNA而不是群落RNA转录组。</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01505/fulltext/fulltext__published__cd661b225d80e30c.pdf</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>cd661b225d80e30ccb3aaa4cd9ae50c21071f26bbf31dfe4b1fb013483710b66</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Fig.5 caption</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>R01505-E03</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>R01505</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>非目标序列编号声明</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>database under accession numbers KF148033–KF148052.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>本研究16S条带核酸记录，非项目。</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01505/fulltext/fulltext__published__cd661b225d80e30c.pdf</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>cd661b225d80e30ccb3aaa4cd9ae50c21071f26bbf31dfe4b1fb013483710b66</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Bacterial analysis（续）</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>R01556-E01</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>R01556</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>The CH4, CO2, N2, O2 and H2S content of biogas was determined by gas chromatography (VARIAN CP-3800 GC) according to Díaz et al. (2010a),</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>GC测气体；其余指标为常规理化，无宏组学建库。</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01556/fulltext/fulltext__published__2f7462391b5df844.pdf</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>2f7462391b5df8445267f2f8a5c0387a7286101c309d4def9310c06541d1c113</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Monitoring and experimental analysis</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>R01556-E02</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>R01556</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>This research was divided into six periods, according to the HS volume of the digester (Table 1). In A1 and A2, the reactor operated MASS FLOW CONTROLLER SEWAGE SLUDGE O2 CYLINDER DIGESTED SLUDGE FLOWMETER BIOGAS (a) P GC T MASS FLOW CONTROLLER SEWAGE SLUDGE O2 CYLINDER DIGESTED SLUDGE GC T BIOGAS (b) MASS FLOW CONTROLLER SEWAGE SLUDGE O2 CYLINDER GC T […]</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>实验按顶空容积和供氧阶段变化，不是社区测序实验。</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01556/fulltext/fulltext__published__2f7462391b5df844.pdf</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2f7462391b5df8445267f2f8a5c0387a7286101c309d4def9310c06541d1c113</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Experimental procedure</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="90" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>R01654-E01</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>R01654</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Through elemental analysis using a Vario Macro Cube (Elementar Analysensysteme), the elemental composition of waste biomass (samples 2 and 3) was determined as follows: C 4.41%, N 0.72%, S 0.41% with ratios C:N 1⁄4 6.1 and C:S 1⁄4 10.8 for sample 2, and C 4.8%, N 0.94%, S 0.44% with ratios C:N 1⁄4 5.1 and C:S 1⁄4 10.9 for sample 3.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Macro Cube为元素分析仪，测C/N/S，不可据Macro词误判组学。</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01654/fulltext/fulltext__published__07361dc13d0f4990.pdf</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>07361dc13d0f4990272d0fca0f7447c5ee84a8f2b900675775f2e6ee1998444a</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Feedstock（续）</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="90" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>R01654-E02</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>R01654</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Volatile fatty acids (VFA) were measured by titration with a 0.05 M solution of H2SO4. TS, VS, and dissolved inorganic salts (DIS) were determined gravimetrically according to Standard Methods for the Examination of Water and Wastewater (APHA/AWWA/WEF ).</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>完整节为滴定、重量法及气体分析，无任何群落核酸测序。</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01654/fulltext/fulltext__published__07361dc13d0f4990.pdf</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>07361dc13d0f4990272d0fca0f7447c5ee84a8f2b900675775f2e6ee1998444a</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Analytical methods</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>R01727-E01</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>R01727</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>The structure analyses were conducted by a spectrum one FTIR system (the Nicolet iN10 IR Microscope) with a universal ATR (Attenuated Total Reection) accessory and wide angle X-ray diffraction, which was in accordance with the reported methods.18 2.6 Analytical methods The biogas yield was measured by water displacement method.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>结构分析为FTIR-ATR和XRD，非基因组/转录组功能分析。</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01727/fulltext/fulltext__published__cf60070671c880d0.pdf</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>cf60070671c880d0eec8957e9b2b2f8d68cc83429c0c3eb7504a2d7f8e2381b3</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Structure analysis of solid fraction of sugarcane bagasse</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="90" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>R01727-E02</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>R01727</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Biogas composition was measured by a gas chromatograph (SP 6890, Shandong Lunan Inc., China), equipped with a Porapak Q stainless steel column (180 cm long, 3 mm outer diameter) and a thermal conductivity detector.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>气体及TS/VS常规分析；完整方法无核酸测序。</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01727/fulltext/fulltext__published__cf60070671c880d0.pdf</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>cf60070671c880d0eec8957e9b2b2f8d68cc83429c0c3eb7504a2d7f8e2381b3</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>R01727-E03</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>R01727</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>附件身份与实际角色核对</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>This is an Accepted Manuscript</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>与出版版题名、Shan-fei Fu等作者完全匹配；实际为本文接受稿，不是独立补充材料。仅记录筛查层核实，保留原清单角色和路径。</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01727/supplementary/supplementary__2b717bb2226270b6.pdf</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>2b717bb2226270b60ed76548490ad50d935cb973cc5017cc2b19aa287c870488</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>[1, 2]</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>原登记supplementary PDF：p1接受稿声明，p2题名/作者</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="90" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>R01785-E01</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>R01785</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Data contained in Table 1 (specifically, VS influent and removal, and biogas production) were estimated from the results of Ramos et al.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>后文明确VS进料/去除和沼气产量取自既有工程研究；不是组学数据再分析。</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01785/fulltext/fulltext__published__1045800466e6b5e7.pdf</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1045800466e6b5e78175d03918711476e7fa0a0ac6638aeb4e474981a713548e</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>2.1 Plant description</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="90" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>R01785-E02</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>R01785</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>The profitability analysis was based on cash flows, and carried out in terms of net present value (NPV) and internal return rate (IRR), according to Chauvel et al.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>研究主体为NPV/IRR经济分析，无测序或核酸方法。</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01785/fulltext/fulltext__published__1045800466e6b5e7.pdf</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1045800466e6b5e78175d03918711476e7fa0a0ac6638aeb4e474981a713548e</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Profitability analysis</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L17"/>
+  <autoFilter ref="A1:L65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43086,7 +46598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -43101,6 +46613,10 @@
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -43162,6 +46678,26 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>后续处理</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>解决状态</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>解决批次</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>解决依据</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>解决证据ID</t>
         </is>
       </c>
     </row>
@@ -43194,6 +46730,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -43224,6 +46764,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -43254,6 +46798,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -43284,6 +46832,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -43314,6 +46866,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -43344,6 +46900,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -43374,6 +46934,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -43404,6 +46968,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -43434,6 +47002,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -43464,6 +47036,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -43494,6 +47070,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -43524,6 +47104,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -43554,6 +47138,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -43584,6 +47172,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -43614,6 +47206,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -43644,6 +47240,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -43674,6 +47274,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -43704,6 +47308,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -43734,6 +47342,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -43764,6 +47376,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -43794,6 +47410,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -43824,6 +47444,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -43854,6 +47478,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -43884,6 +47512,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -43914,6 +47546,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -43944,6 +47580,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -43974,6 +47614,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -44004,6 +47648,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -44034,6 +47682,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -44064,6 +47716,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -44094,6 +47750,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -44124,6 +47784,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -44154,6 +47818,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -44184,6 +47852,10 @@
           <t>本轮跳过，不能作目标测序阴性</t>
         </is>
       </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -44222,6 +47894,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -44260,6 +47936,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -44298,6 +47978,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -44336,6 +48020,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -44374,6 +48062,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -44412,6 +48104,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -44450,6 +48146,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -44488,6 +48188,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
     </row>
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -44526,6 +48230,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -44564,6 +48272,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -44602,6 +48314,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -44637,7 +48353,27 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
+          <t>仅保留历史问题及本轮解决证据；不再作为唯一归属待核实对象计数。</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>已解决</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>完整题名和作者与出版版匹配，PDF声明Accepted Manuscript；实际为同文接受稿，不是独立SI。原清单角色/原件保留。</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>R01727-E03</t>
         </is>
       </c>
     </row>
@@ -44678,6 +48414,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -44716,6 +48456,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -44754,6 +48498,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -44792,6 +48540,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -44830,6 +48582,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
     </row>
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -44868,6 +48624,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -44906,6 +48666,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -44944,6 +48708,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
     </row>
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -44982,6 +48750,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -45020,6 +48792,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -45058,6 +48834,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -45096,6 +48876,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -45134,6 +48918,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -45172,6 +48960,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -45210,6 +49002,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="60" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -45248,6 +49044,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
     </row>
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -45286,6 +49086,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
     </row>
     <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -45324,6 +49128,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
     </row>
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -45362,6 +49170,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
     </row>
     <row r="67" ht="60" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -45400,6 +49212,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -45438,6 +49254,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
     </row>
     <row r="69" ht="60" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -45476,6 +49296,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
     </row>
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -45514,6 +49338,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -45552,6 +49380,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
     </row>
     <row r="72" ht="60" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -45590,6 +49422,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
     </row>
     <row r="73" ht="60" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -45628,6 +49464,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
     </row>
     <row r="74" ht="60" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -45666,6 +49506,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
     </row>
     <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -45704,6 +49548,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
     </row>
     <row r="76" ht="60" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -45742,6 +49590,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -45780,6 +49632,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr"/>
     </row>
     <row r="78" ht="60" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -45818,6 +49674,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="60" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -45856,6 +49716,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -45894,6 +49758,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="60" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -45932,6 +49800,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="60" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -45970,6 +49842,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="60" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -46008,6 +49884,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="60" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -46046,6 +49926,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="60" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -46084,6 +49968,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="60" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -46122,6 +50010,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="60" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
@@ -46160,6 +50052,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="60" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -46198,6 +50094,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="60" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -46236,6 +50136,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="60" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -46274,6 +50178,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="60" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
@@ -46312,6 +50220,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="60" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -46350,6 +50262,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="60" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -46388,6 +50304,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="60" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -46426,6 +50346,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="60" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -46464,6 +50388,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="60" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -46502,6 +50430,10 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="60" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -46560,6 +50492,10 @@
           <t>仅留防误报线索，不作为数据再分析目标</t>
         </is>
       </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="60" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -46602,9 +50538,323 @@
           <t>保留缺附件说明；本轮不追下载，不称SI已查全。</t>
         </is>
       </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>R00795</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>非目标测序编号线索</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00795/fulltext/fulltext__published__874efe69f8123943.pdf</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>874efe69f8123943fc02f6af88d183a26de385e827d7e6016d1efbc719f35d1e</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>KC306914 to KC306931</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>KC306914–KC306931</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>核酸序列记录范围，非项目</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>GenBank</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/KC306914</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>本研究16S PCR-DGGE条带序列；不计目标数据项目，官方状态未核实。</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>留作防误报线索</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>R00915</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>原文献类型与筛查实际类型差异</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R00915/fulltext/fulltext__published__5c669a9f493b8a83.pdf</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>5c669a9f493b8a83e0fffcdf3d5c2e0c2fe6ac287e15c1cfb14999fd50aa9191</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>[1, 2]</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>原队列为研究类，但原件明确Research review paper；已按综述不适用处理并保留原分类。</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>已解决本轮筛查适用性；原分类供用户复核，不自动覆盖总表。</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>R01350</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>非目标测序编号线索</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01350/fulltext/fulltext__published__a2d149d39c1e69ee.pdf</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>a2d149d39c1e69ee44975485bce10a90c0b95435c72a517f785c76d6a20afa86</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>KJ402278–KJ402293</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>KJ402278–KJ402293</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>核酸序列记录范围，非项目</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>GenBank</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/KJ402278</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>本研究古菌16S-DGGE序列；不计目标数据项目，官方状态未核实。</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>保留防误报线索</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>R01362</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>非目标测序编号线索</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01362/fulltext/fulltext__published__01950ce99dba212c.pdf</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>01950ce99dba212c6924e9f4f31ef6db8082a5154717386014a40821ef0e1b6b</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>KJ907449–KJ907466</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>KJ907449–KJ907466</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>核酸序列记录范围，非项目</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>GenBank</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/KJ907449</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>本研究细菌16S克隆序列；不计目标项目，官方状态未核实。</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>保留防误报线索</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>R01505</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>非目标测序编号线索</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01505/fulltext/fulltext__published__cd661b225d80e30c.pdf</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>cd661b225d80e30ccb3aaa4cd9ae50c21071f26bbf31dfe4b1fb013483710b66</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>KF148033–KF148052</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>KF148033–KF148052</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>核酸序列记录范围，非项目</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>GenBank</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/KF148033</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>本研究16S-DGGE条带序列；不计目标项目，官方状态未核实。</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>保留防误报线索</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L98"/>
+  <autoFilter ref="A1:P103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46615,7 +50865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -46681,11 +50931,11 @@
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>累计已完成研究</t>
+          <t>实际类型核验后研究队列</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -46697,31 +50947,27 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>累计目标测序文章（兼有只计一次）</t>
+          <t>累计已核查记录（含新识别综述）</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>累计</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>未完成、缺正文及综述不计阴性；本批零命中不代表剩余队列没有目标测序。</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>仅宏基因组文章</t>
+          <t>累计已完成研究</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -46733,7 +50979,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>仅宏转录组文章</t>
+          <t>累计目标测序文章（兼有只计一次）</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -46744,12 +50990,16 @@
           <t>累计</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>未完成、缺正文及综述不计阴性；本批零命中不代表剩余队列没有目标测序。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>二者兼有文章</t>
+          <t>仅宏基因组文章</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -46765,7 +51015,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>官方确认公开目标数据文章</t>
+          <t>仅宏转录组文章</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -46781,7 +51031,7 @@
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>明确可索取相关测序数据文章</t>
+          <t>二者兼有文章</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -46797,7 +51047,7 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>独立目标项目数（按dataset_key去重）</t>
+          <t>官方确认公开目标数据文章</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -46813,7 +51063,7 @@
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>待确认研究</t>
+          <t>明确可索取相关测序数据文章</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -46829,11 +51079,11 @@
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>未开始研究</t>
+          <t>独立目标项目数（按dataset_key去重）</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -46845,11 +51095,11 @@
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>缺正文跳过（研究）</t>
+          <t>待确认研究</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -46861,11 +51111,11 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>综述不适用（含4条缺正文综述）</t>
+          <t>未开始研究</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>50</v>
+        <v>316</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -46877,11 +51127,11 @@
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>附件唯一归属待核实件数</t>
+          <t>缺正文跳过（研究）</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -46893,13 +51143,11 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>下一批起点</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>R00651</t>
-        </is>
+          <t>综述不适用（含4条缺正文综述）</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -46911,11 +51159,11 @@
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>下一批默认篇数</t>
+          <t>附件唯一归属待核实件数</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -46927,37 +51175,33 @@
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>本批完成ID</t>
+          <t>下一批起点</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>R00273, R00313, R00379, R00430, R00608</t>
+          <t>R01917</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>B001</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>按稳定ID顺序；逐篇检查方法上下文，含扫描件原页核查</t>
-        </is>
-      </c>
+          <t>累计</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
+          <t>下一批默认篇数</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>累计</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -46965,27 +51209,33 @@
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>0</v>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>R00273, R00313, R00379, R00430, R00608</t>
+        </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>B001</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
+          <t>completed_count</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -46997,11 +51247,11 @@
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -47013,11 +51263,13 @@
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>0</v>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -47029,7 +51281,7 @@
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>target_articles</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -47045,7 +51297,7 @@
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>explicit_request_articles</t>
+          <t>metagenomics_only</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -47058,8 +51310,240 @@
       </c>
       <c r="D26" s="2" t="inlineStr"/>
     </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>metatranscriptomics_only</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>explicit_request_articles</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>R00651, R00677, R00795, R00888, R01050, R01126, R01212, R01238, R01297, R01347, R01349, R01350, R01362, R01410, R01414, R01505, R01556, R01654, R01727, R01785</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；实际综述单列后顺延补足研究篇数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>processed_record_count</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>["R00915"]</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>target_articles</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>metagenomics_only</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>metatranscriptomics_only</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>explicit_request_articles</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D26"/>
+  <autoFilter ref="A1:D40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47109,7 +51593,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>目标测序研究/项目表仅列真实阳性；本批空表表示已完成5篇均阴性，不是未开展筛查。</t>
+          <t>目标测序研究/项目表仅列真实阳性；零记录表表示累计已完成研究没有确认阳性；未完成记录不作阴性。</t>
         </is>
       </c>
     </row>
@@ -47121,7 +51605,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>全范围426条含388有核验正文、38无核验正文；进度优先将50综述列不适用，其中4条无核验正文；另34条研究缺正文跳过。</t>
+          <t>全范围426条含388有核验正文、38无核验正文；基线综述50条（4条缺正文），B002按原件新增识别R00915为综述，当前51条；34条研究缺正文跳过。</t>
         </is>
       </c>
     </row>
@@ -47217,7 +51701,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>61件暂不唯一归属；待题名/DOI/正文引用核实，不据目录分配编号。可检查现有附件，不追下载缺件。</t>
+          <t>本轮R01727已核实为同文接受稿，剩60件暂不唯一归属；待题名/DOI/正文引用核实，不据目录分配编号。可检查现有附件，不追下载缺件。</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
+++ b/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径与字段说明" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛查总表'!$A$1:$AE$427</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'目标测序研究'!$A$1:$AE$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛查总表'!$A$1:$AF$427</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'目标测序研究'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据项目与样本'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$P$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$P$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'口径与字段说明'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE427"/>
+  <dimension ref="A1:AF427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -476,6 +476,7 @@
     <col width="25" customWidth="1" min="29" max="29"/>
     <col width="25" customWidth="1" min="30" max="30"/>
     <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -632,6 +633,11 @@
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>完成时间UTC</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>待确认项筛查保存时间UTC</t>
         </is>
       </c>
     </row>
@@ -733,6 +739,7 @@
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -868,6 +875,7 @@
           <t>2026-10-23T05:06:51.580229+00:00</t>
         </is>
       </c>
+      <c r="AF3" s="2" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1007,6 +1015,7 @@
           <t>2026-10-23T05:07:27.430413+00:00</t>
         </is>
       </c>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1110,6 +1119,7 @@
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1249,6 +1259,7 @@
           <t>2026-10-23T05:07:42.826544+00:00</t>
         </is>
       </c>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1388,6 +1399,7 @@
           <t>2026-10-23T05:07:59.420109+00:00</t>
         </is>
       </c>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1487,6 +1499,7 @@
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1622,6 +1635,7 @@
           <t>2026-10-23T05:08:34.590919+00:00</t>
         </is>
       </c>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1761,6 +1775,7 @@
           <t>2026-10-23T06:01:57.230715+00:00</t>
         </is>
       </c>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1900,6 +1915,7 @@
           <t>2026-10-23T06:01:57.258627+00:00</t>
         </is>
       </c>
+      <c r="AF11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -2003,6 +2019,7 @@
         </is>
       </c>
       <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -2142,6 +2159,7 @@
           <t>2026-10-23T06:01:57.287207+00:00</t>
         </is>
       </c>
+      <c r="AF13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2277,6 +2295,7 @@
           <t>2026-10-23T06:02:22.916707+00:00</t>
         </is>
       </c>
+      <c r="AF14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -2408,6 +2427,7 @@
           <t>2026-10-23T06:02:22.944444+00:00</t>
         </is>
       </c>
+      <c r="AF15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2551,6 +2571,7 @@
           <t>2026-10-23T06:02:22.972836+00:00</t>
         </is>
       </c>
+      <c r="AF16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -2654,6 +2675,7 @@
         </is>
       </c>
       <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2793,6 +2815,7 @@
           <t>2026-10-23T06:02:48.011887+00:00</t>
         </is>
       </c>
+      <c r="AF18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2932,6 +2955,7 @@
           <t>2026-10-23T06:02:48.038424+00:00</t>
         </is>
       </c>
+      <c r="AF19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -3071,6 +3095,7 @@
           <t>2026-10-23T06:02:48.064723+00:00</t>
         </is>
       </c>
+      <c r="AF20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -3210,6 +3235,7 @@
           <t>2026-10-23T06:03:29.871808+00:00</t>
         </is>
       </c>
+      <c r="AF21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -3349,6 +3375,7 @@
           <t>2026-10-23T06:03:29.898138+00:00</t>
         </is>
       </c>
+      <c r="AF22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -3488,6 +3515,7 @@
           <t>2026-10-23T06:03:29.926741+00:00</t>
         </is>
       </c>
+      <c r="AF23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -3627,6 +3655,7 @@
           <t>2026-10-23T06:04:24.269546+00:00</t>
         </is>
       </c>
+      <c r="AF24" s="2" t="inlineStr"/>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -3766,6 +3795,7 @@
           <t>2026-10-23T06:04:24.297373+00:00</t>
         </is>
       </c>
+      <c r="AF25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -3905,6 +3935,7 @@
           <t>2026-10-23T06:04:24.325273+00:00</t>
         </is>
       </c>
+      <c r="AF26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -4044,6 +4075,7 @@
           <t>2026-10-23T06:05:13.129266+00:00</t>
         </is>
       </c>
+      <c r="AF27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -4183,6 +4215,7 @@
           <t>2026-10-23T06:05:13.156557+00:00</t>
         </is>
       </c>
+      <c r="AF28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -4322,6 +4355,7 @@
           <t>2026-10-23T06:05:13.183276+00:00</t>
         </is>
       </c>
+      <c r="AF29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -4461,6 +4495,7 @@
           <t>2026-10-23T06:06:27.869539+00:00</t>
         </is>
       </c>
+      <c r="AF30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -4556,6 +4591,7 @@
         </is>
       </c>
       <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -4695,6 +4731,7 @@
           <t>2026-10-23T06:06:27.910019+00:00</t>
         </is>
       </c>
+      <c r="AF32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -4834,6 +4871,7 @@
           <t>2026-10-23T06:06:27.938296+00:00</t>
         </is>
       </c>
+      <c r="AF33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -4929,6 +4967,7 @@
         </is>
       </c>
       <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -5032,6 +5071,7 @@
         </is>
       </c>
       <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -5081,22 +5121,66 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>待确认：测序建库和靶区描述不足</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>PCR后454测序；扩增子特征明显，靶区未明示</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>7 证据不足，待确认</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>正文引用Wan et al.2014的PCR引物/条件，但自身及现有SI未写靶区/引物序列。需核对该具体建库方法或作者说明，不能仅以454/OTU推定。</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>石化园区综合废水</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>有限曝气DO0.1–0.5 mg/L，四个运行阶段</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>有限曝气A和厌氧B并行；第50天各取群落样品</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Roche 454 FLX Titanium</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr"/>
-      <c r="V36" s="2" t="inlineStr"/>
-      <c r="W36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>完整Methods 2.1–2.6：DNA提取后将测序通用引物加入PCR引物，PCR后454和Mothur/OTU分析，具有扩增子特征；未明确靶基因/引物序列、未描述shotgun文库或社区RNA。现有SI为运行/群落丰度图，无建库补充或数据编号。不能仅凭Genome Sequencer仪器名判为宏基因组；保留独立复核项，不强行作阴性。 官方SRA以已知DOI查询未检出关联记录；未发现不等于无数据，仍待确认。</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods，p.5群落结果，全7页数据声明/编号定位；已关联DOC全部文本/图S1–S12说明</t>
+        </is>
+      </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
           <t>["original_files/R01917/fulltext/fulltext__published__e31cfc89134fbe8a.pdf"]</t>
@@ -5120,13 +5204,22 @@
       <c r="AB36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>题名匹配DOC为DO/ORP/COD/群落门丰度、OUR/可生化性及工程应用图；未找到测序项目号。</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["R01917-E01", "R01917-E02", "R01917-E03", "R01917-E04", "R01917-E05"]</t>
         </is>
       </c>
       <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:28:50.396856+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -5230,6 +5323,7 @@
         </is>
       </c>
       <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -5279,22 +5373,58 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>FISH计数及气体/理化分析；未测序</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>污水厂污泥</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>压缩空气经消化器底部回流管注入</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>全规模55°C消化启动，曝气/停曝气时序</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr"/>
-      <c r="V38" s="2" t="inlineStr"/>
-      <c r="W38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Materials and methods 2.1–2.3：产甲烷菌计数用ARC915探针FISH、荧光显微镜计数，另TS/VS和气体红外/GC检测。FISH是杂交成像，不是群落RNA测序。</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.1–3完整Materials and methods；全3页核查</t>
+        </is>
+      </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02094/fulltext/fulltext__published__b306bbf706889c58.pdf"]</t>
@@ -5318,13 +5448,22 @@
       <c r="AB38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE38" s="2" t="inlineStr"/>
+          <t>["R02094-E01", "R02094-E02"]</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:28:50.424119+00:00</t>
+        </is>
+      </c>
+      <c r="AF38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -5374,22 +5513,58 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>55°C微好氧预处理一次加氧；二次微好氧5/10/20 mL/g残余VS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>R0/R/RS1–3和未处理A；双份批次消化</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr"/>
-      <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.5为底物/接种物、两次微好氧处理、AD及分析；GC气体、SCOD比色、元素和TS/VS/纤维素等，没有核酸测序或组学重分析。</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>PDF p.2完整Methods；全4页定位和结果核查</t>
+        </is>
+      </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02115/fulltext/fulltext__published__e07eece2b7522917.pdf"]</t>
@@ -5413,13 +5588,22 @@
       <c r="AB39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE39" s="2" t="inlineStr"/>
+          <t>["R02115-E01", "R02115-E02"]</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:28:50.451863+00:00</t>
+        </is>
+      </c>
+      <c r="AF39" s="2" t="inlineStr"/>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -5469,22 +5653,62 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>16S V3–V4/V4–V5扩增子Illumina MiSeq</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标扩增子）</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>55°C微好氧5 mL O2/g VSsubstrate</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>TMP1供氧、TMP0不供氧；三份反应器</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq 2×250或2×300（16S扩增子）</t>
+        </is>
+      </c>
       <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr"/>
-      <c r="V40" s="2" t="inlineStr"/>
-      <c r="W40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>2.6明确MetaVx扩增子库、针对16S保守区的V3/V4/V5引物及接头，MiSeq和QIIME分类。DNA提取/NGS并不使其成为shotgun；参考文献中metagenomic sequencing不是本研究实验。</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>PDF p.2完整Methods 2.1–2.6；pp.4–5群落结果，pp.5–6参考文献语境；全6页核查</t>
+        </is>
+      </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02176/fulltext/fulltext__published__9b88e4a9a62a14a8.pdf"]</t>
@@ -5508,13 +5732,22 @@
       <c r="AB40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE40" s="2" t="inlineStr"/>
+          <t>["R02176-E01", "R02176-E02"]</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:28:50.479886+00:00</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -5564,22 +5797,58 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>55°C一次注氧，0/5/10/20/30/40 mL/g VSsubstrate</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>R1–R6供氧量、未处理A；双份批次AD</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr"/>
-      <c r="V41" s="2" t="inlineStr"/>
-      <c r="W41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.5为底物、预处理、批次AD、产气拟合、FTIR/XRD/SEM和理化分析；无核酸测序。附带p8勘误仅修正产气拟合公式；题名匹配DOC补充为三幅结构表征图。</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods，p.8勘误；正文pp.1–6与附加页均核查；DOC全部图注/声明</t>
+        </is>
+      </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02188/fulltext/fulltext__published__d71a021f92b210cb.pdf"]</t>
@@ -5603,13 +5872,22 @@
       <c r="AB41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>已关联DOC全读，Fig.S1 FTIR、S2 XRD、S3 SEM。PDF p7低文字隔页另作版面核验。 PDF p7已视觉确认是更新提示页，p8为公式勘误，不含新测序方法。</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE41" s="2" t="inlineStr"/>
+          <t>["R02188-E01", "R02188-E02", "R02188-E03"]</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:29:37.713121+00:00</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -5659,22 +5937,62 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>条形码PCR扩增子Illumina MiSeq测序</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标扩增子）</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>石化及生活混合废水/石化废水</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>MHA底部扩散器0.3 L/h空气；好氧段DO4–6 mg/L</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>MHA-缺氧/好氧串联；第100天取MHA、缺氧、好氧污泥</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq PE250（扩增子）</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr"/>
-      <c r="V42" s="2" t="inlineStr"/>
-      <c r="W42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Analytical methods明确条形码引物PCR、AxyPrep纯化amplicons、重复扩增子合并及amplicon sequencing、97% OTU分类；不是shotgun。靶基因未在自身方法明示，但扩增子文库性质明确，不根据Illumina平台作判断。</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Methods 2.1–2.4；p.5群落结果；全7页定位检查</t>
+        </is>
+      </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02199/fulltext/fulltext__published__4a6994a2d2e1e3aa.pdf"]</t>
@@ -5698,13 +6016,22 @@
       <c r="AB42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE42" s="2" t="inlineStr"/>
+          <t>["R02199-E01", "R02199-E02"]</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:29:37.739688+00:00</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -5750,22 +6077,58 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>石化园区综合废水</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>工程池曝气环管，DO0.2–0.35 mg/L</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>改造后水解酸化进出水监测；好氧可降解性批次比较</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr"/>
-      <c r="V43" s="2" t="inlineStr"/>
-      <c r="W43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>原PDF中文文字层异常，实际正文pp.3–7重新OCR并查看p4方法原页；1.1工程改造、1.2测试指标为COD/BOD5/TOC/硫酸盐/UV254/VFA、超滤分子量分布和好氧降解试验。没有核酸提取、建库或测序；SRB仅由硫酸盐变化讨论。</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.3–7对应印刷3738–3742；p.4完整1.1–1.2原页视觉核查；附加封面/目录不属论文正文</t>
+        </is>
+      </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02239/fulltext/fulltext__version_unverified__0ec9c37ecd0bceff.pdf"]</t>
@@ -5789,13 +6152,22 @@
       <c r="AB43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；本轮重新OCR五页目标正文。</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE43" s="2" t="inlineStr"/>
+          <t>["R02239-E01", "R02239-E02"]</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:30:22.092149+00:00</t>
+        </is>
+      </c>
+      <c r="AF43" s="2" t="inlineStr"/>
     </row>
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -5845,22 +6217,58 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>葡萄糖合成高硫酸盐废水</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>脉冲/连续空气；UASB微曝气</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>三个实验系列，曝气量、COD/硫酸盐比、沸石和温度比较</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr"/>
-      <c r="V44" s="2" t="inlineStr"/>
-      <c r="W44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods为批次与UASB运行、天然沸石、合成废水及COD/固体/氮/pH/硫化物/硫酸盐/DO标准分析；未报告核酸提取、建库或测序。</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Materials and methods；全10页定位检查</t>
+        </is>
+      </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02274/fulltext/fulltext__published__4c7da8384f1f6e3d.pdf"]</t>
@@ -5884,13 +6292,22 @@
       <c r="AB44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE44" s="2" t="inlineStr"/>
+          <t>["R02274-E01", "R02274-E02"]</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:31:27.883247+00:00</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -5994,6 +6411,7 @@
         </is>
       </c>
       <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -6043,22 +6461,58 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>消化前浓缩污泥</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>空气0.05 vvm，24h；联合零价铁3–60 g/L</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>blank、单独曝气、曝气加不同零价铁；三次重复</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr"/>
-      <c r="V46" s="2" t="inlineStr"/>
-      <c r="W46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>韩文完整2研究内容及方法（2.1样品、2.2预处理、2.3分析项）：ORP/DO/COD/SCOD/TN/氨氮/TS/VS，表2列测定仪及标准法，无核酸测序。</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整2研究内容及方法，p.3表1/2；全9页文字可读并定位核查</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02319/fulltext/fulltext__version_unverified__bee09adb76fa2153.pdf"]</t>
@@ -6082,13 +6536,22 @@
       <c r="AB46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE46" s="2" t="inlineStr"/>
+          <t>["R02319-E01", "R02319-E02"]</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:31:27.912694+00:00</t>
+        </is>
+      </c>
+      <c r="AF46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -6138,22 +6601,58 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>城市固体垃圾筛下部分</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>半好氧预曝气50 L/d，连续或每日12h间歇供气</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>IAa/IAb间歇、CAa/CAb连续、ANa/ANb厌氧对照；后续厌氧阶段</t>
+        </is>
+      </c>
       <c r="S47" s="2" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr"/>
       <c r="U47" s="2" t="inlineStr"/>
-      <c r="V47" s="2" t="inlineStr"/>
-      <c r="W47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.1–2.4完整为废物、柱反应器、阶段/产气Gompertz模型及理化分析；气体仪、COD/TOC/VFA/氮/硫酸盐/氯离子、呼吸指数及浸出试验；没有核酸测序或公开组学重分析。</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Materials and methods；全10页定位检查</t>
+        </is>
+      </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02340/fulltext/fulltext__published__97fce73e3525cec6.pdf"]</t>
@@ -6177,13 +6676,22 @@
       <c r="AB47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE47" s="2" t="inlineStr"/>
+          <t>["R02340-E01", "R02340-E02"]</t>
+        </is>
+      </c>
+      <c r="AE47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:31:27.943151+00:00</t>
+        </is>
+      </c>
+      <c r="AF47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -6229,22 +6737,58 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>显微镜/染色、甲烷活性及理化；未测序</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>市政剩余活性污泥；补加硫酸钠</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>空气连续底部供给1.7 L/d</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>两台10 L反应器，微好氧与厌氧对照，40°C</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr"/>
       <c r="U48" s="2" t="inlineStr"/>
-      <c r="V48" s="2" t="inlineStr"/>
-      <c r="W48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>完整Material and methods为污泥组成、SMA产甲烷活性、泡沫、Microscopy和CST。群落观察用湿片及Gram/Neisser染色，元素为XRF，非核酸测序。原件2011年页脚与原表年份差异沿用原核验记录，不改分类。</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Material and methods；全6页定位检查</t>
+        </is>
+      </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02370/fulltext/fulltext__published__534deaaf21ea8112.pdf"]</t>
@@ -6268,13 +6812,22 @@
       <c r="AB48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE48" s="2" t="inlineStr"/>
+          <t>["R02370-E01", "R02370-E02"]</t>
+        </is>
+      </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:32:48.389432+00:00</t>
+        </is>
+      </c>
+      <c r="AF48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -6324,22 +6877,58 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>16S V3 PCR-DGGE、克隆及Sanger测序</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标16S序列）</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆；热处理猪粪消化接种物</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>针筒不同微供氧量；10 L试验选择0.28 mL/(gTS·d)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>微好氧/厌氧发酵产氢；瓶试验及10 L放大</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr"/>
       <c r="U49" s="2" t="inlineStr"/>
-      <c r="V49" s="2" t="inlineStr"/>
-      <c r="W49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>方法明确341F/518R扩增16S rDNA V3、DGGE、切条带再扩增克隆并用双脱氧终止法测序；不是shotgun或RNA-seq。候选5个附件文本已读，仅反应器图及产氢/VFA/pH/ORP数据，唯一关联仍保留待核实，不据目录分配编号。</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Materials and methods；p.6条带结果，全9页相关位置核查；5件候选附件全部文本</t>
+        </is>
+      </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02386/fulltext/fulltext__published__1c804bc9cfc3b614.pdf"]</t>
@@ -6363,13 +6952,22 @@
       <c r="AB49" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4 TXT为产氢/化学指标时间序列，1 DOCX为10 L装置图注；未含测序编号。缺题名/DOI的唯一归属未解决，维持独立附件复核队列。</t>
+        </is>
+      </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE49" s="2" t="inlineStr"/>
+          <t>["R02386-E01", "R02386-E02"]</t>
+        </is>
+      </c>
+      <c r="AE49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:32:48.419189+00:00</t>
+        </is>
+      </c>
+      <c r="AF49" s="2" t="inlineStr"/>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -6419,22 +7017,62 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>16S扩增子Illumina MiSeq（方法转引R02176）</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标扩增子）</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆；BS/AS/ER三种接种群落</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>55°C预处理，注氧0/5/10/20 mL/g VS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>不同接种物与供氧量比较；双份AD</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（沿用16S扩增子方法）</t>
+        </is>
+      </c>
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr"/>
-      <c r="V50" s="2" t="inlineStr"/>
-      <c r="W50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>完整Methods 2.1–2.5：测序文库与MiSeq明确按参考文献19（Fu2015，198:497–502）执行；该引用与库内R02176完全匹配，其已取得正文2.6明确16S V3–V5引物及MetaVx扩增子库。结合自身群落分类结果，判为16S扩增子，不因平台名自动分类。</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.1–2完整Materials and methods，p.6参考文献19，pp.4–5群落结果；R02176 p.2被引具体建库方法；全6页定位核查</t>
+        </is>
+      </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02444/fulltext/fulltext__published__a3cb2ae853beb60c.pdf"]</t>
@@ -6458,13 +7096,22 @@
       <c r="AB50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE50" s="2" t="inlineStr"/>
+          <t>["R02444-E01", "R02444-E02", "R02444-E03"]</t>
+        </is>
+      </c>
+      <c r="AE50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:32:48.460930+00:00</t>
+        </is>
+      </c>
+      <c r="AF50" s="2" t="inlineStr"/>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -6514,22 +7161,58 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>FISH及微生物活性试验；未测序</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>高温消化污泥；活性试验底物为淀粉、葡萄糖和VFA混合物</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>介质预曝气至4.3或8.8 mg O2/L，再接种进行活性试验</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>不同氧水平及不曝气blank；水解/产酸/产甲烷活性试验</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="inlineStr"/>
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr"/>
-      <c r="V51" s="2" t="inlineStr"/>
-      <c r="W51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>完整2.1–2.4为高温生物质、活性试验、化学/气体分析和FISH。FISH识别active microbial populations并非社区RNA-seq；没有核酸测序。</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>PDF p.2完整Materials and methods；全4页定位检查</t>
+        </is>
+      </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02454/fulltext/fulltext__published__59977732e1c6bb84.pdf"]</t>
@@ -6553,13 +7236,22 @@
       <c r="AB51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>正文提及补充图，但当前无独立SI原件；不声称已取得或检查缺失附件。</t>
+        </is>
+      </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE51" s="2" t="inlineStr"/>
+          <t>["R02454-E01", "R02454-E02"]</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:33:31.841878+00:00</t>
+        </is>
+      </c>
+      <c r="AF51" s="2" t="inlineStr"/>
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -6609,22 +7301,62 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>16S V3–V4/V4–V5扩增子MiSeq</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标扩增子）</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>55°C AD每日注入空气0/12.5/25/50/100 mL/LR</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>T0–T4供气量；群落比较T0/T1；SMA另设MO/WO</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S扩增子）</t>
+        </is>
+      </c>
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" s="2" t="inlineStr"/>
-      <c r="W52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Methods 2.5明确MetaVx、16S V3/V4/V5靶向引物和adapter扩增子文库；MiSeq/QIIME分类，非shotgun或社区RNA-seq。SMA由产气测定而非转录组。</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–3完整Material and methods；p.4明确16S结果；全6页定位检查</t>
+        </is>
+      </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02578/fulltext/fulltext__published__6966d35ad0d267fc.pdf"]</t>
@@ -6648,13 +7380,22 @@
       <c r="AB52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE52" s="2" t="inlineStr"/>
+          <t>["R02578-E01", "R02578-E02"]</t>
+        </is>
+      </c>
+      <c r="AE52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:33:31.869872+00:00</t>
+        </is>
+      </c>
+      <c r="AF52" s="2" t="inlineStr"/>
     </row>
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -6704,22 +7445,58 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>水稻秸秆</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>理论氧需求0.5–10倍供氧；另比较空气</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>35°C/55°C发酵，不供氧对照，不同氧量；三次重复</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="inlineStr"/>
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr"/>
-      <c r="V53" s="2" t="inlineStr"/>
-      <c r="W53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>完整Material and Methods为底物/接种物、发酵装置与供氧设计、排水计气、TS/VS重量法、GC气体和H2S标准法，没有核酸提取、建库或测序。</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.3–4完整Material and Methods；全9页定位检查</t>
+        </is>
+      </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02585/fulltext/fulltext__published__ece7fec3277a694d.pdf"]</t>
@@ -6743,13 +7520,22 @@
       <c r="AB53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE53" s="2" t="inlineStr"/>
+          <t>["R02585-E01", "R02585-E02"]</t>
+        </is>
+      </c>
+      <c r="AE53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:33:31.897610+00:00</t>
+        </is>
+      </c>
+      <c r="AF53" s="2" t="inlineStr"/>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -6799,22 +7585,58 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>剩余活性污泥和初沉污泥混合物</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>35°C空气0.1–0.5 vvm，优化0.35 vvm</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>三组实验，未曝气对照/曝气量与时长比较，双份</t>
+        </is>
+      </c>
       <c r="S54" s="2" t="inlineStr"/>
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" s="2" t="inlineStr"/>
-      <c r="W54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>31页接受稿完整Materials and methods pp.5–7：BMP排水计气/NaOH吸收CO2、COD/VSS标准法、蛋白/总糖ASTM及统计。无核酸提取或测序；pp.22–23低文字页经渲染查看为蛋白/总糖曲线，不是漏解析方法。</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.5–7完整Materials and methods、pp.29–31表格；全31页定位；pp.22–23图像原页核查</t>
+        </is>
+      </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02719/fulltext/fulltext__version_unverified__4bf5e309b2ef3431.pdf"]</t>
@@ -6838,13 +7660,22 @@
       <c r="AB54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE54" s="2" t="inlineStr"/>
+          <t>["R02719-E01", "R02719-E02"]</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:34:07.181695+00:00</t>
+        </is>
+      </c>
+      <c r="AF54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -6894,22 +7725,58 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>16S PCR-DGGE指纹；未报告shotgun/RNA测序</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>不适用（仅非目标16S指纹）</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>乙醇合成低硫酸盐废水</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>空气直接顶空注入0.2 mL/min</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>R1厌氧沼气碱洗、R2顶空微曝气；接种/厌氧末/微好氧末群落比较</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="inlineStr"/>
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr"/>
-      <c r="V55" s="2" t="inlineStr"/>
-      <c r="W55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods pp.2–6：细菌16S V6–V8、古菌V2–V3 PCR-DGGE，凝胶图谱统计；功能组织度F0来自DGGE曲线，非功能基因组/转录组。未报告shotgun或社区RNA测序。</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–6完整Materials and methods、pp.10–12 DGGE结果；全15页定位核查</t>
+        </is>
+      </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02819/fulltext/fulltext__published__bf9c210e52bacc5f.pdf"]</t>
@@ -6933,13 +7800,22 @@
       <c r="AB55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE55" s="2" t="inlineStr"/>
+          <t>["R02819-E01", "R02819-E02"]</t>
+        </is>
+      </c>
+      <c r="AE55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:34:07.209977+00:00</t>
+        </is>
+      </c>
+      <c r="AF55" s="2" t="inlineStr"/>
     </row>
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -7043,6 +7919,7 @@
         </is>
       </c>
       <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -7092,22 +7969,58 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>回流活性污泥RAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>水族泵间歇曝气3h:3h，24h后厌氧24h，循环5次</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>3台间歇反应器与3台严格厌氧对照；15°C</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="inlineStr"/>
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr"/>
-      <c r="V57" s="2" t="inlineStr"/>
-      <c r="W57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods为6台反应器、COD/氨/磷/TSS/VSS测定、由氨磷释放和COD计算水解速率及ANOVA。微生物功能解释来自化学计量模型，并非PICRUSt或核酸测序。</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Materials and methods；全8页定位和章节核查</t>
+        </is>
+      </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
           <t>["original_files/R02946/fulltext/fulltext__published__7443ff37439e4d1e.pdf"]</t>
@@ -7131,13 +8044,22 @@
       <c r="AB57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE57" s="2" t="inlineStr"/>
+          <t>["R02946-E01", "R02946-E02"]</t>
+        </is>
+      </c>
+      <c r="AE57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:35:30.340949+00:00</t>
+        </is>
+      </c>
+      <c r="AF57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -7237,6 +8159,7 @@
         </is>
       </c>
       <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -7286,22 +8209,58 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="2" t="inlineStr"/>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>奶牛粪液相</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>田间消化器顶空间歇供气；脱硫桶顶空连续空气</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>六台2m3田间消化器不曝气/低/高曝气；65/104L脱硫桶表面积及有无吸水布比较</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="inlineStr"/>
       <c r="T59" s="2" t="inlineStr"/>
       <c r="U59" s="2" t="inlineStr"/>
-      <c r="V59" s="2" t="inlineStr"/>
-      <c r="W59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods pp.2–4为粪液、田间消化器、脱硫桶、气体仪、TS/VS/pH/碱度和统计；无核酸测序。已读S1 Appendix全部三工作表，是图2/3/5物化数据；泛指data in paper/SI不代表有raw reads。</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>PDF pp.2–4完整Materials and methods，p.1数据声明及p.11 Supporting information；全12页定位；XLSX三工作表全部非空单元格</t>
+        </is>
+      </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03161/fulltext/fulltext__published__ea90043284b5a305.pdf"]</t>
@@ -7325,13 +8284,22 @@
       <c r="AB59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>官方关联S1 Appendix（SHA已核对）；Figure 5 data 60×11、Figure 2 data 39×35、Figure 3 data 51×6全部读取，细胞位置见证据。</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE59" s="2" t="inlineStr"/>
+          <t>["R03161-E01", "R03161-E02", "R03161-E03"]</t>
+        </is>
+      </c>
+      <c r="AE59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:35:30.387773+00:00</t>
+        </is>
+      </c>
+      <c r="AF59" s="2" t="inlineStr"/>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -7427,6 +8395,7 @@
         </is>
       </c>
       <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -7522,6 +8491,7 @@
         </is>
       </c>
       <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -7621,6 +8591,7 @@
         </is>
       </c>
       <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="60" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -7716,6 +8687,7 @@
         </is>
       </c>
       <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
     </row>
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -7811,6 +8783,7 @@
         </is>
       </c>
       <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
     </row>
     <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -7906,6 +8879,7 @@
         </is>
       </c>
       <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
     </row>
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -8009,6 +8983,7 @@
         </is>
       </c>
       <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
     </row>
     <row r="67" ht="60" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -8104,6 +9079,7 @@
         </is>
       </c>
       <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -8199,6 +9175,7 @@
         </is>
       </c>
       <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
     </row>
     <row r="69" ht="60" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -8294,6 +9271,7 @@
         </is>
       </c>
       <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
     </row>
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -8389,6 +9367,7 @@
         </is>
       </c>
       <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -8484,6 +9463,7 @@
         </is>
       </c>
       <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
     </row>
     <row r="72" ht="60" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -8587,6 +9567,7 @@
         </is>
       </c>
       <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
     </row>
     <row r="73" ht="60" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -8690,6 +9671,7 @@
         </is>
       </c>
       <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
     </row>
     <row r="74" ht="60" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -8785,6 +9767,7 @@
         </is>
       </c>
       <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
     </row>
     <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -8888,6 +9871,7 @@
         </is>
       </c>
       <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
     </row>
     <row r="76" ht="60" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -8983,6 +9967,7 @@
         </is>
       </c>
       <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -9086,6 +10071,7 @@
         </is>
       </c>
       <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
     </row>
     <row r="78" ht="60" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -9181,6 +10167,7 @@
         </is>
       </c>
       <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="60" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -9276,6 +10263,7 @@
         </is>
       </c>
       <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -9371,6 +10359,7 @@
         </is>
       </c>
       <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="60" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -9466,6 +10455,7 @@
         </is>
       </c>
       <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="60" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -9569,6 +10559,7 @@
         </is>
       </c>
       <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="60" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -9664,6 +10655,7 @@
         </is>
       </c>
       <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="60" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -9759,6 +10751,7 @@
         </is>
       </c>
       <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="60" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -9854,6 +10847,7 @@
         </is>
       </c>
       <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="60" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -9949,6 +10943,7 @@
         </is>
       </c>
       <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="60" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
@@ -10048,6 +11043,7 @@
         </is>
       </c>
       <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="60" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -10143,6 +11139,7 @@
         </is>
       </c>
       <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="60" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -10234,6 +11231,7 @@
         </is>
       </c>
       <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="60" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -10337,6 +11335,7 @@
         </is>
       </c>
       <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="60" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
@@ -10432,6 +11431,7 @@
         </is>
       </c>
       <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="60" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -10527,6 +11527,7 @@
         </is>
       </c>
       <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="60" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -10622,6 +11623,7 @@
         </is>
       </c>
       <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="60" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -10725,6 +11727,7 @@
         </is>
       </c>
       <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="60" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -10820,6 +11823,7 @@
         </is>
       </c>
       <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="60" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -10915,6 +11919,7 @@
         </is>
       </c>
       <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="60" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -11010,6 +12015,7 @@
         </is>
       </c>
       <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="60" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -11105,6 +12111,7 @@
         </is>
       </c>
       <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="60" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
@@ -11200,6 +12207,7 @@
         </is>
       </c>
       <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="60" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -11299,6 +12307,7 @@
         </is>
       </c>
       <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
     </row>
     <row r="101" ht="60" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
@@ -11394,6 +12403,7 @@
         </is>
       </c>
       <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
     </row>
     <row r="102" ht="60" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -11497,6 +12507,7 @@
         </is>
       </c>
       <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
     </row>
     <row r="103" ht="60" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
@@ -11592,6 +12603,7 @@
         </is>
       </c>
       <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="60" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -11695,6 +12707,7 @@
         </is>
       </c>
       <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
     </row>
     <row r="105" ht="60" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
@@ -11790,6 +12803,7 @@
         </is>
       </c>
       <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
     </row>
     <row r="106" ht="60" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -11885,6 +12899,7 @@
         </is>
       </c>
       <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
     </row>
     <row r="107" ht="60" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
@@ -11980,6 +12995,7 @@
         </is>
       </c>
       <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
     </row>
     <row r="108" ht="60" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -12075,6 +13091,7 @@
         </is>
       </c>
       <c r="AE108" s="2" t="inlineStr"/>
+      <c r="AF108" s="2" t="inlineStr"/>
     </row>
     <row r="109" ht="60" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
@@ -12174,6 +13191,7 @@
         </is>
       </c>
       <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
     </row>
     <row r="110" ht="60" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -12269,6 +13287,7 @@
         </is>
       </c>
       <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
     </row>
     <row r="111" ht="60" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
@@ -12364,6 +13383,7 @@
         </is>
       </c>
       <c r="AE111" s="2" t="inlineStr"/>
+      <c r="AF111" s="2" t="inlineStr"/>
     </row>
     <row r="112" ht="60" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -12459,6 +13479,7 @@
         </is>
       </c>
       <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
     </row>
     <row r="113" ht="60" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -12554,6 +13575,7 @@
         </is>
       </c>
       <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
     </row>
     <row r="114" ht="60" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -12649,6 +13671,7 @@
         </is>
       </c>
       <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
     </row>
     <row r="115" ht="60" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
@@ -12744,6 +13767,7 @@
         </is>
       </c>
       <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
     </row>
     <row r="116" ht="60" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -12839,6 +13863,7 @@
         </is>
       </c>
       <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
     </row>
     <row r="117" ht="60" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
@@ -12934,6 +13959,7 @@
         </is>
       </c>
       <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
     </row>
     <row r="118" ht="60" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -13029,6 +14055,7 @@
         </is>
       </c>
       <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
     </row>
     <row r="119" ht="60" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
@@ -13124,6 +14151,7 @@
         </is>
       </c>
       <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
     </row>
     <row r="120" ht="60" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -13219,6 +14247,7 @@
         </is>
       </c>
       <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
     </row>
     <row r="121" ht="60" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
@@ -13314,6 +14343,7 @@
         </is>
       </c>
       <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
     </row>
     <row r="122" ht="60" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -13409,6 +14439,7 @@
         </is>
       </c>
       <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
     </row>
     <row r="123" ht="60" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
@@ -13504,6 +14535,7 @@
         </is>
       </c>
       <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
     </row>
     <row r="124" ht="60" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -13599,6 +14631,7 @@
         </is>
       </c>
       <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
     </row>
     <row r="125" ht="60" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
@@ -13702,6 +14735,7 @@
         </is>
       </c>
       <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
     </row>
     <row r="126" ht="60" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -13797,6 +14831,7 @@
         </is>
       </c>
       <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
     </row>
     <row r="127" ht="60" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
@@ -13900,6 +14935,7 @@
         </is>
       </c>
       <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
     </row>
     <row r="128" ht="60" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -13995,6 +15031,7 @@
         </is>
       </c>
       <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
     </row>
     <row r="129" ht="60" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
@@ -14090,6 +15127,7 @@
         </is>
       </c>
       <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
     </row>
     <row r="130" ht="60" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -14185,6 +15223,7 @@
         </is>
       </c>
       <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
     </row>
     <row r="131" ht="60" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -14280,6 +15319,7 @@
         </is>
       </c>
       <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
     </row>
     <row r="132" ht="60" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -14375,6 +15415,7 @@
         </is>
       </c>
       <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
     </row>
     <row r="133" ht="60" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
@@ -14470,6 +15511,7 @@
         </is>
       </c>
       <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
     </row>
     <row r="134" ht="60" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -14565,6 +15607,7 @@
         </is>
       </c>
       <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
     </row>
     <row r="135" ht="60" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
@@ -14660,6 +15703,7 @@
         </is>
       </c>
       <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
     </row>
     <row r="136" ht="60" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -14755,6 +15799,7 @@
         </is>
       </c>
       <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
     </row>
     <row r="137" ht="60" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
@@ -14850,6 +15895,7 @@
         </is>
       </c>
       <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
     </row>
     <row r="138" ht="60" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -14945,6 +15991,7 @@
         </is>
       </c>
       <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
     </row>
     <row r="139" ht="60" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
@@ -15040,6 +16087,7 @@
         </is>
       </c>
       <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
     </row>
     <row r="140" ht="60" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -15135,6 +16183,7 @@
         </is>
       </c>
       <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
     </row>
     <row r="141" ht="60" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
@@ -15230,6 +16279,7 @@
         </is>
       </c>
       <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
     </row>
     <row r="142" ht="60" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -15325,6 +16375,7 @@
         </is>
       </c>
       <c r="AE142" s="2" t="inlineStr"/>
+      <c r="AF142" s="2" t="inlineStr"/>
     </row>
     <row r="143" ht="60" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
@@ -15420,6 +16471,7 @@
         </is>
       </c>
       <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
     </row>
     <row r="144" ht="60" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
@@ -15523,6 +16575,7 @@
         </is>
       </c>
       <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
     </row>
     <row r="145" ht="60" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
@@ -15626,6 +16679,7 @@
         </is>
       </c>
       <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
     </row>
     <row r="146" ht="60" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -15721,6 +16775,7 @@
         </is>
       </c>
       <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
     </row>
     <row r="147" ht="60" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
@@ -15816,6 +16871,7 @@
         </is>
       </c>
       <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
     </row>
     <row r="148" ht="60" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -15911,6 +16967,7 @@
         </is>
       </c>
       <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
     </row>
     <row r="149" ht="60" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
@@ -16014,6 +17071,7 @@
         </is>
       </c>
       <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
     </row>
     <row r="150" ht="60" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -16109,6 +17167,7 @@
         </is>
       </c>
       <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
     </row>
     <row r="151" ht="60" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
@@ -16212,6 +17271,7 @@
         </is>
       </c>
       <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
     </row>
     <row r="152" ht="60" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -16307,6 +17367,7 @@
         </is>
       </c>
       <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
     </row>
     <row r="153" ht="60" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
@@ -16410,6 +17471,7 @@
         </is>
       </c>
       <c r="AE153" s="2" t="inlineStr"/>
+      <c r="AF153" s="2" t="inlineStr"/>
     </row>
     <row r="154" ht="60" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -16505,6 +17567,7 @@
         </is>
       </c>
       <c r="AE154" s="2" t="inlineStr"/>
+      <c r="AF154" s="2" t="inlineStr"/>
     </row>
     <row r="155" ht="60" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
@@ -16600,6 +17663,7 @@
         </is>
       </c>
       <c r="AE155" s="2" t="inlineStr"/>
+      <c r="AF155" s="2" t="inlineStr"/>
     </row>
     <row r="156" ht="60" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -16695,6 +17759,7 @@
         </is>
       </c>
       <c r="AE156" s="2" t="inlineStr"/>
+      <c r="AF156" s="2" t="inlineStr"/>
     </row>
     <row r="157" ht="60" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
@@ -16794,6 +17859,7 @@
         </is>
       </c>
       <c r="AE157" s="2" t="inlineStr"/>
+      <c r="AF157" s="2" t="inlineStr"/>
     </row>
     <row r="158" ht="60" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -16897,6 +17963,7 @@
         </is>
       </c>
       <c r="AE158" s="2" t="inlineStr"/>
+      <c r="AF158" s="2" t="inlineStr"/>
     </row>
     <row r="159" ht="60" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
@@ -17000,6 +18067,7 @@
         </is>
       </c>
       <c r="AE159" s="2" t="inlineStr"/>
+      <c r="AF159" s="2" t="inlineStr"/>
     </row>
     <row r="160" ht="60" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -17095,6 +18163,7 @@
         </is>
       </c>
       <c r="AE160" s="2" t="inlineStr"/>
+      <c r="AF160" s="2" t="inlineStr"/>
     </row>
     <row r="161" ht="60" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
@@ -17198,6 +18267,7 @@
         </is>
       </c>
       <c r="AE161" s="2" t="inlineStr"/>
+      <c r="AF161" s="2" t="inlineStr"/>
     </row>
     <row r="162" ht="60" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -17293,6 +18363,7 @@
         </is>
       </c>
       <c r="AE162" s="2" t="inlineStr"/>
+      <c r="AF162" s="2" t="inlineStr"/>
     </row>
     <row r="163" ht="60" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
@@ -17388,6 +18459,7 @@
         </is>
       </c>
       <c r="AE163" s="2" t="inlineStr"/>
+      <c r="AF163" s="2" t="inlineStr"/>
     </row>
     <row r="164" ht="60" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -17483,6 +18555,7 @@
         </is>
       </c>
       <c r="AE164" s="2" t="inlineStr"/>
+      <c r="AF164" s="2" t="inlineStr"/>
     </row>
     <row r="165" ht="60" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
@@ -17578,6 +18651,7 @@
         </is>
       </c>
       <c r="AE165" s="2" t="inlineStr"/>
+      <c r="AF165" s="2" t="inlineStr"/>
     </row>
     <row r="166" ht="60" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -17673,6 +18747,7 @@
         </is>
       </c>
       <c r="AE166" s="2" t="inlineStr"/>
+      <c r="AF166" s="2" t="inlineStr"/>
     </row>
     <row r="167" ht="60" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
@@ -17768,6 +18843,7 @@
         </is>
       </c>
       <c r="AE167" s="2" t="inlineStr"/>
+      <c r="AF167" s="2" t="inlineStr"/>
     </row>
     <row r="168" ht="60" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -17863,6 +18939,7 @@
         </is>
       </c>
       <c r="AE168" s="2" t="inlineStr"/>
+      <c r="AF168" s="2" t="inlineStr"/>
     </row>
     <row r="169" ht="60" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
@@ -17958,6 +19035,7 @@
         </is>
       </c>
       <c r="AE169" s="2" t="inlineStr"/>
+      <c r="AF169" s="2" t="inlineStr"/>
     </row>
     <row r="170" ht="60" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -18053,6 +19131,7 @@
         </is>
       </c>
       <c r="AE170" s="2" t="inlineStr"/>
+      <c r="AF170" s="2" t="inlineStr"/>
     </row>
     <row r="171" ht="60" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
@@ -18156,6 +19235,7 @@
         </is>
       </c>
       <c r="AE171" s="2" t="inlineStr"/>
+      <c r="AF171" s="2" t="inlineStr"/>
     </row>
     <row r="172" ht="60" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -18251,6 +19331,7 @@
         </is>
       </c>
       <c r="AE172" s="2" t="inlineStr"/>
+      <c r="AF172" s="2" t="inlineStr"/>
     </row>
     <row r="173" ht="60" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
@@ -18346,6 +19427,7 @@
         </is>
       </c>
       <c r="AE173" s="2" t="inlineStr"/>
+      <c r="AF173" s="2" t="inlineStr"/>
     </row>
     <row r="174" ht="60" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -18441,6 +19523,7 @@
         </is>
       </c>
       <c r="AE174" s="2" t="inlineStr"/>
+      <c r="AF174" s="2" t="inlineStr"/>
     </row>
     <row r="175" ht="60" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
@@ -18536,6 +19619,7 @@
         </is>
       </c>
       <c r="AE175" s="2" t="inlineStr"/>
+      <c r="AF175" s="2" t="inlineStr"/>
     </row>
     <row r="176" ht="60" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -18631,6 +19715,7 @@
         </is>
       </c>
       <c r="AE176" s="2" t="inlineStr"/>
+      <c r="AF176" s="2" t="inlineStr"/>
     </row>
     <row r="177" ht="60" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
@@ -18734,6 +19819,7 @@
         </is>
       </c>
       <c r="AE177" s="2" t="inlineStr"/>
+      <c r="AF177" s="2" t="inlineStr"/>
     </row>
     <row r="178" ht="60" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -18837,6 +19923,7 @@
         </is>
       </c>
       <c r="AE178" s="2" t="inlineStr"/>
+      <c r="AF178" s="2" t="inlineStr"/>
     </row>
     <row r="179" ht="60" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
@@ -18940,6 +20027,7 @@
         </is>
       </c>
       <c r="AE179" s="2" t="inlineStr"/>
+      <c r="AF179" s="2" t="inlineStr"/>
     </row>
     <row r="180" ht="60" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
@@ -19035,6 +20123,7 @@
         </is>
       </c>
       <c r="AE180" s="2" t="inlineStr"/>
+      <c r="AF180" s="2" t="inlineStr"/>
     </row>
     <row r="181" ht="60" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
@@ -19130,6 +20219,7 @@
         </is>
       </c>
       <c r="AE181" s="2" t="inlineStr"/>
+      <c r="AF181" s="2" t="inlineStr"/>
     </row>
     <row r="182" ht="60" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
@@ -19225,6 +20315,7 @@
         </is>
       </c>
       <c r="AE182" s="2" t="inlineStr"/>
+      <c r="AF182" s="2" t="inlineStr"/>
     </row>
     <row r="183" ht="60" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
@@ -19320,6 +20411,7 @@
         </is>
       </c>
       <c r="AE183" s="2" t="inlineStr"/>
+      <c r="AF183" s="2" t="inlineStr"/>
     </row>
     <row r="184" ht="60" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -19415,6 +20507,7 @@
         </is>
       </c>
       <c r="AE184" s="2" t="inlineStr"/>
+      <c r="AF184" s="2" t="inlineStr"/>
     </row>
     <row r="185" ht="60" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
@@ -19510,6 +20603,7 @@
         </is>
       </c>
       <c r="AE185" s="2" t="inlineStr"/>
+      <c r="AF185" s="2" t="inlineStr"/>
     </row>
     <row r="186" ht="60" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -19605,6 +20699,7 @@
         </is>
       </c>
       <c r="AE186" s="2" t="inlineStr"/>
+      <c r="AF186" s="2" t="inlineStr"/>
     </row>
     <row r="187" ht="60" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
@@ -19708,6 +20803,7 @@
         </is>
       </c>
       <c r="AE187" s="2" t="inlineStr"/>
+      <c r="AF187" s="2" t="inlineStr"/>
     </row>
     <row r="188" ht="60" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -19811,6 +20907,7 @@
         </is>
       </c>
       <c r="AE188" s="2" t="inlineStr"/>
+      <c r="AF188" s="2" t="inlineStr"/>
     </row>
     <row r="189" ht="60" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
@@ -19906,6 +21003,7 @@
         </is>
       </c>
       <c r="AE189" s="2" t="inlineStr"/>
+      <c r="AF189" s="2" t="inlineStr"/>
     </row>
     <row r="190" ht="60" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -20001,6 +21099,7 @@
         </is>
       </c>
       <c r="AE190" s="2" t="inlineStr"/>
+      <c r="AF190" s="2" t="inlineStr"/>
     </row>
     <row r="191" ht="60" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
@@ -20104,6 +21203,7 @@
         </is>
       </c>
       <c r="AE191" s="2" t="inlineStr"/>
+      <c r="AF191" s="2" t="inlineStr"/>
     </row>
     <row r="192" ht="60" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -20207,6 +21307,7 @@
         </is>
       </c>
       <c r="AE192" s="2" t="inlineStr"/>
+      <c r="AF192" s="2" t="inlineStr"/>
     </row>
     <row r="193" ht="60" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
@@ -20302,6 +21403,7 @@
         </is>
       </c>
       <c r="AE193" s="2" t="inlineStr"/>
+      <c r="AF193" s="2" t="inlineStr"/>
     </row>
     <row r="194" ht="60" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -20405,6 +21507,7 @@
         </is>
       </c>
       <c r="AE194" s="2" t="inlineStr"/>
+      <c r="AF194" s="2" t="inlineStr"/>
     </row>
     <row r="195" ht="60" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
@@ -20500,6 +21603,7 @@
         </is>
       </c>
       <c r="AE195" s="2" t="inlineStr"/>
+      <c r="AF195" s="2" t="inlineStr"/>
     </row>
     <row r="196" ht="60" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -20595,6 +21699,7 @@
         </is>
       </c>
       <c r="AE196" s="2" t="inlineStr"/>
+      <c r="AF196" s="2" t="inlineStr"/>
     </row>
     <row r="197" ht="60" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
@@ -20698,6 +21803,7 @@
         </is>
       </c>
       <c r="AE197" s="2" t="inlineStr"/>
+      <c r="AF197" s="2" t="inlineStr"/>
     </row>
     <row r="198" ht="60" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -20801,6 +21907,7 @@
         </is>
       </c>
       <c r="AE198" s="2" t="inlineStr"/>
+      <c r="AF198" s="2" t="inlineStr"/>
     </row>
     <row r="199" ht="60" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
@@ -20896,6 +22003,7 @@
         </is>
       </c>
       <c r="AE199" s="2" t="inlineStr"/>
+      <c r="AF199" s="2" t="inlineStr"/>
     </row>
     <row r="200" ht="60" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
@@ -20999,6 +22107,7 @@
         </is>
       </c>
       <c r="AE200" s="2" t="inlineStr"/>
+      <c r="AF200" s="2" t="inlineStr"/>
     </row>
     <row r="201" ht="60" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
@@ -21094,6 +22203,7 @@
         </is>
       </c>
       <c r="AE201" s="2" t="inlineStr"/>
+      <c r="AF201" s="2" t="inlineStr"/>
     </row>
     <row r="202" ht="60" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -21189,6 +22299,7 @@
         </is>
       </c>
       <c r="AE202" s="2" t="inlineStr"/>
+      <c r="AF202" s="2" t="inlineStr"/>
     </row>
     <row r="203" ht="60" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
@@ -21284,6 +22395,7 @@
         </is>
       </c>
       <c r="AE203" s="2" t="inlineStr"/>
+      <c r="AF203" s="2" t="inlineStr"/>
     </row>
     <row r="204" ht="60" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -21379,6 +22491,7 @@
         </is>
       </c>
       <c r="AE204" s="2" t="inlineStr"/>
+      <c r="AF204" s="2" t="inlineStr"/>
     </row>
     <row r="205" ht="60" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
@@ -21474,6 +22587,7 @@
         </is>
       </c>
       <c r="AE205" s="2" t="inlineStr"/>
+      <c r="AF205" s="2" t="inlineStr"/>
     </row>
     <row r="206" ht="60" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -21569,6 +22683,7 @@
         </is>
       </c>
       <c r="AE206" s="2" t="inlineStr"/>
+      <c r="AF206" s="2" t="inlineStr"/>
     </row>
     <row r="207" ht="60" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
@@ -21672,6 +22787,7 @@
         </is>
       </c>
       <c r="AE207" s="2" t="inlineStr"/>
+      <c r="AF207" s="2" t="inlineStr"/>
     </row>
     <row r="208" ht="60" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
@@ -21767,6 +22883,7 @@
         </is>
       </c>
       <c r="AE208" s="2" t="inlineStr"/>
+      <c r="AF208" s="2" t="inlineStr"/>
     </row>
     <row r="209" ht="60" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
@@ -21862,6 +22979,7 @@
         </is>
       </c>
       <c r="AE209" s="2" t="inlineStr"/>
+      <c r="AF209" s="2" t="inlineStr"/>
     </row>
     <row r="210" ht="60" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
@@ -21957,6 +23075,7 @@
         </is>
       </c>
       <c r="AE210" s="2" t="inlineStr"/>
+      <c r="AF210" s="2" t="inlineStr"/>
     </row>
     <row r="211" ht="60" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
@@ -22052,6 +23171,7 @@
         </is>
       </c>
       <c r="AE211" s="2" t="inlineStr"/>
+      <c r="AF211" s="2" t="inlineStr"/>
     </row>
     <row r="212" ht="60" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -22147,6 +23267,7 @@
         </is>
       </c>
       <c r="AE212" s="2" t="inlineStr"/>
+      <c r="AF212" s="2" t="inlineStr"/>
     </row>
     <row r="213" ht="60" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
@@ -22242,6 +23363,7 @@
         </is>
       </c>
       <c r="AE213" s="2" t="inlineStr"/>
+      <c r="AF213" s="2" t="inlineStr"/>
     </row>
     <row r="214" ht="60" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
@@ -22345,6 +23467,7 @@
         </is>
       </c>
       <c r="AE214" s="2" t="inlineStr"/>
+      <c r="AF214" s="2" t="inlineStr"/>
     </row>
     <row r="215" ht="60" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
@@ -22448,6 +23571,7 @@
         </is>
       </c>
       <c r="AE215" s="2" t="inlineStr"/>
+      <c r="AF215" s="2" t="inlineStr"/>
     </row>
     <row r="216" ht="60" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -22543,6 +23667,7 @@
         </is>
       </c>
       <c r="AE216" s="2" t="inlineStr"/>
+      <c r="AF216" s="2" t="inlineStr"/>
     </row>
     <row r="217" ht="60" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
@@ -22646,6 +23771,7 @@
         </is>
       </c>
       <c r="AE217" s="2" t="inlineStr"/>
+      <c r="AF217" s="2" t="inlineStr"/>
     </row>
     <row r="218" ht="60" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
@@ -22741,6 +23867,7 @@
         </is>
       </c>
       <c r="AE218" s="2" t="inlineStr"/>
+      <c r="AF218" s="2" t="inlineStr"/>
     </row>
     <row r="219" ht="60" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
@@ -22836,6 +23963,7 @@
         </is>
       </c>
       <c r="AE219" s="2" t="inlineStr"/>
+      <c r="AF219" s="2" t="inlineStr"/>
     </row>
     <row r="220" ht="60" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
@@ -22931,6 +24059,7 @@
         </is>
       </c>
       <c r="AE220" s="2" t="inlineStr"/>
+      <c r="AF220" s="2" t="inlineStr"/>
     </row>
     <row r="221" ht="60" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
@@ -23026,6 +24155,7 @@
         </is>
       </c>
       <c r="AE221" s="2" t="inlineStr"/>
+      <c r="AF221" s="2" t="inlineStr"/>
     </row>
     <row r="222" ht="60" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
@@ -23121,6 +24251,7 @@
         </is>
       </c>
       <c r="AE222" s="2" t="inlineStr"/>
+      <c r="AF222" s="2" t="inlineStr"/>
     </row>
     <row r="223" ht="60" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
@@ -23216,6 +24347,7 @@
         </is>
       </c>
       <c r="AE223" s="2" t="inlineStr"/>
+      <c r="AF223" s="2" t="inlineStr"/>
     </row>
     <row r="224" ht="60" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -23311,6 +24443,7 @@
         </is>
       </c>
       <c r="AE224" s="2" t="inlineStr"/>
+      <c r="AF224" s="2" t="inlineStr"/>
     </row>
     <row r="225" ht="60" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
@@ -23406,6 +24539,7 @@
         </is>
       </c>
       <c r="AE225" s="2" t="inlineStr"/>
+      <c r="AF225" s="2" t="inlineStr"/>
     </row>
     <row r="226" ht="60" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
@@ -23501,6 +24635,7 @@
         </is>
       </c>
       <c r="AE226" s="2" t="inlineStr"/>
+      <c r="AF226" s="2" t="inlineStr"/>
     </row>
     <row r="227" ht="60" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
@@ -23604,6 +24739,7 @@
         </is>
       </c>
       <c r="AE227" s="2" t="inlineStr"/>
+      <c r="AF227" s="2" t="inlineStr"/>
     </row>
     <row r="228" ht="60" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
@@ -23699,6 +24835,7 @@
         </is>
       </c>
       <c r="AE228" s="2" t="inlineStr"/>
+      <c r="AF228" s="2" t="inlineStr"/>
     </row>
     <row r="229" ht="60" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
@@ -23794,6 +24931,7 @@
         </is>
       </c>
       <c r="AE229" s="2" t="inlineStr"/>
+      <c r="AF229" s="2" t="inlineStr"/>
     </row>
     <row r="230" ht="60" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
@@ -23889,6 +25027,7 @@
         </is>
       </c>
       <c r="AE230" s="2" t="inlineStr"/>
+      <c r="AF230" s="2" t="inlineStr"/>
     </row>
     <row r="231" ht="60" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
@@ -23984,6 +25123,7 @@
         </is>
       </c>
       <c r="AE231" s="2" t="inlineStr"/>
+      <c r="AF231" s="2" t="inlineStr"/>
     </row>
     <row r="232" ht="60" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
@@ -24087,6 +25227,7 @@
         </is>
       </c>
       <c r="AE232" s="2" t="inlineStr"/>
+      <c r="AF232" s="2" t="inlineStr"/>
     </row>
     <row r="233" ht="60" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
@@ -24182,6 +25323,7 @@
         </is>
       </c>
       <c r="AE233" s="2" t="inlineStr"/>
+      <c r="AF233" s="2" t="inlineStr"/>
     </row>
     <row r="234" ht="60" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
@@ -24277,6 +25419,7 @@
         </is>
       </c>
       <c r="AE234" s="2" t="inlineStr"/>
+      <c r="AF234" s="2" t="inlineStr"/>
     </row>
     <row r="235" ht="60" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
@@ -24372,6 +25515,7 @@
         </is>
       </c>
       <c r="AE235" s="2" t="inlineStr"/>
+      <c r="AF235" s="2" t="inlineStr"/>
     </row>
     <row r="236" ht="60" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
@@ -24475,6 +25619,7 @@
         </is>
       </c>
       <c r="AE236" s="2" t="inlineStr"/>
+      <c r="AF236" s="2" t="inlineStr"/>
     </row>
     <row r="237" ht="60" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
@@ -24570,6 +25715,7 @@
         </is>
       </c>
       <c r="AE237" s="2" t="inlineStr"/>
+      <c r="AF237" s="2" t="inlineStr"/>
     </row>
     <row r="238" ht="60" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -24673,6 +25819,7 @@
         </is>
       </c>
       <c r="AE238" s="2" t="inlineStr"/>
+      <c r="AF238" s="2" t="inlineStr"/>
     </row>
     <row r="239" ht="60" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
@@ -24768,6 +25915,7 @@
         </is>
       </c>
       <c r="AE239" s="2" t="inlineStr"/>
+      <c r="AF239" s="2" t="inlineStr"/>
     </row>
     <row r="240" ht="60" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
@@ -24863,6 +26011,7 @@
         </is>
       </c>
       <c r="AE240" s="2" t="inlineStr"/>
+      <c r="AF240" s="2" t="inlineStr"/>
     </row>
     <row r="241" ht="60" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
@@ -24958,6 +26107,7 @@
         </is>
       </c>
       <c r="AE241" s="2" t="inlineStr"/>
+      <c r="AF241" s="2" t="inlineStr"/>
     </row>
     <row r="242" ht="60" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
@@ -25053,6 +26203,7 @@
         </is>
       </c>
       <c r="AE242" s="2" t="inlineStr"/>
+      <c r="AF242" s="2" t="inlineStr"/>
     </row>
     <row r="243" ht="60" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
@@ -25148,6 +26299,7 @@
         </is>
       </c>
       <c r="AE243" s="2" t="inlineStr"/>
+      <c r="AF243" s="2" t="inlineStr"/>
     </row>
     <row r="244" ht="60" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
@@ -25251,6 +26403,7 @@
         </is>
       </c>
       <c r="AE244" s="2" t="inlineStr"/>
+      <c r="AF244" s="2" t="inlineStr"/>
     </row>
     <row r="245" ht="60" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
@@ -25346,6 +26499,7 @@
         </is>
       </c>
       <c r="AE245" s="2" t="inlineStr"/>
+      <c r="AF245" s="2" t="inlineStr"/>
     </row>
     <row r="246" ht="60" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
@@ -25441,6 +26595,7 @@
         </is>
       </c>
       <c r="AE246" s="2" t="inlineStr"/>
+      <c r="AF246" s="2" t="inlineStr"/>
     </row>
     <row r="247" ht="60" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
@@ -25536,6 +26691,7 @@
         </is>
       </c>
       <c r="AE247" s="2" t="inlineStr"/>
+      <c r="AF247" s="2" t="inlineStr"/>
     </row>
     <row r="248" ht="60" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
@@ -25631,6 +26787,7 @@
         </is>
       </c>
       <c r="AE248" s="2" t="inlineStr"/>
+      <c r="AF248" s="2" t="inlineStr"/>
     </row>
     <row r="249" ht="60" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
@@ -25726,6 +26883,7 @@
         </is>
       </c>
       <c r="AE249" s="2" t="inlineStr"/>
+      <c r="AF249" s="2" t="inlineStr"/>
     </row>
     <row r="250" ht="60" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
@@ -25821,6 +26979,7 @@
         </is>
       </c>
       <c r="AE250" s="2" t="inlineStr"/>
+      <c r="AF250" s="2" t="inlineStr"/>
     </row>
     <row r="251" ht="60" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
@@ -25924,6 +27083,7 @@
         </is>
       </c>
       <c r="AE251" s="2" t="inlineStr"/>
+      <c r="AF251" s="2" t="inlineStr"/>
     </row>
     <row r="252" ht="60" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -26019,6 +27179,7 @@
         </is>
       </c>
       <c r="AE252" s="2" t="inlineStr"/>
+      <c r="AF252" s="2" t="inlineStr"/>
     </row>
     <row r="253" ht="60" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
@@ -26122,6 +27283,7 @@
         </is>
       </c>
       <c r="AE253" s="2" t="inlineStr"/>
+      <c r="AF253" s="2" t="inlineStr"/>
     </row>
     <row r="254" ht="60" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
@@ -26221,6 +27383,7 @@
         </is>
       </c>
       <c r="AE254" s="2" t="inlineStr"/>
+      <c r="AF254" s="2" t="inlineStr"/>
     </row>
     <row r="255" ht="60" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
@@ -26316,6 +27479,7 @@
         </is>
       </c>
       <c r="AE255" s="2" t="inlineStr"/>
+      <c r="AF255" s="2" t="inlineStr"/>
     </row>
     <row r="256" ht="60" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
@@ -26419,6 +27583,7 @@
         </is>
       </c>
       <c r="AE256" s="2" t="inlineStr"/>
+      <c r="AF256" s="2" t="inlineStr"/>
     </row>
     <row r="257" ht="60" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
@@ -26514,6 +27679,7 @@
         </is>
       </c>
       <c r="AE257" s="2" t="inlineStr"/>
+      <c r="AF257" s="2" t="inlineStr"/>
     </row>
     <row r="258" ht="60" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
@@ -26609,6 +27775,7 @@
         </is>
       </c>
       <c r="AE258" s="2" t="inlineStr"/>
+      <c r="AF258" s="2" t="inlineStr"/>
     </row>
     <row r="259" ht="60" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
@@ -26712,6 +27879,7 @@
         </is>
       </c>
       <c r="AE259" s="2" t="inlineStr"/>
+      <c r="AF259" s="2" t="inlineStr"/>
     </row>
     <row r="260" ht="60" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
@@ -26803,6 +27971,7 @@
         </is>
       </c>
       <c r="AE260" s="2" t="inlineStr"/>
+      <c r="AF260" s="2" t="inlineStr"/>
     </row>
     <row r="261" ht="60" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
@@ -26898,6 +28067,7 @@
         </is>
       </c>
       <c r="AE261" s="2" t="inlineStr"/>
+      <c r="AF261" s="2" t="inlineStr"/>
     </row>
     <row r="262" ht="60" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
@@ -26993,6 +28163,7 @@
         </is>
       </c>
       <c r="AE262" s="2" t="inlineStr"/>
+      <c r="AF262" s="2" t="inlineStr"/>
     </row>
     <row r="263" ht="60" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
@@ -27096,6 +28267,7 @@
         </is>
       </c>
       <c r="AE263" s="2" t="inlineStr"/>
+      <c r="AF263" s="2" t="inlineStr"/>
     </row>
     <row r="264" ht="60" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
@@ -27191,6 +28363,7 @@
         </is>
       </c>
       <c r="AE264" s="2" t="inlineStr"/>
+      <c r="AF264" s="2" t="inlineStr"/>
     </row>
     <row r="265" ht="60" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
@@ -27286,6 +28459,7 @@
         </is>
       </c>
       <c r="AE265" s="2" t="inlineStr"/>
+      <c r="AF265" s="2" t="inlineStr"/>
     </row>
     <row r="266" ht="60" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -27381,6 +28555,7 @@
         </is>
       </c>
       <c r="AE266" s="2" t="inlineStr"/>
+      <c r="AF266" s="2" t="inlineStr"/>
     </row>
     <row r="267" ht="60" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
@@ -27476,6 +28651,7 @@
         </is>
       </c>
       <c r="AE267" s="2" t="inlineStr"/>
+      <c r="AF267" s="2" t="inlineStr"/>
     </row>
     <row r="268" ht="60" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
@@ -27571,6 +28747,7 @@
         </is>
       </c>
       <c r="AE268" s="2" t="inlineStr"/>
+      <c r="AF268" s="2" t="inlineStr"/>
     </row>
     <row r="269" ht="60" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
@@ -27666,6 +28843,7 @@
         </is>
       </c>
       <c r="AE269" s="2" t="inlineStr"/>
+      <c r="AF269" s="2" t="inlineStr"/>
     </row>
     <row r="270" ht="60" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
@@ -27761,6 +28939,7 @@
         </is>
       </c>
       <c r="AE270" s="2" t="inlineStr"/>
+      <c r="AF270" s="2" t="inlineStr"/>
     </row>
     <row r="271" ht="60" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
@@ -27856,6 +29035,7 @@
         </is>
       </c>
       <c r="AE271" s="2" t="inlineStr"/>
+      <c r="AF271" s="2" t="inlineStr"/>
     </row>
     <row r="272" ht="60" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
@@ -27951,6 +29131,7 @@
         </is>
       </c>
       <c r="AE272" s="2" t="inlineStr"/>
+      <c r="AF272" s="2" t="inlineStr"/>
     </row>
     <row r="273" ht="60" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
@@ -28046,6 +29227,7 @@
         </is>
       </c>
       <c r="AE273" s="2" t="inlineStr"/>
+      <c r="AF273" s="2" t="inlineStr"/>
     </row>
     <row r="274" ht="60" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -28141,6 +29323,7 @@
         </is>
       </c>
       <c r="AE274" s="2" t="inlineStr"/>
+      <c r="AF274" s="2" t="inlineStr"/>
     </row>
     <row r="275" ht="60" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
@@ -28236,6 +29419,7 @@
         </is>
       </c>
       <c r="AE275" s="2" t="inlineStr"/>
+      <c r="AF275" s="2" t="inlineStr"/>
     </row>
     <row r="276" ht="60" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -28331,6 +29515,7 @@
         </is>
       </c>
       <c r="AE276" s="2" t="inlineStr"/>
+      <c r="AF276" s="2" t="inlineStr"/>
     </row>
     <row r="277" ht="60" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
@@ -28434,6 +29619,7 @@
         </is>
       </c>
       <c r="AE277" s="2" t="inlineStr"/>
+      <c r="AF277" s="2" t="inlineStr"/>
     </row>
     <row r="278" ht="60" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
@@ -28537,6 +29723,7 @@
         </is>
       </c>
       <c r="AE278" s="2" t="inlineStr"/>
+      <c r="AF278" s="2" t="inlineStr"/>
     </row>
     <row r="279" ht="60" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
@@ -28632,6 +29819,7 @@
         </is>
       </c>
       <c r="AE279" s="2" t="inlineStr"/>
+      <c r="AF279" s="2" t="inlineStr"/>
     </row>
     <row r="280" ht="60" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -28727,6 +29915,7 @@
         </is>
       </c>
       <c r="AE280" s="2" t="inlineStr"/>
+      <c r="AF280" s="2" t="inlineStr"/>
     </row>
     <row r="281" ht="60" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -28822,6 +30011,7 @@
         </is>
       </c>
       <c r="AE281" s="2" t="inlineStr"/>
+      <c r="AF281" s="2" t="inlineStr"/>
     </row>
     <row r="282" ht="60" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -28917,6 +30107,7 @@
         </is>
       </c>
       <c r="AE282" s="2" t="inlineStr"/>
+      <c r="AF282" s="2" t="inlineStr"/>
     </row>
     <row r="283" ht="60" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
@@ -29012,6 +30203,7 @@
         </is>
       </c>
       <c r="AE283" s="2" t="inlineStr"/>
+      <c r="AF283" s="2" t="inlineStr"/>
     </row>
     <row r="284" ht="60" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -29107,6 +30299,7 @@
         </is>
       </c>
       <c r="AE284" s="2" t="inlineStr"/>
+      <c r="AF284" s="2" t="inlineStr"/>
     </row>
     <row r="285" ht="60" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
@@ -29202,6 +30395,7 @@
         </is>
       </c>
       <c r="AE285" s="2" t="inlineStr"/>
+      <c r="AF285" s="2" t="inlineStr"/>
     </row>
     <row r="286" ht="60" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
@@ -29297,6 +30491,7 @@
         </is>
       </c>
       <c r="AE286" s="2" t="inlineStr"/>
+      <c r="AF286" s="2" t="inlineStr"/>
     </row>
     <row r="287" ht="60" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
@@ -29392,6 +30587,7 @@
         </is>
       </c>
       <c r="AE287" s="2" t="inlineStr"/>
+      <c r="AF287" s="2" t="inlineStr"/>
     </row>
     <row r="288" ht="60" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
@@ -29487,6 +30683,7 @@
         </is>
       </c>
       <c r="AE288" s="2" t="inlineStr"/>
+      <c r="AF288" s="2" t="inlineStr"/>
     </row>
     <row r="289" ht="60" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
@@ -29582,6 +30779,7 @@
         </is>
       </c>
       <c r="AE289" s="2" t="inlineStr"/>
+      <c r="AF289" s="2" t="inlineStr"/>
     </row>
     <row r="290" ht="60" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
@@ -29677,6 +30875,7 @@
         </is>
       </c>
       <c r="AE290" s="2" t="inlineStr"/>
+      <c r="AF290" s="2" t="inlineStr"/>
     </row>
     <row r="291" ht="60" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
@@ -29768,6 +30967,7 @@
         </is>
       </c>
       <c r="AE291" s="2" t="inlineStr"/>
+      <c r="AF291" s="2" t="inlineStr"/>
     </row>
     <row r="292" ht="60" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
@@ -29863,6 +31063,7 @@
         </is>
       </c>
       <c r="AE292" s="2" t="inlineStr"/>
+      <c r="AF292" s="2" t="inlineStr"/>
     </row>
     <row r="293" ht="60" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
@@ -29958,6 +31159,7 @@
         </is>
       </c>
       <c r="AE293" s="2" t="inlineStr"/>
+      <c r="AF293" s="2" t="inlineStr"/>
     </row>
     <row r="294" ht="60" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
@@ -30053,6 +31255,7 @@
         </is>
       </c>
       <c r="AE294" s="2" t="inlineStr"/>
+      <c r="AF294" s="2" t="inlineStr"/>
     </row>
     <row r="295" ht="60" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
@@ -30148,6 +31351,7 @@
         </is>
       </c>
       <c r="AE295" s="2" t="inlineStr"/>
+      <c r="AF295" s="2" t="inlineStr"/>
     </row>
     <row r="296" ht="60" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
@@ -30243,6 +31447,7 @@
         </is>
       </c>
       <c r="AE296" s="2" t="inlineStr"/>
+      <c r="AF296" s="2" t="inlineStr"/>
     </row>
     <row r="297" ht="60" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
@@ -30338,6 +31543,7 @@
         </is>
       </c>
       <c r="AE297" s="2" t="inlineStr"/>
+      <c r="AF297" s="2" t="inlineStr"/>
     </row>
     <row r="298" ht="60" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
@@ -30433,6 +31639,7 @@
         </is>
       </c>
       <c r="AE298" s="2" t="inlineStr"/>
+      <c r="AF298" s="2" t="inlineStr"/>
     </row>
     <row r="299" ht="60" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
@@ -30528,6 +31735,7 @@
         </is>
       </c>
       <c r="AE299" s="2" t="inlineStr"/>
+      <c r="AF299" s="2" t="inlineStr"/>
     </row>
     <row r="300" ht="60" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
@@ -30623,6 +31831,7 @@
         </is>
       </c>
       <c r="AE300" s="2" t="inlineStr"/>
+      <c r="AF300" s="2" t="inlineStr"/>
     </row>
     <row r="301" ht="60" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
@@ -30718,6 +31927,7 @@
         </is>
       </c>
       <c r="AE301" s="2" t="inlineStr"/>
+      <c r="AF301" s="2" t="inlineStr"/>
     </row>
     <row r="302" ht="60" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
@@ -30813,6 +32023,7 @@
         </is>
       </c>
       <c r="AE302" s="2" t="inlineStr"/>
+      <c r="AF302" s="2" t="inlineStr"/>
     </row>
     <row r="303" ht="60" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
@@ -30908,6 +32119,7 @@
         </is>
       </c>
       <c r="AE303" s="2" t="inlineStr"/>
+      <c r="AF303" s="2" t="inlineStr"/>
     </row>
     <row r="304" ht="60" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
@@ -31003,6 +32215,7 @@
         </is>
       </c>
       <c r="AE304" s="2" t="inlineStr"/>
+      <c r="AF304" s="2" t="inlineStr"/>
     </row>
     <row r="305" ht="60" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
@@ -31106,6 +32319,7 @@
         </is>
       </c>
       <c r="AE305" s="2" t="inlineStr"/>
+      <c r="AF305" s="2" t="inlineStr"/>
     </row>
     <row r="306" ht="60" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
@@ -31201,6 +32415,7 @@
         </is>
       </c>
       <c r="AE306" s="2" t="inlineStr"/>
+      <c r="AF306" s="2" t="inlineStr"/>
     </row>
     <row r="307" ht="60" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
@@ -31296,6 +32511,7 @@
         </is>
       </c>
       <c r="AE307" s="2" t="inlineStr"/>
+      <c r="AF307" s="2" t="inlineStr"/>
     </row>
     <row r="308" ht="60" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
@@ -31391,6 +32607,7 @@
         </is>
       </c>
       <c r="AE308" s="2" t="inlineStr"/>
+      <c r="AF308" s="2" t="inlineStr"/>
     </row>
     <row r="309" ht="60" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
@@ -31486,6 +32703,7 @@
         </is>
       </c>
       <c r="AE309" s="2" t="inlineStr"/>
+      <c r="AF309" s="2" t="inlineStr"/>
     </row>
     <row r="310" ht="60" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
@@ -31581,6 +32799,7 @@
         </is>
       </c>
       <c r="AE310" s="2" t="inlineStr"/>
+      <c r="AF310" s="2" t="inlineStr"/>
     </row>
     <row r="311" ht="60" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
@@ -31676,6 +32895,7 @@
         </is>
       </c>
       <c r="AE311" s="2" t="inlineStr"/>
+      <c r="AF311" s="2" t="inlineStr"/>
     </row>
     <row r="312" ht="60" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
@@ -31771,6 +32991,7 @@
         </is>
       </c>
       <c r="AE312" s="2" t="inlineStr"/>
+      <c r="AF312" s="2" t="inlineStr"/>
     </row>
     <row r="313" ht="60" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
@@ -31866,6 +33087,7 @@
         </is>
       </c>
       <c r="AE313" s="2" t="inlineStr"/>
+      <c r="AF313" s="2" t="inlineStr"/>
     </row>
     <row r="314" ht="60" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
@@ -31961,6 +33183,7 @@
         </is>
       </c>
       <c r="AE314" s="2" t="inlineStr"/>
+      <c r="AF314" s="2" t="inlineStr"/>
     </row>
     <row r="315" ht="60" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
@@ -32056,6 +33279,7 @@
         </is>
       </c>
       <c r="AE315" s="2" t="inlineStr"/>
+      <c r="AF315" s="2" t="inlineStr"/>
     </row>
     <row r="316" ht="60" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
@@ -32151,6 +33375,7 @@
         </is>
       </c>
       <c r="AE316" s="2" t="inlineStr"/>
+      <c r="AF316" s="2" t="inlineStr"/>
     </row>
     <row r="317" ht="60" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
@@ -32254,6 +33479,7 @@
         </is>
       </c>
       <c r="AE317" s="2" t="inlineStr"/>
+      <c r="AF317" s="2" t="inlineStr"/>
     </row>
     <row r="318" ht="60" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
@@ -32349,6 +33575,7 @@
         </is>
       </c>
       <c r="AE318" s="2" t="inlineStr"/>
+      <c r="AF318" s="2" t="inlineStr"/>
     </row>
     <row r="319" ht="60" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
@@ -32444,6 +33671,7 @@
         </is>
       </c>
       <c r="AE319" s="2" t="inlineStr"/>
+      <c r="AF319" s="2" t="inlineStr"/>
     </row>
     <row r="320" ht="60" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
@@ -32539,6 +33767,7 @@
         </is>
       </c>
       <c r="AE320" s="2" t="inlineStr"/>
+      <c r="AF320" s="2" t="inlineStr"/>
     </row>
     <row r="321" ht="60" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
@@ -32634,6 +33863,7 @@
         </is>
       </c>
       <c r="AE321" s="2" t="inlineStr"/>
+      <c r="AF321" s="2" t="inlineStr"/>
     </row>
     <row r="322" ht="60" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
@@ -32729,6 +33959,7 @@
         </is>
       </c>
       <c r="AE322" s="2" t="inlineStr"/>
+      <c r="AF322" s="2" t="inlineStr"/>
     </row>
     <row r="323" ht="60" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
@@ -32824,6 +34055,7 @@
         </is>
       </c>
       <c r="AE323" s="2" t="inlineStr"/>
+      <c r="AF323" s="2" t="inlineStr"/>
     </row>
     <row r="324" ht="60" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
@@ -32919,6 +34151,7 @@
         </is>
       </c>
       <c r="AE324" s="2" t="inlineStr"/>
+      <c r="AF324" s="2" t="inlineStr"/>
     </row>
     <row r="325" ht="60" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
@@ -33014,6 +34247,7 @@
         </is>
       </c>
       <c r="AE325" s="2" t="inlineStr"/>
+      <c r="AF325" s="2" t="inlineStr"/>
     </row>
     <row r="326" ht="60" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
@@ -33109,6 +34343,7 @@
         </is>
       </c>
       <c r="AE326" s="2" t="inlineStr"/>
+      <c r="AF326" s="2" t="inlineStr"/>
     </row>
     <row r="327" ht="60" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
@@ -33204,6 +34439,7 @@
         </is>
       </c>
       <c r="AE327" s="2" t="inlineStr"/>
+      <c r="AF327" s="2" t="inlineStr"/>
     </row>
     <row r="328" ht="60" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
@@ -33299,6 +34535,7 @@
         </is>
       </c>
       <c r="AE328" s="2" t="inlineStr"/>
+      <c r="AF328" s="2" t="inlineStr"/>
     </row>
     <row r="329" ht="60" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
@@ -33402,6 +34639,7 @@
         </is>
       </c>
       <c r="AE329" s="2" t="inlineStr"/>
+      <c r="AF329" s="2" t="inlineStr"/>
     </row>
     <row r="330" ht="60" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
@@ -33497,6 +34735,7 @@
         </is>
       </c>
       <c r="AE330" s="2" t="inlineStr"/>
+      <c r="AF330" s="2" t="inlineStr"/>
     </row>
     <row r="331" ht="60" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
@@ -33588,6 +34827,7 @@
         </is>
       </c>
       <c r="AE331" s="2" t="inlineStr"/>
+      <c r="AF331" s="2" t="inlineStr"/>
     </row>
     <row r="332" ht="60" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
@@ -33683,6 +34923,7 @@
         </is>
       </c>
       <c r="AE332" s="2" t="inlineStr"/>
+      <c r="AF332" s="2" t="inlineStr"/>
     </row>
     <row r="333" ht="60" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
@@ -33778,6 +35019,7 @@
         </is>
       </c>
       <c r="AE333" s="2" t="inlineStr"/>
+      <c r="AF333" s="2" t="inlineStr"/>
     </row>
     <row r="334" ht="60" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
@@ -33873,6 +35115,7 @@
         </is>
       </c>
       <c r="AE334" s="2" t="inlineStr"/>
+      <c r="AF334" s="2" t="inlineStr"/>
     </row>
     <row r="335" ht="60" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
@@ -33968,6 +35211,7 @@
         </is>
       </c>
       <c r="AE335" s="2" t="inlineStr"/>
+      <c r="AF335" s="2" t="inlineStr"/>
     </row>
     <row r="336" ht="60" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
@@ -34063,6 +35307,7 @@
         </is>
       </c>
       <c r="AE336" s="2" t="inlineStr"/>
+      <c r="AF336" s="2" t="inlineStr"/>
     </row>
     <row r="337" ht="60" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
@@ -34158,6 +35403,7 @@
         </is>
       </c>
       <c r="AE337" s="2" t="inlineStr"/>
+      <c r="AF337" s="2" t="inlineStr"/>
     </row>
     <row r="338" ht="60" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
@@ -34253,6 +35499,7 @@
         </is>
       </c>
       <c r="AE338" s="2" t="inlineStr"/>
+      <c r="AF338" s="2" t="inlineStr"/>
     </row>
     <row r="339" ht="60" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
@@ -34348,6 +35595,7 @@
         </is>
       </c>
       <c r="AE339" s="2" t="inlineStr"/>
+      <c r="AF339" s="2" t="inlineStr"/>
     </row>
     <row r="340" ht="60" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
@@ -34443,6 +35691,7 @@
         </is>
       </c>
       <c r="AE340" s="2" t="inlineStr"/>
+      <c r="AF340" s="2" t="inlineStr"/>
     </row>
     <row r="341" ht="60" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
@@ -34538,6 +35787,7 @@
         </is>
       </c>
       <c r="AE341" s="2" t="inlineStr"/>
+      <c r="AF341" s="2" t="inlineStr"/>
     </row>
     <row r="342" ht="60" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
@@ -34633,6 +35883,7 @@
         </is>
       </c>
       <c r="AE342" s="2" t="inlineStr"/>
+      <c r="AF342" s="2" t="inlineStr"/>
     </row>
     <row r="343" ht="60" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
@@ -34728,6 +35979,7 @@
         </is>
       </c>
       <c r="AE343" s="2" t="inlineStr"/>
+      <c r="AF343" s="2" t="inlineStr"/>
     </row>
     <row r="344" ht="60" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
@@ -34823,6 +36075,7 @@
         </is>
       </c>
       <c r="AE344" s="2" t="inlineStr"/>
+      <c r="AF344" s="2" t="inlineStr"/>
     </row>
     <row r="345" ht="60" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
@@ -34918,6 +36171,7 @@
         </is>
       </c>
       <c r="AE345" s="2" t="inlineStr"/>
+      <c r="AF345" s="2" t="inlineStr"/>
     </row>
     <row r="346" ht="60" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
@@ -35013,6 +36267,7 @@
         </is>
       </c>
       <c r="AE346" s="2" t="inlineStr"/>
+      <c r="AF346" s="2" t="inlineStr"/>
     </row>
     <row r="347" ht="60" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
@@ -35108,6 +36363,7 @@
         </is>
       </c>
       <c r="AE347" s="2" t="inlineStr"/>
+      <c r="AF347" s="2" t="inlineStr"/>
     </row>
     <row r="348" ht="60" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
@@ -35203,6 +36459,7 @@
         </is>
       </c>
       <c r="AE348" s="2" t="inlineStr"/>
+      <c r="AF348" s="2" t="inlineStr"/>
     </row>
     <row r="349" ht="60" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
@@ -35306,6 +36563,7 @@
         </is>
       </c>
       <c r="AE349" s="2" t="inlineStr"/>
+      <c r="AF349" s="2" t="inlineStr"/>
     </row>
     <row r="350" ht="60" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
@@ -35401,6 +36659,7 @@
         </is>
       </c>
       <c r="AE350" s="2" t="inlineStr"/>
+      <c r="AF350" s="2" t="inlineStr"/>
     </row>
     <row r="351" ht="60" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
@@ -35496,6 +36755,7 @@
         </is>
       </c>
       <c r="AE351" s="2" t="inlineStr"/>
+      <c r="AF351" s="2" t="inlineStr"/>
     </row>
     <row r="352" ht="60" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
@@ -35591,6 +36851,7 @@
         </is>
       </c>
       <c r="AE352" s="2" t="inlineStr"/>
+      <c r="AF352" s="2" t="inlineStr"/>
     </row>
     <row r="353" ht="60" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
@@ -35686,6 +36947,7 @@
         </is>
       </c>
       <c r="AE353" s="2" t="inlineStr"/>
+      <c r="AF353" s="2" t="inlineStr"/>
     </row>
     <row r="354" ht="60" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
@@ -35781,6 +37043,7 @@
         </is>
       </c>
       <c r="AE354" s="2" t="inlineStr"/>
+      <c r="AF354" s="2" t="inlineStr"/>
     </row>
     <row r="355" ht="60" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
@@ -35876,6 +37139,7 @@
         </is>
       </c>
       <c r="AE355" s="2" t="inlineStr"/>
+      <c r="AF355" s="2" t="inlineStr"/>
     </row>
     <row r="356" ht="60" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
@@ -35971,6 +37235,7 @@
         </is>
       </c>
       <c r="AE356" s="2" t="inlineStr"/>
+      <c r="AF356" s="2" t="inlineStr"/>
     </row>
     <row r="357" ht="60" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
@@ -36066,6 +37331,7 @@
         </is>
       </c>
       <c r="AE357" s="2" t="inlineStr"/>
+      <c r="AF357" s="2" t="inlineStr"/>
     </row>
     <row r="358" ht="60" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
@@ -36161,6 +37427,7 @@
         </is>
       </c>
       <c r="AE358" s="2" t="inlineStr"/>
+      <c r="AF358" s="2" t="inlineStr"/>
     </row>
     <row r="359" ht="60" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
@@ -36256,6 +37523,7 @@
         </is>
       </c>
       <c r="AE359" s="2" t="inlineStr"/>
+      <c r="AF359" s="2" t="inlineStr"/>
     </row>
     <row r="360" ht="60" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
@@ -36351,6 +37619,7 @@
         </is>
       </c>
       <c r="AE360" s="2" t="inlineStr"/>
+      <c r="AF360" s="2" t="inlineStr"/>
     </row>
     <row r="361" ht="60" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
@@ -36446,6 +37715,7 @@
         </is>
       </c>
       <c r="AE361" s="2" t="inlineStr"/>
+      <c r="AF361" s="2" t="inlineStr"/>
     </row>
     <row r="362" ht="60" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
@@ -36541,6 +37811,7 @@
         </is>
       </c>
       <c r="AE362" s="2" t="inlineStr"/>
+      <c r="AF362" s="2" t="inlineStr"/>
     </row>
     <row r="363" ht="60" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
@@ -36636,6 +37907,7 @@
         </is>
       </c>
       <c r="AE363" s="2" t="inlineStr"/>
+      <c r="AF363" s="2" t="inlineStr"/>
     </row>
     <row r="364" ht="60" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
@@ -36731,6 +38003,7 @@
         </is>
       </c>
       <c r="AE364" s="2" t="inlineStr"/>
+      <c r="AF364" s="2" t="inlineStr"/>
     </row>
     <row r="365" ht="60" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
@@ -36826,6 +38099,7 @@
         </is>
       </c>
       <c r="AE365" s="2" t="inlineStr"/>
+      <c r="AF365" s="2" t="inlineStr"/>
     </row>
     <row r="366" ht="60" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
@@ -36921,6 +38195,7 @@
         </is>
       </c>
       <c r="AE366" s="2" t="inlineStr"/>
+      <c r="AF366" s="2" t="inlineStr"/>
     </row>
     <row r="367" ht="60" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
@@ -37016,6 +38291,7 @@
         </is>
       </c>
       <c r="AE367" s="2" t="inlineStr"/>
+      <c r="AF367" s="2" t="inlineStr"/>
     </row>
     <row r="368" ht="60" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
@@ -37111,6 +38387,7 @@
         </is>
       </c>
       <c r="AE368" s="2" t="inlineStr"/>
+      <c r="AF368" s="2" t="inlineStr"/>
     </row>
     <row r="369" ht="60" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
@@ -37206,6 +38483,7 @@
         </is>
       </c>
       <c r="AE369" s="2" t="inlineStr"/>
+      <c r="AF369" s="2" t="inlineStr"/>
     </row>
     <row r="370" ht="60" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
@@ -37301,6 +38579,7 @@
         </is>
       </c>
       <c r="AE370" s="2" t="inlineStr"/>
+      <c r="AF370" s="2" t="inlineStr"/>
     </row>
     <row r="371" ht="60" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
@@ -37396,6 +38675,7 @@
         </is>
       </c>
       <c r="AE371" s="2" t="inlineStr"/>
+      <c r="AF371" s="2" t="inlineStr"/>
     </row>
     <row r="372" ht="60" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
@@ -37491,6 +38771,7 @@
         </is>
       </c>
       <c r="AE372" s="2" t="inlineStr"/>
+      <c r="AF372" s="2" t="inlineStr"/>
     </row>
     <row r="373" ht="60" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
@@ -37586,6 +38867,7 @@
         </is>
       </c>
       <c r="AE373" s="2" t="inlineStr"/>
+      <c r="AF373" s="2" t="inlineStr"/>
     </row>
     <row r="374" ht="60" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
@@ -37681,6 +38963,7 @@
         </is>
       </c>
       <c r="AE374" s="2" t="inlineStr"/>
+      <c r="AF374" s="2" t="inlineStr"/>
     </row>
     <row r="375" ht="60" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
@@ -37776,6 +39059,7 @@
         </is>
       </c>
       <c r="AE375" s="2" t="inlineStr"/>
+      <c r="AF375" s="2" t="inlineStr"/>
     </row>
     <row r="376" ht="60" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
@@ -37871,6 +39155,7 @@
         </is>
       </c>
       <c r="AE376" s="2" t="inlineStr"/>
+      <c r="AF376" s="2" t="inlineStr"/>
     </row>
     <row r="377" ht="60" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
@@ -37974,6 +39259,7 @@
         </is>
       </c>
       <c r="AE377" s="2" t="inlineStr"/>
+      <c r="AF377" s="2" t="inlineStr"/>
     </row>
     <row r="378" ht="60" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
@@ -38077,6 +39363,7 @@
         </is>
       </c>
       <c r="AE378" s="2" t="inlineStr"/>
+      <c r="AF378" s="2" t="inlineStr"/>
     </row>
     <row r="379" ht="60" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
@@ -38176,6 +39463,7 @@
         </is>
       </c>
       <c r="AE379" s="2" t="inlineStr"/>
+      <c r="AF379" s="2" t="inlineStr"/>
     </row>
     <row r="380" ht="60" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
@@ -38271,6 +39559,7 @@
         </is>
       </c>
       <c r="AE380" s="2" t="inlineStr"/>
+      <c r="AF380" s="2" t="inlineStr"/>
     </row>
     <row r="381" ht="60" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
@@ -38366,6 +39655,7 @@
         </is>
       </c>
       <c r="AE381" s="2" t="inlineStr"/>
+      <c r="AF381" s="2" t="inlineStr"/>
     </row>
     <row r="382" ht="60" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
@@ -38469,6 +39759,7 @@
         </is>
       </c>
       <c r="AE382" s="2" t="inlineStr"/>
+      <c r="AF382" s="2" t="inlineStr"/>
     </row>
     <row r="383" ht="60" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
@@ -38564,6 +39855,7 @@
         </is>
       </c>
       <c r="AE383" s="2" t="inlineStr"/>
+      <c r="AF383" s="2" t="inlineStr"/>
     </row>
     <row r="384" ht="60" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
@@ -38659,6 +39951,7 @@
         </is>
       </c>
       <c r="AE384" s="2" t="inlineStr"/>
+      <c r="AF384" s="2" t="inlineStr"/>
     </row>
     <row r="385" ht="60" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
@@ -38754,6 +40047,7 @@
         </is>
       </c>
       <c r="AE385" s="2" t="inlineStr"/>
+      <c r="AF385" s="2" t="inlineStr"/>
     </row>
     <row r="386" ht="60" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
@@ -38849,6 +40143,7 @@
         </is>
       </c>
       <c r="AE386" s="2" t="inlineStr"/>
+      <c r="AF386" s="2" t="inlineStr"/>
     </row>
     <row r="387" ht="60" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
@@ -38944,6 +40239,7 @@
         </is>
       </c>
       <c r="AE387" s="2" t="inlineStr"/>
+      <c r="AF387" s="2" t="inlineStr"/>
     </row>
     <row r="388" ht="60" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
@@ -39039,6 +40335,7 @@
         </is>
       </c>
       <c r="AE388" s="2" t="inlineStr"/>
+      <c r="AF388" s="2" t="inlineStr"/>
     </row>
     <row r="389" ht="60" customHeight="1">
       <c r="A389" s="2" t="inlineStr">
@@ -39134,6 +40431,7 @@
         </is>
       </c>
       <c r="AE389" s="2" t="inlineStr"/>
+      <c r="AF389" s="2" t="inlineStr"/>
     </row>
     <row r="390" ht="60" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
@@ -39229,6 +40527,7 @@
         </is>
       </c>
       <c r="AE390" s="2" t="inlineStr"/>
+      <c r="AF390" s="2" t="inlineStr"/>
     </row>
     <row r="391" ht="60" customHeight="1">
       <c r="A391" s="2" t="inlineStr">
@@ -39324,6 +40623,7 @@
         </is>
       </c>
       <c r="AE391" s="2" t="inlineStr"/>
+      <c r="AF391" s="2" t="inlineStr"/>
     </row>
     <row r="392" ht="60" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
@@ -39419,6 +40719,7 @@
         </is>
       </c>
       <c r="AE392" s="2" t="inlineStr"/>
+      <c r="AF392" s="2" t="inlineStr"/>
     </row>
     <row r="393" ht="60" customHeight="1">
       <c r="A393" s="2" t="inlineStr">
@@ -39514,6 +40815,7 @@
         </is>
       </c>
       <c r="AE393" s="2" t="inlineStr"/>
+      <c r="AF393" s="2" t="inlineStr"/>
     </row>
     <row r="394" ht="60" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
@@ -39609,6 +40911,7 @@
         </is>
       </c>
       <c r="AE394" s="2" t="inlineStr"/>
+      <c r="AF394" s="2" t="inlineStr"/>
     </row>
     <row r="395" ht="60" customHeight="1">
       <c r="A395" s="2" t="inlineStr">
@@ -39704,6 +41007,7 @@
         </is>
       </c>
       <c r="AE395" s="2" t="inlineStr"/>
+      <c r="AF395" s="2" t="inlineStr"/>
     </row>
     <row r="396" ht="60" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
@@ -39799,6 +41103,7 @@
         </is>
       </c>
       <c r="AE396" s="2" t="inlineStr"/>
+      <c r="AF396" s="2" t="inlineStr"/>
     </row>
     <row r="397" ht="60" customHeight="1">
       <c r="A397" s="2" t="inlineStr">
@@ -39894,6 +41199,7 @@
         </is>
       </c>
       <c r="AE397" s="2" t="inlineStr"/>
+      <c r="AF397" s="2" t="inlineStr"/>
     </row>
     <row r="398" ht="60" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
@@ -39977,6 +41283,7 @@
         </is>
       </c>
       <c r="AE398" s="2" t="inlineStr"/>
+      <c r="AF398" s="2" t="inlineStr"/>
     </row>
     <row r="399" ht="60" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
@@ -40060,6 +41367,7 @@
         </is>
       </c>
       <c r="AE399" s="2" t="inlineStr"/>
+      <c r="AF399" s="2" t="inlineStr"/>
     </row>
     <row r="400" ht="60" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
@@ -40163,6 +41471,7 @@
         </is>
       </c>
       <c r="AE400" s="2" t="inlineStr"/>
+      <c r="AF400" s="2" t="inlineStr"/>
     </row>
     <row r="401" ht="60" customHeight="1">
       <c r="A401" s="2" t="inlineStr">
@@ -40258,6 +41567,7 @@
         </is>
       </c>
       <c r="AE401" s="2" t="inlineStr"/>
+      <c r="AF401" s="2" t="inlineStr"/>
     </row>
     <row r="402" ht="60" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
@@ -40345,6 +41655,7 @@
         </is>
       </c>
       <c r="AE402" s="2" t="inlineStr"/>
+      <c r="AF402" s="2" t="inlineStr"/>
     </row>
     <row r="403" ht="60" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
@@ -40448,6 +41759,7 @@
         </is>
       </c>
       <c r="AE403" s="2" t="inlineStr"/>
+      <c r="AF403" s="2" t="inlineStr"/>
     </row>
     <row r="404" ht="60" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
@@ -40531,6 +41843,7 @@
         </is>
       </c>
       <c r="AE404" s="2" t="inlineStr"/>
+      <c r="AF404" s="2" t="inlineStr"/>
     </row>
     <row r="405" ht="60" customHeight="1">
       <c r="A405" s="2" t="inlineStr">
@@ -40626,6 +41939,7 @@
         </is>
       </c>
       <c r="AE405" s="2" t="inlineStr"/>
+      <c r="AF405" s="2" t="inlineStr"/>
     </row>
     <row r="406" ht="60" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
@@ -40729,6 +42043,7 @@
         </is>
       </c>
       <c r="AE406" s="2" t="inlineStr"/>
+      <c r="AF406" s="2" t="inlineStr"/>
     </row>
     <row r="407" ht="60" customHeight="1">
       <c r="A407" s="2" t="inlineStr">
@@ -40832,6 +42147,7 @@
         </is>
       </c>
       <c r="AE407" s="2" t="inlineStr"/>
+      <c r="AF407" s="2" t="inlineStr"/>
     </row>
     <row r="408" ht="60" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
@@ -40927,6 +42243,7 @@
         </is>
       </c>
       <c r="AE408" s="2" t="inlineStr"/>
+      <c r="AF408" s="2" t="inlineStr"/>
     </row>
     <row r="409" ht="60" customHeight="1">
       <c r="A409" s="2" t="inlineStr">
@@ -41010,6 +42327,7 @@
         </is>
       </c>
       <c r="AE409" s="2" t="inlineStr"/>
+      <c r="AF409" s="2" t="inlineStr"/>
     </row>
     <row r="410" ht="60" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
@@ -41105,6 +42423,7 @@
         </is>
       </c>
       <c r="AE410" s="2" t="inlineStr"/>
+      <c r="AF410" s="2" t="inlineStr"/>
     </row>
     <row r="411" ht="60" customHeight="1">
       <c r="A411" s="2" t="inlineStr">
@@ -41188,6 +42507,7 @@
         </is>
       </c>
       <c r="AE411" s="2" t="inlineStr"/>
+      <c r="AF411" s="2" t="inlineStr"/>
     </row>
     <row r="412" ht="60" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
@@ -41283,6 +42603,7 @@
         </is>
       </c>
       <c r="AE412" s="2" t="inlineStr"/>
+      <c r="AF412" s="2" t="inlineStr"/>
     </row>
     <row r="413" ht="60" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
@@ -41378,6 +42699,7 @@
         </is>
       </c>
       <c r="AE413" s="2" t="inlineStr"/>
+      <c r="AF413" s="2" t="inlineStr"/>
     </row>
     <row r="414" ht="60" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
@@ -41461,6 +42783,7 @@
         </is>
       </c>
       <c r="AE414" s="2" t="inlineStr"/>
+      <c r="AF414" s="2" t="inlineStr"/>
     </row>
     <row r="415" ht="60" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
@@ -41560,6 +42883,7 @@
         </is>
       </c>
       <c r="AE415" s="2" t="inlineStr"/>
+      <c r="AF415" s="2" t="inlineStr"/>
     </row>
     <row r="416" ht="60" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
@@ -41655,6 +42979,7 @@
         </is>
       </c>
       <c r="AE416" s="2" t="inlineStr"/>
+      <c r="AF416" s="2" t="inlineStr"/>
     </row>
     <row r="417" ht="60" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
@@ -41750,6 +43075,7 @@
         </is>
       </c>
       <c r="AE417" s="2" t="inlineStr"/>
+      <c r="AF417" s="2" t="inlineStr"/>
     </row>
     <row r="418" ht="60" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
@@ -41853,6 +43179,7 @@
         </is>
       </c>
       <c r="AE418" s="2" t="inlineStr"/>
+      <c r="AF418" s="2" t="inlineStr"/>
     </row>
     <row r="419" ht="60" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
@@ -41948,6 +43275,7 @@
         </is>
       </c>
       <c r="AE419" s="2" t="inlineStr"/>
+      <c r="AF419" s="2" t="inlineStr"/>
     </row>
     <row r="420" ht="60" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
@@ -42051,6 +43379,7 @@
         </is>
       </c>
       <c r="AE420" s="2" t="inlineStr"/>
+      <c r="AF420" s="2" t="inlineStr"/>
     </row>
     <row r="421" ht="60" customHeight="1">
       <c r="A421" s="2" t="inlineStr">
@@ -42138,6 +43467,7 @@
         </is>
       </c>
       <c r="AE421" s="2" t="inlineStr"/>
+      <c r="AF421" s="2" t="inlineStr"/>
     </row>
     <row r="422" ht="60" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
@@ -42225,6 +43555,7 @@
         </is>
       </c>
       <c r="AE422" s="2" t="inlineStr"/>
+      <c r="AF422" s="2" t="inlineStr"/>
     </row>
     <row r="423" ht="60" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
@@ -42312,6 +43643,7 @@
         </is>
       </c>
       <c r="AE423" s="2" t="inlineStr"/>
+      <c r="AF423" s="2" t="inlineStr"/>
     </row>
     <row r="424" ht="60" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
@@ -42403,6 +43735,7 @@
         </is>
       </c>
       <c r="AE424" s="2" t="inlineStr"/>
+      <c r="AF424" s="2" t="inlineStr"/>
     </row>
     <row r="425" ht="60" customHeight="1">
       <c r="A425" s="2" t="inlineStr">
@@ -42494,6 +43827,7 @@
         </is>
       </c>
       <c r="AE425" s="2" t="inlineStr"/>
+      <c r="AF425" s="2" t="inlineStr"/>
     </row>
     <row r="426" ht="60" customHeight="1">
       <c r="A426" s="2" t="inlineStr">
@@ -42589,6 +43923,7 @@
         </is>
       </c>
       <c r="AE426" s="2" t="inlineStr"/>
+      <c r="AF426" s="2" t="inlineStr"/>
     </row>
     <row r="427" ht="60" customHeight="1">
       <c r="A427" s="2" t="inlineStr">
@@ -42676,9 +44011,10 @@
         </is>
       </c>
       <c r="AE427" s="2" t="inlineStr"/>
+      <c r="AF427" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE427"/>
+  <autoFilter ref="A1:AF427"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42689,7 +44025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -42723,6 +44059,7 @@
     <col width="25" customWidth="1" min="29" max="29"/>
     <col width="25" customWidth="1" min="30" max="30"/>
     <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -42881,9 +44218,14 @@
           <t>完成时间UTC</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>待确认项筛查保存时间UTC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE1"/>
+  <autoFilter ref="A1:AF1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43051,7 +44393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -46586,8 +47928,2500 @@
         </is>
       </c>
     </row>
+    <row r="66" ht="90" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>R01917-E01</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>R01917</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>The universal primer for sequencing has been added into the primers used for PCR amplification. The primers and amplification conditions were conducted according to the description of Wan et al.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>通用测序引物加入PCR引物，有扩增子特征；文章没有明确扩增靶区，不能据平台判shotgun。</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01917/fulltext/fulltext__published__e31cfc89134fbe8a.pdf</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>e31cfc89134fbe8a1ec0d5fcb8a7bfabaec9dac86febd83fa661ee9a73b2e335</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial community structure analysis</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>R01917-E02</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>R01917</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>The primers and amplification conditions were conducted according to the description of Wan et al. (2014). A 454 Life Sciences Genome Sequencer FLX Titanium instrument (Roche) was used for sequencing in this study.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>引物与扩增条件转引Wan2014；当前证据保留方法不充分的复核状态。</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01917/fulltext/fulltext__published__e31cfc89134fbe8a.pdf</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>e31cfc89134fbe8a1ec0d5fcb8a7bfabaec9dac86febd83fa661ee9a73b2e335</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial community structure analysis</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>R01917-E03</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>R01917</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>The observed OTUs in reactor A (DO = 0.2–0.3 mg/L) and B samples were 3027 and 2806, respectively. The abundances of different phylum in two reactor’s sludge were shown in Fig.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>结果为群落分类/OTU，但该结果本身不足以独立证明宏基因组或排除所有建库可能。</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01917/fulltext/fulltext__published__e31cfc89134fbe8a.pdf</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>e31cfc89134fbe8a1ec0d5fcb8a7bfabaec9dac86febd83fa661ee9a73b2e335</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>3.2 Microbial community structure</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>R02094-E01</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>R02094</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Fluorescent insitu hybridization was performed as described in Blackall (1999). A general probe for Archaea, ARC915, was used to identify all methanogens (Crocetti, 2006).</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>原文为Fluorescent in-situ hybridization；ARC915探针标记古菌并显微计数，不是测序。</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02094/fulltext/fulltext__published__b306bbf706889c58.pdf</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>b306bbf706889c58e62cc0c5119561f4b8b30305dca51e530eee5e5d61a090db</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Sampling and analyses</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="90" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>R02094-E02</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>R02094</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>10–15 fields of view were counted for each sample. Gas samples were analysed in situ using an infrared gas analyzer (GEM 2000 Plus, Geotech) and in the lab using a Clarus 580 GC (PerkinElmer).</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>显微视野计数为群落检测方法，无DNA/RNA建库。</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02094/fulltext/fulltext__published__b306bbf706889c58.pdf</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>b306bbf706889c58e62cc0c5119561f4b8b30305dca51e530eee5e5d61a090db</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Sampling and analyses</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="90" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>R02115-E01</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>R02115</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Biogas composition was measured by a gas chromatograph (SP 6890, Shandong Lunan Inc., China), equipped with a Porapak Q stainless steel column (180 cm long, 3 mm outer diameter) and a thermal conductivity detector.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>GC测气体，后续SCOD/元素/TS/VS/纤维素测定；完整节无核酸建库。</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02115/fulltext/fulltext__published__e07eece2b7522917.pdf</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>e07eece2b7522917c23b5c14d1a0d1f6dec0430ba43b5690e7a2ffde49d39671</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>R02115-E02</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>R02115</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Cellulose, hemicelluloses and lignin were determined according to the method as Goering and van Soest (1970) described. 3. Results and discussion 3.1.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>测底物纤维组分，不是组学功能分析。</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02115/fulltext/fulltext__published__e07eece2b7522917.pdf</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>e07eece2b7522917c23b5c14d1a0d1f6dec0430ba43b5690e7a2ffde49d39671</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="90" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>R02176-E01</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>R02176</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Besides the 16S target-specific sequence, the primers also contain adaptor sequences allowing uniform amplification of the library with high complexity ready for downstream NGS sequencing on Illumina MiSeq.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>明确16S靶向扩增子加接头，排除宏基因组/宏转录组。</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02176/fulltext/fulltext__published__9b88e4a9a62a14a8.pdf</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>9b88e4a9a62a14a890bfdd4909f394a8a82ce138df57c2b355878cac31323f2a</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Microbial community structure analysis</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="90" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>R02176-E02</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>R02176</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>A panel of proprietary primers was designed to anneal to the relatively conserved regions bordering V3, V4, and V5 hypervariable regions.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>保守区夹V3–V5超变区；不是随机片段shotgun。</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02176/fulltext/fulltext__published__9b88e4a9a62a14a8.pdf</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>9b88e4a9a62a14a890bfdd4909f394a8a82ce138df57c2b355878cac31323f2a</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Microbial community structure analysis</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>R01917-E04</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>R01917</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Figure S4 The abundances of different phylum in two reactor’s sludge.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>题名/作者匹配；补充文件为12幅运行/群落及工程图，未提供靶区或项目号。</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01917/supplementary/supplementary__1cecc1f159878862.doc</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1cecc1f159878862165dd3daed50120cce8d494bc51e2578982bf28c2dde27a9</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>DOC antiword lines 1–66; Figures S1–S12</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="90" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>R02188-E01</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>R02188</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>VFA was measured by a gas chromatograph (Varian 450-GC, USA), equipped with Innowax column (30 m [U+0005] 0.25 mm [U+0005] 0.25 lm) and flame ionization detectors.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>产气和VFA的色谱分析；后续完整方法为物化结构表征，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02188/fulltext/fulltext__published__d71a021f92b210cb.pdf</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>d71a021f92b210cbd2a3d7894b5267e2bfcc894c5827aef0474e58aa0436a38f</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Batch anaerobic digestion tests</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="90" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>R02188-E02</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>R02188</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>SEM pictures were taken of untreated and pretreated corn straw using Hitachi S-4800 scanning microscope at 3 kV. Samples were mounted onto aluminium pin stubs and sputter-coated with a thin layer of gold.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Scanning是电子显微镜成像，不是sequencing。</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02188/fulltext/fulltext__published__d71a021f92b210cb.pdf</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>d71a021f92b210cbd2a3d7894b5267e2bfcc894c5827aef0474e58aa0436a38f</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>2.5.3 Scanning electron microscopy</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="90" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>R02188-E03</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>R02188</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>This supplementary material contains 3 figures</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>三幅图分别为FTIR-ATR、XRD和SEM，无核酸测序或数据编号；题名/作者匹配。</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02188/supplementary/supplementary__341e3f61107726d5.doc</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>341e3f61107726d5b9a34760bdcf985dcde7fa6b5527a89c8abd47f356cc3c98</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>DOC全部文本；补充声明及Fig.S1–S3</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="90" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>R02199-E01</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>R02199</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>PCR amplification was performed using specifically synthesized primers with barcode. Amplicons were purified using an AxyPrepTM DNA Gel Extraction Kit (AXYGEN, USA) and eluted with Tris HCl.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>条形码引物扩增，后文多次明确amplicons纯化/合并。</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02199/fulltext/fulltext__published__4a6994a2d2e1e3aa.pdf</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>4a6994a2d2e1e3aaa0eeeff847c7778c2416d35ba870907a944c8377f3f4cc11</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="90" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>R02199-E02</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>R02199</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Then the amplicon sequencing was performed using an Illumina MiSeq PE250 system by Shanghai Majorbio Bio-pharm Biotechnology (Shanghai, China); (4) results were optimized and Operational Taxonomic Units (OTU) clustering and taxonomy analysis was carried out at a 97% similarity level.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>原文明示amplicon sequencing，非群落shotgun或群落RNA。</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02199/fulltext/fulltext__published__4a6994a2d2e1e3aa.pdf</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>4a6994a2d2e1e3aaa0eeeff847c7778c2416d35ba870907a944c8377f3f4cc11</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="90" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>R02239-E01</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>R02239</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>主要测定指标有COD、BOD5、TOC、SO4²⁻、UV254、VFA等。</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>从方法原页人工校对并将化学下标转为普通文本；均为水质指标，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02239/fulltext/fulltext__version_unverified__0ec9c37ecd0bceff.pdf</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>0ec9c37ecd0bceff7d0e81623b74cd6a4cbb0d700b5918ace3852be314430d7d</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>1.2 测试指标及方法（印刷3739页）</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="90" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>R02239-E02</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>R02239</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>采用超滤法对进、出水相对分子质量分布进行测定。</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>分子质量分布为超滤分析，不是测序分子数据；下一段为48h好氧COD试验。</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02239/fulltext/fulltext__version_unverified__0ec9c37ecd0bceff.pdf</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>0ec9c37ecd0bceff7d0e81623b74cd6a4cbb0d700b5918ace3852be314430d7d</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>1.2 测试指标及方法</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="90" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>R02274-E01</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>R02274</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>All parameters (COD, solids, nitrogen, pH, sulfides, sulfates, dissolved oxygen) were determined according to Standard Methods for Water and Wastewater Examination (2012).</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>原文跨行列氮、pH、硫化物、硫酸盐和DO，按水/废水标准方法；无组学。</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02274/fulltext/fulltext__published__4c7da8384f1f6e3d.pdf</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Materials and methods（续）</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="90" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>R02274-E02</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>R02274</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>The initial inoculum (10 g/L volatile suspended solids, VSS) came from anaerobic digester sewage sludge (La Farfana, Santiago de Chile) and was used to generate an initial COD/VSS = 0.1 in all reactors.</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>描述接种污泥来源和浓度，而非核酸提取或测序文库。</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02274/fulltext/fulltext__published__4c7da8384f1f6e3d.pdf</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Materials and methods</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="90" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>R02319-E01</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>R02319</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>농축슬러지 성상 분석항목으로는 ORP(Oxidation reduction potential), DO(Dissolve oxygen), CODcr (chemical oxygen demand), SCODcr(Soluble chemical oxygen demand), 총 질소(T-N), 암모니아 성 질소(NH3-N), TS(Total solids), VS(Volatile solids)을 대상으로 하였고 모든 실험은 반복실험을 실시하였다.</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>该节列ORP、DO、COD/SCOD、总氮/氨氮、TS/VS；分析对象为污泥理化指标，无DNA/RNA建库。</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02319/fulltext/fulltext__version_unverified__bee09adb76fa2153.pdf</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>bee09adb76fa2153dc6e51c04da98c6fffe6fd38c643452173fd1dc3341370e0</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>2.3 분석항목; Table 2 Methods and instruments</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="90" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>R02319-E02</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>R02319</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>T-N, NH3-N, TS, VS Standard method Table 2. Methods and instruments 조에 투입 후 공기주입 펌프를 이용하여 6개의 시료 에 0.05 volume of air per volume of sludge per minute(vvm)의 공기를 24 hr동안 주입하였다.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>表2对应标准方法，其他行pH/ORP/DO仪及重铬酸盐COD；未测序。</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02319/fulltext/fulltext__version_unverified__bee09adb76fa2153.pdf</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>bee09adb76fa2153dc6e51c04da98c6fffe6fd38c643452173fd1dc3341370e0</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Table 2 Methods and instruments</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="90" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>R02340-E01</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>R02340</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Leachate samples were analyzed periodically for pH, VFA, alkalinity, COD, TOC, BOD5, TKN, N–NH4 +, SO4 2[U+0003] and Cl[U+0003]. The ratio between VFA and alkalinity was calculated to obtain the so called FOS/TAC (Voss et al., 2009).</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>完整分析为渗滤液理化参数。</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02340/fulltext/fulltext__published__97fce73e3525cec6.pdf</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>97fce73e3525cec6028a56e81fac50aa1cbb3e2abe85424d09504309ca947980</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="90" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>R02340-E02</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>R02340</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Respiration Index (RI4 and RI7 mgO2/gTS) was determined by means of Sapromat apparatus (H + P Labortechnik, Germany). A leaching test was carried out according to the standard UNI EN 12457-2 on waste samples (L/S was brought to 10 L/kgTS, mixing for 24 h and filtration at 0.45 lm).</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>RI4/RI7用Sapromat测耗氧，非转录组或DNA测序。</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02340/fulltext/fulltext__published__97fce73e3525cec6.pdf</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>97fce73e3525cec6028a56e81fac50aa1cbb3e2abe85424d09504309ca947980</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="90" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>R02370-E01</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>R02370</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Gram and Neisser staining procedures were applied to determine the abundance and to identify filamentous microorganisms. CST Capillary suction time (CST) is a simple parameter and method used for characterization of sludge dewaterability.</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>丝状微生物用染色/显微镜辨认，不是测序。</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02370/fulltext/fulltext__published__534deaaf21ea8112.pdf</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>534deaaf21ea81128d1d8f274bfdcfeb929363b9d6872939487b6f2945bc6fb6</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Microscopy（续）</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="90" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>R02370-E02</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>R02370</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>The volume of produced methane was monitored and maximum methane production rate calculated according to guidelines proposed by Angelidaki et al., [18].</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>SMA是产甲烷速率测定，非宏转录组表达分析。</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02370/fulltext/fulltext__published__534deaaf21ea8112.pdf</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>534deaaf21ea81128d1d8f274bfdcfeb929363b9d6872939487b6f2945bc6fb6</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Specific Activity of Methanogenic Bacteria</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="90" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>R02386-E01</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>R02386</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>PCR amplification of the variable V3 region of 16S rDNA from the purified genomic DNA. PCR amplification was conducted in an automated thermal cycler using the following protocol, that is; initial denaturation for 4 min at 94 [U+0003]C, 30 cycles of denaturation for 1 min at 94 [U+0003]C, annealing for 30 s at 55 [U+0003]C, extension for 1 min at […]</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>明确16S V3定向扩增。</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02386/fulltext/fulltext__published__1c804bc9cfc3b614.pdf</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1c804bc9cfc3b6148036c433a48c8ef76de04b3c9dd0b176b94621e28c6d1348</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>DNA isolation and PCR-DGGE analysis</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="90" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>R02386-E02</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>R02386</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>were determined by dideoxy chain termination (Genewiz, Suzhou, China) and compared with available sequences in GenBank database using the BLAST program.</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>测序模板为再扩增及克隆的DGGE条带，是16S Sanger而非shotgun。</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02386/fulltext/fulltext__published__1c804bc9cfc3b614.pdf</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1c804bc9cfc3b6148036c433a48c8ef76de04b3c9dd0b176b94621e28c6d1348</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>DNA isolation and PCR-DGGE analysis（续）</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="90" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>R02444-E01</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>R02444</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>sequencing library preparations and Illumina MiSeq sequencing were conducted at GENEWIZ, Inc. (Beijing, China), which was in accordance with the reported methods.19 3.</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>后文明确in accordance with the reported methods.19；需溯源到具体16S方法，不能仅凭MiSeq判定。</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02444/fulltext/fulltext__published__a3cb2ae853beb60c.pdf</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>a3cb2ae853beb60cdd86458109ff70f4de83697200b6f975284de2a205e03bc0</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial Community Structure Analysis</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="90" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>R02444-E02</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>R02444</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>方法引用身份匹配</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>The chemical properties and microbial community characterization of the thermophilic microaerobic pretreatment process. Bioresour.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>完整题名、2015年及198:497–502对应现有R02176；其方法为16S扩增子。</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02444/fulltext/fulltext__published__a3cb2ae853beb60c.pdf</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>a3cb2ae853beb60cdd86458109ff70f4de83697200b6f975284de2a205e03bc0</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Reference 19</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="90" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>R02444-E03</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>R02444</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>已取得被引方法交叉核对</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Besides the 16S target-specific sequence, the primers also contain adaptor sequences allowing uniform amplification of the library with high complexity ready for downstream NGS sequencing on Illumina MiSeq.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>R02444 p2明确沿用参考文献19方法；其p6完整题名/期刊卷页匹配R02176，现有原件方法明确16S引物和扩增子库。这里只作方法溯源，不将引用文章数据当本研究数据。</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02176/fulltext/fulltext__published__9b88e4a9a62a14a8.pdf</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>9b88e4a9a62a14a890bfdd4909f394a8a82ce138df57c2b355878cac31323f2a</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>R02176 2.6 Microbial community structure analysis（R02444参考文献19所指方法）</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="90" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>R02454-E01</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>R02454</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>FISH technique was used to identify active microbial populations. Fresh biomass samples were taken on days 0, 2, 7 and 9 of the second methanogenic activity test and prepared according to the procedure described by Amann et al.</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>活跃群落通过FISH探针杂交识别，非宏转录组。</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02454/fulltext/fulltext__published__59977732e1c6bb84.pdf</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>59977732e1c6bb84508f823f00ae1c48f9809a63ba2bce7cdb6997d8cf1d90f9</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Fluorescent in situ hybridization (FISH)</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="90" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>R02454-E02</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>R02454</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>The specific activity (g COD g[U+0003]1 VSS d[U+0003]1) was calculated as the ratio between the maximum slope of substrate consumption/production of methane (g COD L[U+0003]1 d[U+0003]1) and the biomass concentration (g VSS L[U+0003]1).</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>活性由底物消耗/甲烷产生斜率和生物量计算，不是测序功能分析。</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02454/fulltext/fulltext__published__59977732e1c6bb84.pdf</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>59977732e1c6bb84508f823f00ae1c48f9809a63ba2bce7cdb6997d8cf1d90f9</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Microbial activity tests</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="90" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>R02578-E01</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>R02578</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Besides the 16S target-specific sequence, the primers also contain adaptor sequences allowing uniform amplification of the library with high complexity ready for downstream NGS sequencing on Illumina Miseq.</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>明确16S引物加接头，非宏基因组。</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02578/fulltext/fulltext__published__6966d35ad0d267fc.pdf</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>6966d35ad0d267fcce96c7957b89e3c92faa8874435872995bfb40f6d8ca3c29</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial community structure（续）</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="90" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>R02578-E02</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>R02578</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>The V3 and V4 regions were amplified using forward primers containing the sequence ‘‘CCTACGGRRBGCASCAGKVRVGAAT” and reverse primers containing the sequence ‘‘GGACTACNVGGGTWTCTAATCC”.</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>扩增特定16S区域；即便PE250/PE300高通量也不符合目标组学。</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02578/fulltext/fulltext__published__6966d35ad0d267fc.pdf</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>6966d35ad0d267fcce96c7957b89e3c92faa8874435872995bfb40f6d8ca3c29</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial community structure（续）</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="90" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>R02585-E01</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>R02585</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>The TS and VS of rice straw or biogas slurry were measured using the gravimetric method. Biogas composition, such as oxygen and methane content, was determined by gas chromatography (GC, thermal conductivity detector (TCD), TDX-01column, carrier gas: argon, column temperature 90 °C, TCD temperature 120 °C, injection port […]</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>完整分析节为重量法、GC和H2S标准分析，无核酸测序。</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02585/fulltext/fulltext__published__ece7fec3277a694d.pdf</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>ece7fec3277a694dcd08802e923d5bc08707b6ecb484f91830cb11a4060b51d6</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Experimental Analytical Methods</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="90" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>R02585-E02</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>R02585</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>The hydrogen sulfide concentration in the biogas was measured using the BNatural gas - Determination of sulfur compound^ standard (GB/T11060.2-2008) (Fig.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>检测H2S按天然气硫化合物标准；微生物仅作过程机理解释。</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02585/fulltext/fulltext__published__ece7fec3277a694d.pdf</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>ece7fec3277a694dcd08802e923d5bc08707b6ecb484f91830cb11a4060b51d6</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Experimental Analytical Methods</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="90" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>R02719-E01</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>R02719</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>All chemical analysis were determined according to American Public Health Association 142 Standard Methods.[29] Specifically, chemical oxygen demand (COD) and volatile suspended 143 solids were analysed according to the closed digestion and colorimetric 5220D method and 144</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>完整分析为COD/VSS等标准理化指标，无组学。</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02719/fulltext/fulltext__version_unverified__4bf5e309b2ef3431.pdf</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Materials and methods（续）</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="90" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>R02719-E02</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>R02719</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Soluble proteins and total sugars were determined using the ASTM D5712 and ASTM 147 D6406 standard methods, respectively. 148 For the statistic processing and analysis of the data, the software Minitab 8 was utilized.</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>蛋白/总糖用ASTM化学测定，非宏蛋白组或测序功能分析。</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02719/fulltext/fulltext__version_unverified__4bf5e309b2ef3431.pdf</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>[7]</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Materials and methods（续）</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="90" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>R02819-E01</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>R02819</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>The 16S rRNA gene hypervariable regions V6–V8 of bacteria and V2–V3 of archaea were amplified by polymerase chain reaction (PCR) using the universal bacterial primers 1401-R and 968-F, and the archaeal primers A 109(T)-F and 515-R (IDT, USA).</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>16S DNA定向PCR，非混合群落RNA-seq。</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02819/fulltext/fulltext__published__bf9c210e52bacc5f.pdf</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>bf9c210e52bacc5f3433ec82a22c8c2ca5c02f522cef26091f584d904fe96289</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Microbial Community Analysis（续）</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="90" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>R02819-E02</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>R02819</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>The double gradient DGGE analysis were performed in a D-Code Universal Mutation Detection System (Bio Rad Laboratories, USA) using polyacrylamide gels with a urea/ formamide denaturing gradient of 42–67 % for bacterial community analysis and 30– 60 % for archaeal community analysis, superimposed with a porous gradient of […]</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>分子检测为16S-DGGE凝胶图谱；后续生态参数均由图谱推导，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02819/fulltext/fulltext__published__bf9c210e52bacc5f.pdf</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>bf9c210e52bacc5f3433ec82a22c8c2ca5c02f522cef26091f584d904fe96289</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Microbial Community Analysis（续）</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="90" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>R02946-E01</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>R02946</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>During the anaerobic periods measurements were carried out on the parameters; soluble COD, NH4-N and PO4-P in both the strictly anaerobic reactors and the intermittent reactors.</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>指标为sCOD、NH4-N、PO4-P，后续比色法及TSS/VSS；无核酸建库。</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02946/fulltext/fulltext__published__7443ff37439e4d1e.pdf</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>7443ff37439e4d1e143f35f9051dcea1c0b6ad3900b9de29d7d662f0dcc1dfe2</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Measurements</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="90" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>R02946-E02</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>R02946</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>The methods are empirical and are indirect means of calculating the anaerobic hydrolysis rates based on the total production of soluble COD (COD(S)) during anaerobic hydrolysis.</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>计算水解速率是基于化学指标的经验方法，不是宏组学或16S功能预测。</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R02946/fulltext/fulltext__published__7443ff37439e4d1e.pdf</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>7443ff37439e4d1e143f35f9051dcea1c0b6ad3900b9de29d7d662f0dcc1dfe2</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Calculation of anaerobic hydrolysis rates</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="90" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>R03161-E01</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>R03161</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Influent and effluent samples from the FS digesters were collected weekly and analyzed for total solids (TS), volatile solids (VS), pH, and alkalinity according to Standard Methods [11].</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>测TS、VS、pH及碱度，气体用便携仪；完整方法无组学。</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03161/fulltext/fulltext__published__ea90043284b5a305.pdf</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>ea90043284b5a305ea2567b3fd65909a17585eeb08bfccd84be2c51df7c90453</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Analytical methods</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="90" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>R03161-E02</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>R03161</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>数据声明语境核查</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>All relevant data are within the paper and its Supporting Information files.</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>仅泛指正文和SI数据可用；结合方法及XLSX，不代表公开原始测序数据。</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03161/fulltext/fulltext__published__ea90043284b5a305.pdf</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>ea90043284b5a305ea2567b3fd65909a17585eeb08bfccd84be2c51df7c90453</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Data Availability Statement</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="90" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>R03161-E03</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>R03161</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>补充表格核查</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Hydrogen sulfide removal as a function of hydrogen sulfide input in biogas using horizontal and vertical barrels</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>工作簿三表为图2/3/5的H2S、氧、产气/去除等工程数值；不是原始测序reads。正文p11明确其为图数据。</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03161/supplementary/supplementary__d7cc276f64fa4c14.xlsx</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>d7cc276f64fa4c14cae6112225870bf2a5daabbfd3ed1243c5cebba459e320f9</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>S1 Appendix XLSX: Figure 2 data; Figure 3 data; Figure 5 data</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Figure 2 data; Figure 3 data; Figure 5 data</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Figure 2 data!A3:B3; Figure 3 data!B2,A6:B6; Figure 5 data!D2,G5</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="90" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>R01917-E05</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>R01917</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>官方元数据查询</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>"count": "0"</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>已知DOI在SRA未检出关联记录；检索索引可能不含DOI，此结果不证明无数据，也不解决建库类型，保留待确认。</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>omics_screening/batches/B003/official_metadata_query_R01917.json</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>3761c60158e6f87701f7aee9c12566c08666c2da6b08c4e0b5787c051918dff0</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA ESearch, exact known DOI; result count</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L65"/>
+  <autoFilter ref="A1:L111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46598,7 +50432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -50853,8 +54687,58 @@
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr"/>
     </row>
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>R01917</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>测序建库/靶区待确认</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R01917/fulltext/fulltext__published__e31cfc89134fbe8a.pdf</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>e31cfc89134fbe8a1ec0d5fcb8a7bfabaec9dac86febd83fa661ee9a73b2e335</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>[2, 3, 5]</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>https://eutils.ncbi.nlm.nih.gov/entrez/eutils/esearch.fcgi?db=sra&amp;term=10.1016%2Fj.biortech.2015.06.072&amp;retmode=json&amp;retmax=20</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>DNA→PCR→454→Mothur/OTU，靶基因和引物序列未明示；现有SI无补充方法/编号。未确认shotgun，不计目标阳性，也不作阴性。 官方SRA以已知DOI查询0条结果；可能未索引DOI，不证明无数据，也未解决建库类型。</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>复核正文引用Wan et al.2014 Long-term storage of aerobic granules in liquid media: viable but non-culturable status 的具体PCR建库方法；本轮不下载缺失文献。</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P103"/>
+  <autoFilter ref="A1:P104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50865,7 +54749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -50951,7 +54835,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -50967,7 +54851,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -50992,7 +54876,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>未完成、缺正文及综述不计阴性；本批零命中不代表剩余队列没有目标测序。</t>
+          <t>未完成、待确认、缺正文及综述不计阴性；本批零命中不代表剩余队列没有目标测序。</t>
         </is>
       </c>
     </row>
@@ -51099,7 +54983,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -51115,7 +54999,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -51180,7 +55064,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>R01917</t>
+          <t>R03164</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -51231,7 +55115,7 @@
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
+          <t>research_screened_count</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -51247,7 +55131,7 @@
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>processed_record_count</t>
+          <t>completed_count</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -51263,13 +55147,11 @@
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>review_not_applicable_ids</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>pending_count</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -51281,11 +55163,13 @@
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0</v>
+          <t>pending_ids</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -51297,11 +55181,11 @@
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -51313,11 +55197,13 @@
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0</v>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -51329,7 +55215,7 @@
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>target_articles</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -51345,7 +55231,7 @@
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>metagenomics_only</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -51361,7 +55247,7 @@
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>explicit_request_articles</t>
+          <t>metatranscriptomics_only</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -51377,37 +55263,31 @@
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>本批完成ID</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>R00651, R00677, R00795, R00888, R01050, R01126, R01212, R01238, R01297, R01347, R01349, R01350, R01362, R01410, R01414, R01505, R01556, R01654, R01727, R01785</t>
-        </is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>B002</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>按稳定ID顺序，逐篇阅读方法；实际综述单列后顺延补足研究篇数。</t>
-        </is>
-      </c>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
+          <t>public_data_articles</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -51415,15 +55295,15 @@
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>processed_record_count</t>
+          <t>explicit_request_articles</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -51431,12 +55311,12 @@
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>review_not_applicable_ids</t>
+          <t>本批完成ID</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>["R00915"]</t>
+          <t>R00651, R00677, R00795, R00888, R01050, R01126, R01212, R01238, R01297, R01347, R01349, R01350, R01362, R01410, R01414, R01505, R01556, R01654, R01727, R01785</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -51444,16 +55324,20 @@
           <t>B002</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；实际综述单列后顺延补足研究篇数。</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
+          <t>research_screened_count</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -51465,11 +55349,11 @@
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
+          <t>completed_count</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -51481,7 +55365,7 @@
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
+          <t>pending_count</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -51497,11 +55381,13 @@
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>0</v>
+          <t>pending_ids</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -51513,11 +55399,11 @@
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -51529,21 +55415,337 @@
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>["R00915"]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>target_articles</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>metagenomics_only</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>metatranscriptomics_only</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>explicit_request_articles</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>B002</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>R02094, R02115, R02176, R02188, R02199, R02239, R02274, R02319, R02340, R02370, R02386, R02444, R02454, R02578, R02585, R02719, R02819, R02946, R03161</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。 未解决项保留待确认，未标记完成或阴性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>research_screened_count</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>pending_count</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>pending_ids</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>["R01917"]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>processed_record_count</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>target_articles</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>metagenomics_only</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>metatranscriptomics_only</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>explicit_request_articles</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D40"/>
+  <autoFilter ref="A1:D59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -51665,7 +55867,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>仅对目标或疑似目标项目读取官方数据库元数据，检查题名、样本、library strategy、公开状态和分组；不下载原始reads。不成功保留文中编号且标未核实。本批无目标/疑似编号，未发起目标库请求。</t>
+          <t>仅对目标或疑似目标项目读取官方数据库元数据，检查题名、样本、library strategy、公开状态和分组；不下载原始reads。不成功保留文中编号且标未核实。仅对已知文章做官方元数据核对；无编号或无结果不证明无数据，见各批次查询记录。</t>
         </is>
       </c>
     </row>
@@ -51708,7 +55910,7 @@
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>当前附件限制</t>
+          <t>B001附件说明</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">

--- a/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
+++ b/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
@@ -19,9 +19,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛查总表'!$A$1:$AF$427</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'目标测序研究'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据项目与样本'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$P$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'口径与字段说明'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8349,22 +8349,62 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析和BMP实验</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>小麦秸秆</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>纯氧注入液相；5/10/15 mL O2/g VS，1–3次脉冲，1–3天</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>AD接种物与AD/堆肥混合接种物；微曝气与不曝气对照</t>
+        </is>
+      </c>
       <c r="S60" s="2" t="inlineStr"/>
       <c r="T60" s="2" t="inlineStr"/>
-      <c r="U60" s="2" t="inlineStr"/>
-      <c r="V60" s="2" t="inlineStr"/>
-      <c r="W60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>BMP批次三平行（不等同于测序重复）</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>完整阅读§2.1–2.5（PDF2–3页）：接种物/底物、响应面设计、BMP批次、理化与色谱分析；未报告核酸提取、建库、测序或公开组学数据复用。</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>正文PDF1–8页定位；方法PDF2–3页§2.1–2.5；末页结论/致谢/参考文献</t>
+        </is>
+      </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03164/fulltext/fulltext__published__948ccf2541317dc8.pdf"]</t>
@@ -8388,13 +8428,21 @@
       <c r="AB60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE60" s="2" t="inlineStr"/>
+          <t>["R03164-E01", "R03164-E02"]</t>
+        </is>
+      </c>
+      <c r="AE60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:49:33.450588+00:00</t>
+        </is>
+      </c>
       <c r="AF60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="60" customHeight="1">
@@ -8445,22 +8493,62 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化分析、GC及SEM</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Napier草（Pennisetum purpureum）</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0/10/15 mL O2/g VS；培养1/3/5天</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>ADCM与ADWAS接种；不同氧剂量和培养时间；无底物空白</t>
+        </is>
+      </c>
       <c r="S61" s="2" t="inlineStr"/>
       <c r="T61" s="2" t="inlineStr"/>
-      <c r="U61" s="2" t="inlineStr"/>
-      <c r="V61" s="2" t="inlineStr"/>
-      <c r="W61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>实验三平行（无测序）</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6（PDF2–3页）及两份现有DOCX均已阅读；仅VFA/沼气/纤维组成/SEM及方差分析，无目标测序或公开数据复用。</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>正文PDF1–7页定位；方法PDF2–3页§2.1–2.6；两份DOCX全部段落/表格</t>
+        </is>
+      </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03220/fulltext/fulltext__published__e3a420e737821dfe.pdf"]</t>
@@ -8484,13 +8572,21 @@
       <c r="AB61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>两份DOCX均为ANOVA表（S1 VFA产率、S2结构碳水）；内容一致但题名/DOI未明确，保持唯一归属待核实，不将附件当独立测序证据。</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE61" s="2" t="inlineStr"/>
+          <t>["R03220-E01", "R03220-E02", "R03220-E03", "R03220-E04"]</t>
+        </is>
+      </c>
+      <c r="AE61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:49:33.478502+00:00</t>
+        </is>
+      </c>
       <c r="AF61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="60" customHeight="1">
@@ -8641,22 +8737,58 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>PCR/DGGE；ADM1-S/O模型（非目标测序）</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>模拟啤酒废水</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>UMSB微曝气与UASB不曝气；空气自第74天起1 L/d；模型改变O2:S</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>复用Krayzelova等[4]反应器过程实验数据进行模型校验，非公开组学数据再分析</t>
+        </is>
+      </c>
       <c r="S63" s="2" t="inlineStr"/>
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr"/>
-      <c r="V63" s="2" t="inlineStr"/>
-      <c r="W63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>完整阅读§2（PDF2–5页）和现有DOCX：ADM1-S/O模型扩展、液气相平衡和Aquasim模拟；颗粒污泥用PCR/DGGE分析（未发表结果），无宏基因组/宏转录组。</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>正文PDF1–9页定位；§2 PDF2–5页；DOCX全部895段落含表S1–S6及§S.1–S.5</t>
+        </is>
+      </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03400/fulltext/fulltext__published__cba2185ab15ca24d.pdf"]</t>
@@ -8680,13 +8812,21 @@
       <c r="AB63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>DOCX§S.1 ADM1-S/O、S.3 pH、S.4气液传质与正文特定交叉引用一致；筛查层记录内容关联证据，原清单的身份待核实状态不改写。无测序方法/编号。</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE63" s="2" t="inlineStr"/>
+          <t>["R03400-E01", "R03400-E02", "R03400-E03"]</t>
+        </is>
+      </c>
+      <c r="AE63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:50:38.276355+00:00</t>
+        </is>
+      </c>
       <c r="AF63" s="2" t="inlineStr"/>
     </row>
     <row r="64" ht="60" customHeight="1">
@@ -8737,22 +8877,58 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；污泥消化/脱硫理化分析</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr"/>
-      <c r="P64" s="2" t="inlineStr"/>
-      <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>碱预处理剩余活性污泥；加硫酸钠</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>每日向顶空供氧；半连续反应器P3–P7为1/5/10/15/20 mL</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>P1无铁无氧；P2加铁无氧；P3–P7加铁供氧；另有铁剂量批次实验</t>
+        </is>
+      </c>
       <c r="S64" s="2" t="inlineStr"/>
       <c r="T64" s="2" t="inlineStr"/>
       <c r="U64" s="2" t="inlineStr"/>
-      <c r="V64" s="2" t="inlineStr"/>
-      <c r="W64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.3（PDF2–4页）：污泥/RSI、批次和半连续消化、理化参数、铁硫形态及气体分析；PDF11内嵌SI为硫平衡和反应器图。未报告核酸/测序。</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>正文PDF1–11页定位；方法PDF2–4页§2；嵌入补充材料PDF11页Table S1/Fig S1</t>
+        </is>
+      </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03455/fulltext/fulltext__published__64a8528ddfd93bdf.pdf"]</t>
@@ -8776,13 +8952,21 @@
       <c r="AB64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>无独立SI文件；PDF11页内嵌Supplementary material已读，内容为硫质量分布及反应器示意图，无测序。</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE64" s="2" t="inlineStr"/>
+          <t>["R03455-E01", "R03455-E02", "R03455-E03"]</t>
+        </is>
+      </c>
+      <c r="AE64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:50:38.306418+00:00</t>
+        </is>
+      </c>
       <c r="AF64" s="2" t="inlineStr"/>
     </row>
     <row r="65" ht="60" customHeight="1">
@@ -8833,22 +9017,62 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；产气、HPLC、理化及模型计算</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr"/>
-      <c r="P65" s="2" t="inlineStr"/>
-      <c r="Q65" s="2" t="inlineStr"/>
-      <c r="R65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>餐厨复合食物废物</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>进料前曝气60 min；§2.1约400 L O2</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>不曝气60 g COD/L对照；曝气60–100 g COD/L不同负荷</t>
+        </is>
+      </c>
       <c r="S65" s="2" t="inlineStr"/>
       <c r="T65" s="2" t="inlineStr"/>
-      <c r="U65" s="2" t="inlineStr"/>
-      <c r="V65" s="2" t="inlineStr"/>
-      <c r="W65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>实验三平行（非测序重复）</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）为底物预曝气、接种物热处理、混合生物膜反应器、产气/HPLC/理化与数据计算；本研究未报告测序。metagenomic profiling仅出现在Sarkar等2016参考文献题名。</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>正文PDF1–9页定位；方法PDF2–3页§2；参考文献PDF9页；DOCX全部34段落</t>
+        </is>
+      </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03475/fulltext/fulltext__published__87798503de877f9d.pdf"]</t>
@@ -8861,7 +9085,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>已取得1件原格式补充材料；其中1件唯一关联待核实；完整性未确认</t>
+          <t>已取得1件DOCX；题名、作者及机构核实关联；完整性未确认</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8870,15 +9094,23 @@
         </is>
       </c>
       <c r="AB65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>DOCX题名仅food/volatile等措辞有差异，Omprakash Sarkar和S. Venkata Mohan两位作者及CSIR-IICT机构与正文一致，研究主题及biohythane图相符；B004筛查层确认唯一关联。仅图及反应式，无测序。原清单字段/原件保留。</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE65" s="2" t="inlineStr"/>
+          <t>["R03475-E01", "R03475-E02", "R03475-E03"]</t>
+        </is>
+      </c>
+      <c r="AE65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T06:50:38.336559+00:00</t>
+        </is>
+      </c>
       <c r="AF65" s="2" t="inlineStr"/>
     </row>
     <row r="66" ht="60" customHeight="1">
@@ -9033,22 +9265,58 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化、SEM/EDX与XRD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr"/>
-      <c r="P67" s="2" t="inlineStr"/>
-      <c r="Q67" s="2" t="inlineStr"/>
-      <c r="R67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>生活污水</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>UASB外接微曝气模块曝气并回流</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>带聚氨酯载体的厌氧混合反应器与微曝气UASB</t>
+        </is>
+      </c>
       <c r="S67" s="2" t="inlineStr"/>
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr"/>
-      <c r="V67" s="2" t="inlineStr"/>
-      <c r="W67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF3–5页）为污水来源、反应器、硫形态/水质分析、SEM/EDX、XRD与硫平衡；无核酸提取、建库、测序或组学再分析。</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；方法PDF3–5页§2.1–2.4</t>
+        </is>
+      </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03497/fulltext/fulltext__published__2d594b9c7205bdf2.pdf"]</t>
@@ -9072,13 +9340,21 @@
       <c r="AB67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE67" s="2" t="inlineStr"/>
+          <t>["R03497-E01", "R03497-E02"]</t>
+        </is>
+      </c>
+      <c r="AE67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:56:27.012526+00:00</t>
+        </is>
+      </c>
       <c r="AF67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="60" customHeight="1">
@@ -9129,22 +9405,62 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；EEM/PARAFAC与理化分析</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr"/>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>合成城市固体废物MSW</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>预曝气0/4/8/14天；0.5 L/min/kg，起始10 min开20 min停</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>AN无预曝气；R(4)/R(8)/R(14)预曝气后100天干式AD</t>
+        </is>
+      </c>
       <c r="S68" s="2" t="inlineStr"/>
       <c r="T68" s="2" t="inlineStr"/>
-      <c r="U68" s="2" t="inlineStr"/>
-      <c r="V68" s="2" t="inlineStr"/>
-      <c r="W68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>固液气分析二平行（非测序重复）</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–4页）为柱实验、荧光EEM/PARAFAC、固液气理化及PCA；现有DOCX为相关图S1–S5，无核酸或测序。</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页定位；方法PDF2–4页§2；DOCX全部96段落</t>
+        </is>
+      </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03518/fulltext/fulltext__published__aa5fd3d1e00f1e87.pdf"]</t>
@@ -9168,13 +9484,21 @@
       <c r="AB68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>现有DOCX为分半/残差、pH/NH4/SCOD、产气及EEM图；内容与正文一致，但无独立题名/DOI，保留原归属待核实，不从图中推断测序。</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE68" s="2" t="inlineStr"/>
+          <t>["R03518-E01", "R03518-E02", "R03518-E03"]</t>
+        </is>
+      </c>
+      <c r="AE68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:56:27.050528+00:00</t>
+        </is>
+      </c>
       <c r="AF68" s="2" t="inlineStr"/>
     </row>
     <row r="69" ht="60" customHeight="1">
@@ -9225,22 +9549,58 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；全规模脱硫运行观测</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr"/>
-      <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>市政污水厂污泥</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>七座污水厂向消化污泥回流管投加空气</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>中央欧洲七座污水厂2003–2015年长期运行；比较微曝气前后H2S及污泥/上清质量</t>
+        </is>
+      </c>
       <c r="S69" s="2" t="inlineStr"/>
       <c r="T69" s="2" t="inlineStr"/>
       <c r="U69" s="2" t="inlineStr"/>
-      <c r="V69" s="2" t="inlineStr"/>
-      <c r="W69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>完整§2（PDF2页）与结果表1–4（PDF2–3页）为七厂运行条件、空气投加及产气/污泥参数；全文无核酸、建库、测序或公开组学数据复用。</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–5页定位；方法PDF2页§2；结果PDF2–3页Tables1–4</t>
+        </is>
+      </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03522/fulltext/fulltext__published__73e8e5aed501f6e5.pdf"]</t>
@@ -9264,13 +9624,21 @@
       <c r="AB69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE69" s="2" t="inlineStr"/>
+          <t>["R03522-E01", "R03522-E02"]</t>
+        </is>
+      </c>
+      <c r="AE69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:56:27.083649+00:00</t>
+        </is>
+      </c>
       <c r="AF69" s="2" t="inlineStr"/>
     </row>
     <row r="70" ht="60" customHeight="1">
@@ -9321,22 +9689,66 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA基因PCR/DGGE条带测序；非宏基因组/宏转录组</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr"/>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>碱预处理剩余活性污泥</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>每日向顶空供氧；P3–P7为1/5/10/15/20 mL</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>P1无铁无氧；P2加20 g/L RSI无氧；P3–P7铁+氧</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>PCR热循环仪、BioRad DGGE；TaKaRa条带PCR产物测序（平台未报告）</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>P1/P2/P6末日共3份污泥；选取DGGE条带</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr"/>
-      <c r="V70" s="2" t="inlineStr"/>
-      <c r="W70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF3–6页）：总DNA提取后以细菌341F/907R、古菌787F/1059R扩增16S；DGGE切带再PCR测序并BLAST。是标记基因条带测序，无shotgun或RNA测序。</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–19页定位；方法PDF3–6页§2；DGGE结果PDF13–15页§3.4及Table5</t>
+        </is>
+      </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03564/fulltext/fulltext__published__2f2d17a0a7254275.pdf"]</t>
@@ -9360,13 +9772,21 @@
       <c r="AB70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE70" s="2" t="inlineStr"/>
+          <t>["R03564-E01", "R03564-E02"]</t>
+        </is>
+      </c>
+      <c r="AE70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:57:18.404965+00:00</t>
+        </is>
+      </c>
       <c r="AF70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="60" customHeight="1">
@@ -9417,22 +9837,62 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；BMP、固相AD及理化分析</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr"/>
-      <c r="P71" s="2" t="inlineStr"/>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>稻草</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>25/35/45°C预曝气；0.5 L/min/kg干底物，0–8天</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>不同温度/预曝气时长及原/稀释接种物；低S/I对照和无底物空白</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="inlineStr"/>
       <c r="T71" s="2" t="inlineStr"/>
-      <c r="U71" s="2" t="inlineStr"/>
-      <c r="V71" s="2" t="inlineStr"/>
-      <c r="W71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>每条件三反应器/分析三平行；无测序</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–4页）：预曝气、AMPTS BMP与固态AD、理化/纤维组分/HPLC及统计；未报告核酸提取、建库或目标测序。</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；方法PDF2–4页§2.1–2.4</t>
+        </is>
+      </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03575/fulltext/fulltext__published__736bf01b6ba7c6e7.pdf"]</t>
@@ -9456,13 +9916,21 @@
       <c r="AB71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE71" s="2" t="inlineStr"/>
+          <t>["R03575-E01", "R03575-E02"]</t>
+        </is>
+      </c>
+      <c r="AE71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:57:18.454176+00:00</t>
+        </is>
+      </c>
       <c r="AF71" s="2" t="inlineStr"/>
     </row>
     <row r="72" ht="60" customHeight="1">
@@ -9721,22 +10189,66 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>16S V4–V5扩增子、18S克隆测序及SSU qPCR（非目标）</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr"/>
-      <c r="S74" s="2" t="inlineStr"/>
-      <c r="T74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>餐厨食物废物</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>气体50 L/h，回流300 L/h；O2 0/5/10/21%，1–4天</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>原料T0；四氧浓度×预处理T1–T4，比较BMP/菌群/酶活</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>Ion Torrent PGM（16S）；18S克隆测序平台未报告</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>文中各FW样本16S；21%O2第4天真菌18S克隆48条；非目标测序</t>
+        </is>
+      </c>
       <c r="U74" s="2" t="inlineStr"/>
-      <c r="V74" s="2" t="inlineStr"/>
-      <c r="W74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.8（PDF2–4页）：§2.6明确16S V4–V5高通量测序+97% OTU/QIIME及422 bp 18S克隆测序；酶活为FDA/APIZYM生化测定，非宏转录组。未报告目标测序/公开组学复用。</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页定位；方法PDF2–4页§2；真菌编号PDF7页§3.2.3；16S多样性PDF8页</t>
+        </is>
+      </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03737/fulltext/fulltext__published__a01cf0612b37cb24.pdf"]</t>
@@ -9760,13 +10272,21 @@
       <c r="AB74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立SI原件；正文有明确的16S/18S与酶活方法。</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE74" s="2" t="inlineStr"/>
+          <t>["R03737-E01", "R03737-E02", "R03737-E03"]</t>
+        </is>
+      </c>
+      <c r="AE74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:57:18.486181+00:00</t>
+        </is>
+      </c>
       <c r="AF74" s="2" t="inlineStr"/>
     </row>
     <row r="75" ht="60" customHeight="1">
@@ -9921,22 +10441,66 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA基因V3–V4扩增子（非目标）</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr"/>
-      <c r="S76" s="2" t="inlineStr"/>
-      <c r="T76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>模拟厌氧消化后市政废水，葡萄糖COD 70 mg/L</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>跌水复氧及回流调节DO；三阶段约1.53/0.37/0.5 mg/L</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>种泥S1；第60天S2；第128天S3</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（文中使用pyrosequencing措辞；靶标明确为16S PCR产物）</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>3份污泥样本S1/S2/S3</t>
+        </is>
+      </c>
       <c r="U76" s="2" t="inlineStr"/>
-      <c r="V76" s="2" t="inlineStr"/>
-      <c r="W76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6（PDF2–3页）：DNA提取后以341F/805R扩增16S V3–V4，MiSeq测PCR产物；其余水质/SEM。无群落shotgun或RNA建库。</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；方法PDF2–3页§2；PDF7页补充材料说明</t>
+        </is>
+      </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
           <t>["original_files/R03900/fulltext/fulltext__published__254540c6f1846351.pdf"]</t>
@@ -9960,13 +10524,21 @@
       <c r="AB76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>正文PDF7页称现有未取得的电子SI为颗粒化SEM图；当前无独立SI原件，单列缺口；不将SEM图视为原始reads。</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE76" s="2" t="inlineStr"/>
+          <t>["R03900-E01", "R03900-E02", "R03900-E03"]</t>
+        </is>
+      </c>
+      <c r="AE76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:57:57.716907+00:00</t>
+        </is>
+      </c>
       <c r="AF76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="60" customHeight="1">
@@ -10121,22 +10693,62 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；纯菌培养、酶活、BMP与XRD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>5 mL O2/g VS，37°C微好氧预处理24 h</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>沼液/枯草芽孢杆菌培养液比例1:0、2:1、1:1、1:2、0:1；无菌/无曝气直接消化对照</t>
+        </is>
+      </c>
       <c r="S78" s="2" t="inlineStr"/>
       <c r="T78" s="2" t="inlineStr"/>
-      <c r="U78" s="2" t="inlineStr"/>
-      <c r="V78" s="2" t="inlineStr"/>
-      <c r="W78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>预处理和消化实验三平行（无测序）</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）：Bacillus subtilis培养、微好氧预处理、BMP、GC/VFA、比色酶活、纤维组分和XRD；未报告纯菌或群落核酸测序。</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–6页定位；方法PDF2–3页§2.1–2.5</t>
+        </is>
+      </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04028/fulltext/fulltext__published__6c89d60f8df5d2c8.pdf"]</t>
@@ -10160,13 +10772,21 @@
       <c r="AB78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE78" s="2" t="inlineStr"/>
+          <t>["R04028-E01", "R04028-E02"]</t>
+        </is>
+      </c>
+      <c r="AE78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:57:57.750936+00:00</t>
+        </is>
+      </c>
       <c r="AF78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="60" customHeight="1">
@@ -10217,22 +10837,58 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；反应器、理化/产气与R统计</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="2" t="inlineStr"/>
-      <c r="Q79" s="2" t="inlineStr"/>
-      <c r="R79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>市政剩余活性污泥</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>中间55°C好氧段0.25 L空气/kg/min</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>单级37°C厌氧1S；三级厌氧-好氧-厌氧3S</t>
+        </is>
+      </c>
       <c r="S79" s="2" t="inlineStr"/>
       <c r="T79" s="2" t="inlineStr"/>
       <c r="U79" s="2" t="inlineStr"/>
-      <c r="V79" s="2" t="inlineStr"/>
-      <c r="W79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>完整METHODS（PDF2–3页）为两系统搭建、干物质/VS/COD/pH、气相色谱与DO测量、R的biogas统计计算；无DNA/RNA提取、建库或测序/组学再分析。</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–6页定位；METHODS PDF2–3页Reactor systems / Sample collection and analysis / Data analysis</t>
+        </is>
+      </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04060/fulltext/fulltext__published__5cb0e5b9a358787b.pdf"]</t>
@@ -10256,13 +10912,21 @@
       <c r="AB79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE79" s="2" t="inlineStr"/>
+          <t>["R04060-E01", "R04060-E02"]</t>
+        </is>
+      </c>
+      <c r="AE79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:57:57.785782+00:00</t>
+        </is>
+      </c>
       <c r="AF79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="60" customHeight="1">
@@ -10313,22 +10977,58 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；ADM1过程模型及理化分析</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr"/>
-      <c r="Q80" s="2" t="inlineStr"/>
-      <c r="R80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>浓缩混合污泥，加Na2SO4</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>污泥回流线微曝气；根据沼气产量手动调整O2流量</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>200 L中温反应器前70天严格厌氧，随后微曝气；过程模型校准</t>
+        </is>
+      </c>
       <c r="S80" s="2" t="inlineStr"/>
       <c r="T80" s="2" t="inlineStr"/>
       <c r="U80" s="2" t="inlineStr"/>
-      <c r="V80" s="2" t="inlineStr"/>
-      <c r="W80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–3页）为反应器过程数据、GC/HPLC与水质分析、Matlab ADM1扩展/参数校准；“微生物群落”是模型状态量，无群落DNA/RNA测序或公开组学复用。</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–7页定位；方法PDF2–3页§2.1–2.4</t>
+        </is>
+      </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04092/fulltext/fulltext__published__187b868956ed3e07.pdf"]</t>
@@ -10352,13 +11052,21 @@
       <c r="AB80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE80" s="2" t="inlineStr"/>
+          <t>["R04092-E01", "R04092-E02"]</t>
+        </is>
+      </c>
+      <c r="AE80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:58:27.292417+00:00</t>
+        </is>
+      </c>
       <c r="AF80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="60" customHeight="1">
@@ -10409,22 +11117,58 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；生物膜气体传质/氧化与理化分析</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr"/>
-      <c r="P81" s="2" t="inlineStr"/>
-      <c r="Q81" s="2" t="inlineStr"/>
-      <c r="R81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>实验室模拟沼气；中试乳清进料</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>PVDF生物膜供空气；中试从400降至0.8–4 mL空气/min等阶段</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>裸膜、湿膜、生物膜三配置；250 L中试CSTR分供氧阶段</t>
+        </is>
+      </c>
       <c r="S81" s="2" t="inlineStr"/>
       <c r="T81" s="2" t="inlineStr"/>
       <c r="U81" s="2" t="inlineStr"/>
-      <c r="V81" s="2" t="inlineStr"/>
-      <c r="W81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–4页）：膜传质/反应速率计算、CSTR、H2S传感器、GC、标准水质/元素及XRF；未报告核酸、测序或组学再分析。</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页定位；方法PDF2–4页§2.1–2.4</t>
+        </is>
+      </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04111/fulltext/fulltext__published__4e16411a50808da0.pdf"]</t>
@@ -10448,13 +11192,21 @@
       <c r="AB81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE81" s="2" t="inlineStr"/>
+          <t>["R04111-E01", "R04111-E02"]</t>
+        </is>
+      </c>
+      <c r="AE81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:58:27.324350+00:00</t>
+        </is>
+      </c>
       <c r="AF81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="60" customHeight="1">
@@ -10609,22 +11361,58 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；水质、产气与污泥粒径分析</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr"/>
-      <c r="P83" s="2" t="inlineStr"/>
-      <c r="Q83" s="2" t="inlineStr"/>
-      <c r="R83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>葡萄糖人工废水</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>各隔室曝气，DO约0.3 mg/L，ORP −380至−400 mV</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>微好氧折流反应器与厌氧ABR平行；六个进水COD阶段</t>
+        </is>
+      </c>
       <c r="S83" s="2" t="inlineStr"/>
       <c r="T83" s="2" t="inlineStr"/>
       <c r="U83" s="2" t="inlineStr"/>
-      <c r="V83" s="2" t="inlineStr"/>
-      <c r="W83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）：装置/废水/接种物/负荷条件，COD/VFA/DO、排水量气与湿筛粒径；无核酸、建库或测序。</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–7页定位；方法PDF2–3页§2.1–2.5</t>
+        </is>
+      </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04177/fulltext/fulltext__published__09b0de58af2ff1e6.pdf"]</t>
@@ -10648,13 +11436,21 @@
       <c r="AB83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE83" s="2" t="inlineStr"/>
+          <t>["R04177-E01"]</t>
+        </is>
+      </c>
+      <c r="AE83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:58:27.353507+00:00</t>
+        </is>
+      </c>
       <c r="AF83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="60" customHeight="1">
@@ -10705,22 +11501,62 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；产气、水质与Gompertz模型</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
-      <c r="R84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>餐厨食物废物</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>开放烧瓶接触空气，37°C预处理2/5/8天，每日摇动三次</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>不同预处理时间；不预处理对照；ISR 1.0与0.9；接种物空白</t>
+        </is>
+      </c>
       <c r="S84" s="2" t="inlineStr"/>
       <c r="T84" s="2" t="inlineStr"/>
-      <c r="U84" s="2" t="inlineStr"/>
-      <c r="V84" s="2" t="inlineStr"/>
-      <c r="W84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>消化实验二平行；无测序</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.3（PDF2–3页）：预处理/AD实验，固体/元素/pH/HPLC/气相色谱与Gompertz模型。未报告核酸、测序或公开组学再分析。</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；方法PDF2–3页§2.1–2.3</t>
+        </is>
+      </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04324/fulltext/fulltext__published__1590c60360a46d39.pdf"]</t>
@@ -10744,13 +11580,21 @@
       <c r="AB84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE84" s="2" t="inlineStr"/>
+          <t>["R04324-E01", "R04324-E02"]</t>
+        </is>
+      </c>
+      <c r="AE84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:59:00.158934+00:00</t>
+        </is>
+      </c>
       <c r="AF84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="60" customHeight="1">
@@ -10801,22 +11645,58 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；运行、产气与理化分析</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr"/>
-      <c r="P85" s="2" t="inlineStr"/>
-      <c r="Q85" s="2" t="inlineStr"/>
-      <c r="R85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>禽舍垫料，另有鹅掌楸木片测质量损失</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>地下H形管每次供气200 mL/15 min；0/1/4/10次每天</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>133 L消化工作体积，四个供气水平，连续周进料</t>
+        </is>
+      </c>
       <c r="S85" s="2" t="inlineStr"/>
       <c r="T85" s="2" t="inlineStr"/>
       <c r="U85" s="2" t="inlineStr"/>
-      <c r="V85" s="2" t="inlineStr"/>
-      <c r="W85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>原始实验研究，完整§2.1–2.3（PDF2–4页）为装置/操作、气体/废水/固体标准分析和GC/SAS统计。未报告DNA/RNA测序；原分类保持。</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；方法PDF2–4页§2.1–2.3</t>
+        </is>
+      </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04477/fulltext/fulltext__published__dc52821c42ce8476.pdf"]</t>
@@ -10840,13 +11720,21 @@
       <c r="AB85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE85" s="2" t="inlineStr"/>
+          <t>["R04477-E01", "R04477-E02"]</t>
+        </is>
+      </c>
+      <c r="AE85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:59:00.188434+00:00</t>
+        </is>
+      </c>
       <c r="AF85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="60" customHeight="1">
@@ -10897,22 +11785,62 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；理化、金属ICP与产气分析</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="inlineStr"/>
-      <c r="Q86" s="2" t="inlineStr"/>
-      <c r="R86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>富硫酸盐/硫化物合成废水</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>连续空气0.008 vvm</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>低/高COD负荷；矿业固废MW、粉煤灰FA、微曝气MA及不处理对照</t>
+        </is>
+      </c>
       <c r="S86" s="2" t="inlineStr"/>
       <c r="T86" s="2" t="inlineStr"/>
-      <c r="U86" s="2" t="inlineStr"/>
-      <c r="V86" s="2" t="inlineStr"/>
-      <c r="W86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>处理/对照三平行；分析至少二平行（非测序）</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>阅读当前32页接受稿完整Materials and methods（PDF4–8页）：反应器、金属废物、接种物/设计、APHA理化、ICP金属及t检验/ANOVA；没有目标测序或组学复用。</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–32页定位；方法PDF4–8页；图表PDF24–32页</t>
+        </is>
+      </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04510/fulltext/fulltext__version_unverified__c4520ca79e301bb6.pdf"]</t>
@@ -10936,13 +11864,21 @@
       <c r="AB86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>当前正文为接受稿（PDF1页明示）；保持清单版本原字段。后部为本文图表，无独立SI原件。</t>
+        </is>
+      </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE86" s="2" t="inlineStr"/>
+          <t>["R04510-E01", "R04510-E02"]</t>
+        </is>
+      </c>
+      <c r="AE86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:59:00.217616+00:00</t>
+        </is>
+      </c>
       <c r="AF86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="60" customHeight="1">
@@ -44393,7 +45329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -50420,8 +51356,2732 @@
         </is>
       </c>
     </row>
+    <row r="112" ht="90" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>R03164-E01</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>R03164</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Batch assays were conducted in thermophilic conditions (55 [U+0003]C)
+in triplicates according to the guidelines of Angelidaki et al. (2009).</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>BMP批次实验；完整方法无目标测序流程。</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03164/fulltext/fulltext__published__948ccf2541317dc8.pdf</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>948ccf2541317dc8e00eb42160e9daec06bc8b39c43b79359b07d0bcd90014a5</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Experimental procedure</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="90" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>R03164-E02</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>R03164</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>The TS, VS, TKN, NHþ
+4 -N and COD were determined according to
+the Standard Methods (APHA, 2005).</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>完整分析方法为理化、元素/碳水组成及气相/离子色谱；未报告群落DNA/RNA测序。</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03164/fulltext/fulltext__published__948ccf2541317dc8.pdf</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>948ccf2541317dc8e00eb42160e9daec06bc8b39c43b79359b07d0bcd90014a5</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="90" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>R03220-E01</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>R03220</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Fiber compositions (i.e.,
+NDF, ADF, and ADL) were analyzed before and after AD using a cell
+wall fractionation method, according to Van Soest (Faithfull, 2002).</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6为Napier草VFA实验、纤维组成、GC及SEM分析，无核酸/测序方法。</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03220/fulltext/fulltext__published__e3a420e737821dfe.pdf</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>e3a420e737821dfea7af915ed874babf5028acd2c2ac56810527678967b2b408</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="90" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>R03220-E02</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>R03220</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Then the specimens were viewed with a ﬁeld
+emission SEM (Hitachi S-4800, japan) at an accelerating voltage
+of 5.0 kV.</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>形态检测为SEM，不是测序。</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03220/fulltext/fulltext__published__e3a420e737821dfe.pdf</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>e3a420e737821dfea7af915ed874babf5028acd2c2ac56810527678967b2b408</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="90" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>R03220-E03</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>R03220</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Appendix A. Supplementary data</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>全文读取现有附件：仅ANOVA表，无测序方法/编号；目录与内容相符但无独立题名/DOI，不用其编号归属正文。</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03220/supplementary/supplementary__c26f71c81867faf0.docx</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>c26f71c81867faf0f35f9d5573b3f197c6b071c173aeb47911a1e7bd7f21badb</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落1–71</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="90" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>R03220-E04</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>R03220</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Table S2. ANOVA table of structural carbohydrate in selected conditions compared with the raw Napier grass</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>全文读取现有附件：仅ANOVA表，无测序方法/编号；目录与内容相符但无独立题名/DOI，不用其编号归属正文。</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03220/supplementary/supplementary__285191e1fb2e2380.docx</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>285191e1fb2e2380af580874c7bc1fe0511fdeacc29d469b2a65533c413cef1b</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落1–21</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="90" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>R03400-E01</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>R03400</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>The
+ granular
+ sludge
+ from
+ UASB
+ and
+ UMSB
+ reactor
+ [4]
+ was
+ ana-
+lysed
+ by
+ PCR
+ and
+ DGGE.</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>原PDF逐词换行，此处只合并空白；检测明确为PCR/DGGE，非目标测序。</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03400/fulltext/fulltext__published__cba2185ab15ca24d.pdf</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>cba2185ab15ca24da84a7c037b3828d6d8e604231ec94a59baf4ca3062420a67</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Reactor configuration – simulation set-up</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="90" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>R03400-E02</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>R03400</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>The
+ model
+ was
+ validated
+ on
+ the
+ experimental
+ data
+ described
+ by
+Krayzelova
+ et
+ al.
+ [4], comparing
+ the
+ behavior
+ of
+ two
+ UASB
+ reac-
+tors,
+ a
+ strictly
+ anaerobic
+ UASB
+ and
+ a
+ microaerobic
+ one
+ (termed
+UMSB).</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>复用的是过程实验数据；完整方法未使用既有公开组学数据。</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03400/fulltext/fulltext__published__cba2185ab15ca24d.pdf</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>cba2185ab15ca24da84a7c037b3828d6d8e604231ec94a59baf4ca3062420a67</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Reactor configuration – simulation set-up</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="90" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>R03400-E03</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>R03400</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>The stoichiometric matrix, composition matrix and kinetic expressions for ADM1-S/O are summarized in Tables S1 and S2.  Tables S3, S4 and S5 list the corresponding stoichiometric, kinetic and physicochemical parameters, respectively.</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>补充内容是ADM1-S/O计量矩阵和模型参数，与正文§2跨节引用一致；无目标测序。</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03400/supplementary/supplementary__01a0c3f189551435.docx</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>01a0c3f1895514354073ac76fd5eba93eb36e465a996317f8fb16b0f985f2639</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落2–3、817–871；§S.1–S.5</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="90" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>R03455-E01</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>R03455</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>TS, VS, total suspended solids (TSS), volatile suspended 
+solids (VSS), total chemical oxygen demand (TCOD) and 
+soluble chemical oxygen demand (SCOD) were measured 
+according to the standard methods [21].</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>完整分析方法为理化和硫/铁/气体测量，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03455/fulltext/fulltext__published__64a8528ddfd93bdf.pdf</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>64a8528ddfd93bdf1c052560305416eb52315f9e1c60e1e846a8201168bfe2bd</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analysis</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="90" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>R03455-E02</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>R03455</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Biogas composition (CH4, CO2, H2S and O2) was mea­
+sured daily using a portable biogas analyzer (Biogas 5000, 
+Geotech, UK).</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>气体组分检测而非测序。</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03455/fulltext/fulltext__published__64a8528ddfd93bdf.pdf</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>64a8528ddfd93bdf1c052560305416eb52315f9e1c60e1e846a8201168bfe2bd</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analysis</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="90" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>R03455-E03</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>R03455</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>The mass distribution of sulfur compounds (mg) in the system before and after semi-continuous anaerobic and microaerobic</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>内嵌SI为硫平衡表和装置示意图。</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03455/fulltext/fulltext__published__64a8528ddfd93bdf.pdf</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>64a8528ddfd93bdf1c052560305416eb52315f9e1c60e1e846a8201168bfe2bd</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>[11]</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary material, Table S1/Fig S1</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="90" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>R03475-E01</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>R03475</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Biogas
+composition
+was
+analyzed
+using
+gas
+chromatography (GC; NUCON 5765) with thermal conductivity
+detector (TCD)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>完整方法为产气、VFA/醇色谱和理化分析，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03475/fulltext/fulltext__published__87798503de877f9d.pdf</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>87798503de877f9daa12f0581b7411045b6801a5a720bc6d6510c01d9a01dd32</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analysis</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="90" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>R03475-E02</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>R03475</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>术语命中排除</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>metagenomic proﬁling. RSC Adv. 6,
+18641.</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>目标术语为参考文献题名，不是本研究测序方法。</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03475/fulltext/fulltext__published__87798503de877f9d.pdf</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>87798503de877f9daa12f0581b7411045b6801a5a720bc6d6510c01d9a01dd32</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>[9]</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>References: Sarkar et al. 2016</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="90" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>R03475-E03</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>R03475</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Pre-aeration of waste to augment acidogenic process at higher organic load: Valorizing Biohydrogen, Fatty acids and Biohythane
+Omprakash Sarkar and S. Venkata Mohan*
+Bioengineering and Environmental Sciences Lab, EEFF Department,
+CSIR-Indian Institute of Chemical Technology (CSIR-IICT), Hyderabad 500 007, India</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>题名细微措辞差异，两位作者及机构一致，支持本研究补充材料唯一关联；内容为biohythane图和化学反应式，无目标测序/编号。</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03475/supplementary/supplementary__e076e49096bc6bd6.docx</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>e076e49096bc6bd6044ca3d101f15ed36f99724ebe224f8bd571bcfdb4029a91</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落1–5、11、21–29</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="90" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>R03497-E01</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>R03497</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>The standard methods described by the APHA/AWWA/
+WEF [22] were employed to assess COD (titrimetric
+closed reﬂux; APHA/AWWA/WEF section 5220C), sul-
+phide
+(methylene
+blue
+method;
+APHA/AWWA/WEF
+section 4500D) and pH (potentiometry).</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>完整分析方法为水质/硫形态、离子色谱及物相分析，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03497/fulltext/fulltext__published__2d594b9c7205bdf2.pdf</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>2d594b9c7205bdf2e74f389879019103da37df12335f8ec4410e17b716273d88</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analysis of raw sewage and reactor effluents</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="90" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>R03497-E02</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>R03497</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Scanning electron microscopy
+with energy-dispersive X-ray (SEM/EDX) was performed
+using a TM-1000 bench model instrument (Hitachi,
+Tokyo, Japan) to observe submicron-scale features of
+the solid material precipitated in the anaerobic ﬁlter
+efﬂuent and to provide elemental identiﬁcation and
+quantitative compositional information.</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>SEM/EDX观察沉淀材料并做元素鉴定，不是序列数据。</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03497/fulltext/fulltext__published__2d594b9c7205bdf2.pdf</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>2d594b9c7205bdf2e74f389879019103da37df12335f8ec4410e17b716273d88</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analysis of raw sewage and reactor effluents</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="90" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>R03518-E01</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>R03518</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Fluorescence EEM spectroscopy was measured using a Hitachi
+F-7000 ﬂuorescence spectrometer (Hitachi, Japan) at room temper-
+ature according to He et al. [23], with minor modiﬁcations.</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>测量为DOM荧光光谱；完整方法无测序。</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03518/fulltext/fulltext__published__aa5fd3d1e00f1e87.pdf</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>aa5fd3d1e00f1e8768d9bad2473792657a558c3343e29685e3f49a421f92e1f5</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Characterisation of spectroscopy</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="90" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>R03518-E02</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>R03518</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>The ﬁltrate was tested for pH, dissolved organic carbon
+(DOC),
+alkalinity,
+soluble
+chemical
+oxygen
+demand
+(SCOD),
+NH4
++-N, and VFAs according to APHA methods [29].</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>其他分析为水质与理化参数。</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03518/fulltext/fulltext__published__aa5fd3d1e00f1e87.pdf</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>aa5fd3d1e00f1e8768d9bad2473792657a558c3343e29685e3f49a421f92e1f5</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Other analytical methods</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="90" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>R03518-E03</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>R03518</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Figure S5. Typical EEM spectra of DOM in the leachate from dry AD process with different pre-aeration durations; normalized to 5 mg/L DOC.</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>现有附件仅光谱/产气/水质图，无测序方法或编号；保留唯一归属待核实。</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03518/supplementary/supplementary__be818d1094ea8d29.docx</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>be818d1094ea8d2923262b22fae68207e53b62fb804db043c45a43353bd3112e</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落1–6及28–95</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="90" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>R03522-E01</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>R03522</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Microaeration has been applied on seven municipal wastewater
+treatment plants (WWTPs) in central Europe. Their characteriza-
+tion is described in Table 1.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>原始全规模运行研究；并非综述，方法没有测序。</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03522/fulltext/fulltext__published__73e8e5aed501f6e5.pdf</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>73e8e5aed501f6e51c306bb0e9a6208d27f9d0dcd78b08465ec99c1c8bec1c29</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>2 Material and methods</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="90" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>R03522-E02</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>R03522</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>In all evaluated di-
+gesters, air has been dosed into the recirculation stream (Fig. 2).</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>描述空气投加装置；全文结果为脱硫及污泥质量变化，不含目标测序。</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03522/fulltext/fulltext__published__73e8e5aed501f6e5.pdf</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>73e8e5aed501f6e51c306bb0e9a6208d27f9d0dcd78b08465ec99c1c8bec1c29</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>2 Material and methods</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="90" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>R03564-E01</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>R03564</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>A primer combination of 341F
+(5′-CCTACGGGAGGCAGCAG-3′) and 907R (5′-CCGTCAATTCCTTTGAGTTT-3′) was used to
+selectively amplify the 16S rRNA sequences of bacteria [27]. Another primer combination of 787F
+(5′-ATTAGA TACCCTGGTAGTCC-3′) and 1059R (5′-GGACTACCAGGGTATCTAAT-3′) was used to
+selectively amplify the 16S rRNA sequences of archaea [28].</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>明确两套引物扩增细菌/古菌16S rRNA基因，不是群落DNA随机建库。</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03564/fulltext/fulltext__published__2f2d17a0a7254275.pdf</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>2f2d17a0a7254275b5799c7fcd7ba57973ca0b4c3ec6b9eaf4fcfe65bf7f66d9</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>2.4 DNA Extraction, Amplification by PCR, DGGE and Sequencing</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="90" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>R03564-E02</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>R03564</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Selected DGGE bands were excised and re-ampliﬁed by PCR with the aforementioned primers
+without the GC clamp. The PCR products were sequenced at TaKaRa Biotechnology Co.
+Ltd.,
+(Dalian, China).</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>测序对象是切胶再扩增的标记基因条带；全文方法未报告目标测序。</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03564/fulltext/fulltext__published__2f2d17a0a7254275.pdf</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>2f2d17a0a7254275b5799c7fcd7ba57973ca0b4c3ec6b9eaf4fcfe65bf7f66d9</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>2.4 DNA Extraction, Amplification by PCR, DGGE and Sequencing</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="90" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>R03575-E01</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>R03575</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>To determine the biochemical methane potential (BMP) and
+compare the efﬁciency from the rice straw treated under different
+regimes (incubation temperatures and aeration times), the batch-
+mode Automatic Methane Potential Test System (AMPTS II) (Bio-
+process Control AB, Sweden) was used to perform BMP tests.</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>实验为BMP产气评估。</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03575/fulltext/fulltext__published__736bf01b6ba7c6e7.pdf</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>736bf01b6ba7c6e7251c68d2c24899da7cf96fca77f1ddb24151133618ed45f5</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>2.2.2 Methane potential assessment</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="90" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>R03575-E02</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>R03575</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>The changes of cellulose, hemicellulose and lignin contents
+were determined by the standard analysis of hydrolysis process
+described by the National Renewable Energy Laboratory (NREL)
+Analytical Procedure (Sluiter et al., 2008).</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>完整分析方法为固体、碳氮、纤维组分及VFAs等理化分析，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03575/fulltext/fulltext__published__736bf01b6ba7c6e7.pdf</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>736bf01b6ba7c6e7251c68d2c24899da7cf96fca77f1ddb24151133618ed45f5</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="90" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>R03737-E01</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>R03737</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Bacterial and archaeal diver-
+sity was determined by high throughput DNA sequencing of the
+16S rRNA gene V4-V5 variable regions using Ion TorrentTM PGM
+technology (Life Technologies, USA) at the IRSTEA BIOMIC team
+(Antony, France) (Poirier et al. (2016).</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Ion Torrent测的是16S V4–V5，非宏基因组。</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03737/fulltext/fulltext__published__a01cf0612b37cb24.pdf</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>a01cf0612b37cb24266d34adcc648fcab6d66b40737d0f275e61dd9c4e3f4de0</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Characterisation and dynamics of FW microbial community</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="90" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>R03737-E02</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>R03737</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Fungal diversity was investigated by col-
+lecting mycelium on day 4 of the 21%O2 pre-treatment condition,
+extracting DNA and cloning and sequencing of a 422 bp fragment
+of the 18S rRNA genes.</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>真菌为422bp 18S标记片段克隆，不是宏转录组。</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03737/fulltext/fulltext__published__a01cf0612b37cb24.pdf</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>a01cf0612b37cb24266d34adcc648fcab6d66b40737d0f275e61dd9c4e3f4de0</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Characterisation and dynamics of FW microbial community</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="90" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>R03737-E03</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>R03737</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>非目标编号排除</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Out of the 48 clones
+sequenced, 31 were identiﬁed as Rhizopus oryzae isolate A2 (acc.
+KM527239) and 12 as Lichtheimia ramosa (acc. LK023322), all with
+99% of sequence similarity.</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>KM527239、LK023322是文中用于克隆比对鉴定的序列编号，非本研究目标测序项目号。</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03737/fulltext/fulltext__published__a01cf0612b37cb24.pdf</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>a01cf0612b37cb24266d34adcc648fcab6d66b40737d0f275e61dd9c4e3f4de0</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>[7]</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>3.2.3 Fungal growth/identification</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="90" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>R03900-E01</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>R03900</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Ampliﬁcations of bacterial 16S rRNA genes for
+the V3–V4 regions were performed with bacterial fused primers 341F
+and 805R (Herlemann et al., 2011; Hugerth et al., 2014).</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>靶标和引物明确：16S V3–V4扩增子，不是宏基因组。</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03900/fulltext/fulltext__published__254540c6f1846351.pdf</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>254540c6f1846351c168ff143b23a9032a3d0d2ea7dfa538972b5679d47155fc</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>2.5 DNA extraction and Illumina MiSeq sequencing</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="90" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>R03900-E02</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>R03900</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>The speciﬁc
+procedure of polymerase chain reaction (PCR) was conducted according
+to a previous study (Zhou et al., 2015). The composition of PCR pro-
+ducts of V4 region was determined by pyrosequencing using the Illu-
+mina Miseq sequencer platform (Shanghai Sangon, China).</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>MiSeq用于PCR扩增产物；不能仅根据平台判断宏基因组。</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03900/fulltext/fulltext__published__254540c6f1846351.pdf</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>254540c6f1846351c168ff143b23a9032a3d0d2ea7dfa538972b5679d47155fc</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>2.5 DNA extraction and Illumina MiSeq sequencing</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="90" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>R03900-E03</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>R03900</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>补充材料缺口</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>The SEM images of granulation process were shown in E-supplementary
+data and could be found in e-version of this paper online.</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>未取得的电子SI被正文描述为SEM图；记录缺口，不扩大到目标测序。</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03900/fulltext/fulltext__published__254540c6f1846351.pdf</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>254540c6f1846351c168ff143b23a9032a3d0d2ea7dfa538972b5679d47155fc</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>[7]</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>3.4 Granulation / E-supplementary data</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="90" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>R04028-E01</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>R04028</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>During the micro-aerobic pretreatment
+process, the supernatants were sampled after 24 h for determination of
+volatile
+fatty
+acid
+(VFAs),
+peroxidase,
+carboxymethyl
+cellulase
+(CMCase) and glucose. Corn straw in every bottle was collected to
+measure crystallinity degree after pretreatment.</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>测量对象为VFA、酶活、葡萄糖及结晶度，非测序。</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04028/fulltext/fulltext__published__6c89d60f8df5d2c8.pdf</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>6c89d60f8df5d2c84795246955c483c1fc417ced115b4bc688f693481acf8306</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Bacteria micro-aerobic pretreatment</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="90" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>R04028-E02</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>R04028</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Cellulase (CMCase) was
+determined by sodium carboxymethyl cellulose method at 540 nm
+(Ridge &amp; Osborne, 1969).</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>酶活为比色底物法，不能视为转录组。</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04028/fulltext/fulltext__published__6c89d60f8df5d2c8.pdf</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>6c89d60f8df5d2c84795246955c483c1fc417ced115b4bc688f693481acf8306</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>2.4.2 Enzyme analysis</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="90" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>R04060-E01</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>R04060</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Feed dry matter (DM) and VS were determined weekly or
+every time a new batch of raw sludge was collected from
+the wastewater treatment plant, based on drying at 105 [U+0001]C
+and combustion at 550 [U+0001]C (APHA, AWWA, WEF ).</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>完整分析方法为固体/水质及产气指标，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04060/fulltext/fulltext__published__5cb0e5b9a358787b.pdf</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>5cb0e5b9a358787b0372cd47291d6e4263f7a8b62aec464bf4999625319a94f5</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>METHODS – Sample collection and analysis</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="90" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>R04060-E02</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>R04060</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>All data analysis was done using R (R Core Team ).
+Biogas
+and
+CH4
+production
+were
+determined
+from
+measured volumes and composition using the cumBg func-
+tion in the biogas package (Hafner et al. ) and
+expressed as dry volume at 0 [U+0001]C and 101.325 kPa.</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>biogas为R计算包，用于气量计算，非生物信息学测序分析。</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04060/fulltext/fulltext__published__5cb0e5b9a358787b.pdf</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>5cb0e5b9a358787b0372cd47291d6e4263f7a8b62aec464bf4999625319a94f5</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>METHODS – Data analysis</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="90" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>R04092-E01</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>R04092</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>The biogas production
+was measured by liquid displacement and the biogas composition
+was determined by GC-TCD. Sulfate concentration was measured
+by HPLC-IC. VFA concentrations were quantiﬁed by GC-FID.
+Alkalinity, ammonium, TKN, COD, TS, VS, total dissolved sulﬁde,
+pH and ORP were determined according to standard methods [19].</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>完整实验数据为气体、硫酸盐、VFA及理化指标。</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04092/fulltext/fulltext__published__187b868956ed3e07.pdf</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>187b868956ed3e07456eb08dd523d037ffb342e17033c71274fc2618ce78b4ef</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>2.1 Experimental data</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="90" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>R04092-E02</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>R04092</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>ADM1 was implemented and solved in Matlab12015b along
+with the general modiﬁcation suggested by Rosen and Jeppsson
+[20].</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>过程数学模型，不是宏基因组分析。</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04092/fulltext/fulltext__published__187b868956ed3e07.pdf</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>187b868956ed3e07456eb08dd523d037ffb342e17033c71274fc2618ce78b4ef</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1 Model implementation and ADM1 modification</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="90" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>R04111-E01</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>R04111</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Gas permeation (the con-
+centration of hydrogen sulfide, oxygen, nitrogen, methane
+and carbon dioxide) through the membrane was measured in
+three configurations: bare membrane (experiments with a dry
+membrane), wet membrane (the membrane was submerged
+for 30 minutes in tap water before the experiment), and bio-
+membrane (the membrane was submerged for 30 minutes in
+mesophilic sludge for biofilm attachment before the experi-
+ment).</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>三膜配置比较气体通透性，无测序。</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04111/fulltext/fulltext__published__4e16411a50808da0.pdf</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>4e16411a50808da04b9eee3d3090cc587e0222f008c01b6a99b9e26589e20caa</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>2.1 Experimental set-up: lab-scale biomembrane unit</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="90" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>R04111-E02</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>R04111</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Analyses of COD,
+pH, VFA, solids, ammonia and sulfide were performed
+according to the Standard Methods (American Public Health
+Association, 1997).</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>完整分析方法为气体、水质、元素和XRF检测，非目标测序。</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04111/fulltext/fulltext__published__4e16411a50808da0.pdf</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>4e16411a50808da04b9eee3d3090cc587e0222f008c01b6a99b9e26589e20caa</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="90" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>R04177-E01</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>R04177</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>The COD and VFA concentrations were determined by 
+employing standard methods [12]. The DO was determined 
+with a Model 55 analyzer (YSI, USA) [13], whereas the biogas 
+production was determined by using the liquid displacement 
+technique [14]. The granular sludge particle-size distribution 
+was determined via the wet-screening method [15].</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>完整分析方法限定为理化、气量和粒径；不是DNA/RNA测序。</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04177/fulltext/fulltext__published__09b0de58af2ff1e6.pdf</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>09b0de58af2ff1e679e24cecf4a4a617fa2a0e539dc66351e2edb4076d2e7b72</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Items and methods of analysis</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="90" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>R04324-E01</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>R04324</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Both VFAs and ethanol were measured via
+high-performance liquid chromatography following the method re-
+ported by Yu et al. (2018).</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>功能/代谢物测量为HPLC，不是宏转录组。</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04324/fulltext/fulltext__published__1590c60360a46d39.pdf</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>1590c60360a46d392999a24ef4147ea6023717eb6f845a839d69b8dccaf6f4a8</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="90" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>R04324-E02</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>R04324</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>The methane contents were
+analysed via gas chromatography (GC-2010, Shimadzu International
+Trading Co., Ltd., Shanghai, China) equipped with a CP-Porabond Q
+column and a thermal conductivity detector.</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>完整方法为理化、产气及数学拟合，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04324/fulltext/fulltext__published__1590c60360a46d39.pdf</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>1590c60360a46d392999a24ef4147ea6023717eb6f845a839d69b8dccaf6f4a8</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="90" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>R04477-E01</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>R04477</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>All gas and wastewater analyses were performed on samples obtained from the digesters
+immediately prior to weekly feedings of poultry litter. Wastewater and solids analyses were performed</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>分析对象为气体、废水和固体；其后PDF4页续为标准方法与GC。</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04477/fulltext/fulltext__published__dc52821c42ce8476.pdf</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>dc52821c42ce84765057b8c1aba951d40c1eb338df462600a5aaadc8659d073d</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>[3, 4]</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analyses</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="90" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>R04477-E02</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>R04477</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Gas chromatographic analyses were performed as previously described [18] and statistical
+analyses were performed using SAS version 9.3 (SAS Institute, Cary, NC, USA).</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>完整分析章节为GC/统计，无建库或测序。</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04477/fulltext/fulltext__published__dc52821c42ce8476.pdf</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>dc52821c42ce84765057b8c1aba951d40c1eb338df462600a5aaadc8659d073d</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analyses</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="90" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>R04510-E01</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>R04510</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>The following chemical parameters were determined: soluble chemical oxygen demand 
+(CODs), total volatile solids (TVS), volatile suspended solids (VSS), alkalinity, sulfate, 
+sulfide and pH. All these parameters were analyzed according to APHA Standard Methods. 
+31</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>完整方法中分析项目为COD/固体/碱度/硫酸盐/硫化物/pH，无核酸或测序。</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04510/fulltext/fulltext__version_unverified__c4520ca79e301bb6.pdf</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>[7]</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Materials and methods – Chemical and statistical analyses</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="90" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>R04510-E02</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>R04510</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Optima 3000 ICP according to standard protocols based on official methods of the US-
+EPA. 33</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>接前页金属浓度检测为ICP，非序列技术。</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04510/fulltext/fulltext__version_unverified__c4520ca79e301bb6.pdf</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>[7, 8]</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Chemical and statistical analyses</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L111"/>
+  <autoFilter ref="A1:L158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50432,7 +54092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -53967,13 +57627,29 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr"/>
-      <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="inlineStr"/>
+          <t>仅保留历史问题与解决证据；不再计唯一关联待核实。</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>已解决</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>DOCX题名细微措辞差异，两位作者及CSIR-IICT机构一致；内容为本文biohythane图与反应式。原件及原清单字段保留。</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>R03475-E03</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="60" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -54737,8 +58413,116 @@
       <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr"/>
     </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>R03737</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>非目标序列编号（比对参考）</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03737/fulltext/fulltext__published__a01cf0612b37cb24.pdf</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>a01cf0612b37cb24266d34adcc648fcab6d66b40737d0f275e61dd9c4e3f4de0</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>[7]</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>KM527239; LK023322</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>KM527239; LK023322</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>单条核酸参考记录（非项目）</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>GenBank</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/KM527239 ; https://www.ncbi.nlm.nih.gov/nuccore/LK023322</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>KM527239 / LK023322，正文PDF7页真菌18S克隆鉴定，99%相似性；不作为本研究宏基因组/宏转录组项目或独立数据集。</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>留存线索，不计目标项目；未开展非目标数据库核验</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>R03900</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>正文提及SI但当前无原件</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R03900/fulltext/fulltext__published__254540c6f1846351.pdf</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>254540c6f1846351c168ff143b23a9032a3d0d2ea7dfa538972b5679d47155fc</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>PDF7页电子SI说明为颗粒化SEM图片；未下载。正文明确16S扩增子。</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>保留SI缺口；不作为目标测序候选或原始reads</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P104"/>
+  <autoFilter ref="A1:P106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54749,7 +58533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -54835,7 +58619,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -54851,7 +58635,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -54999,7 +58783,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -55047,7 +58831,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -55064,7 +58848,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>R03164</t>
+          <t>R04646</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -55744,8 +59528,226 @@
       </c>
       <c r="D59" s="2" t="inlineStr"/>
     </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>R03164, R03220, R03400, R03455, R03475, R03497, R03518, R03522, R03564, R03575, R03737, R03900, R04028, R04060, R04092, R04111, R04177, R04324, R04477, R04510</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>research_screened_count</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>pending_count</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>pending_ids</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>processed_record_count</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>target_articles</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>metagenomics_only</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>metatranscriptomics_only</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>explicit_request_articles</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D59"/>
+  <autoFilter ref="A1:D72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -55903,7 +59905,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>本轮R01727已核实为同文接受稿，剩60件暂不唯一归属；待题名/DOI/正文引用核实，不据目录分配编号。可检查现有附件，不追下载缺件。</t>
+          <t>B002的R01727已核实为同文接受稿；B004的R03475 DOCX以题名、两位作者和机构核实关联，剩59件唯一归属待核实。不据目录分配编号；其余现有附件有内容吻合者仍保留归属限制，不追下载缺件。</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
+++ b/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
@@ -19,9 +19,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛查总表'!$A$1:$AF$427</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'目标测序研究'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据项目与样本'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$158</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$P$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$P$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'口径与字段说明'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12029,22 +12029,58 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；水质、光谱/GC、Microtox及动力学</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr"/>
-      <c r="Q88" s="2" t="inlineStr"/>
-      <c r="R88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Direct Black22染料/乙醇合成废水</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.25±0.05 L/min；连续或30 min/2 h间歇</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>R1严格厌氧；R2厌氧12 h+微曝气11 h；R3间歇微曝气</t>
+        </is>
+      </c>
       <c r="S88" s="2" t="inlineStr"/>
       <c r="T88" s="2" t="inlineStr"/>
       <c r="U88" s="2" t="inlineStr"/>
-      <c r="V88" s="2" t="inlineStr"/>
-      <c r="W88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–3页）为配水、SBR运行、水质/染料光谱、GC、Microtox毒性和动力学；sequencing batch reactor是序批式反应器术语，不是测序。未报告核酸建库或目标组学。</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；方法PDF2–3页§2.1–2.4</t>
+        </is>
+      </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04646/fulltext/fulltext__published__e1d4e0f3c97d519f.pdf"]</t>
@@ -12068,13 +12104,21 @@
       <c r="AB88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>正文提及SI用于NMR纯度和动力学计算；当前无独立原件，保留缺口，不追下载。</t>
+        </is>
+      </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE88" s="2" t="inlineStr"/>
+          <t>["R04646-E01", "R04646-E02"]</t>
+        </is>
+      </c>
+      <c r="AE88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:08:59.157148+00:00</t>
+        </is>
+      </c>
       <c r="AF88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="60" customHeight="1">
@@ -12121,22 +12165,58 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；AMPTS/BMP、GC、粒径及SMA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="inlineStr"/>
-      <c r="Q89" s="2" t="inlineStr"/>
-      <c r="R89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>合成市政废水；纤维素对照</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>3/5 bar微气泡白水处理接种污泥</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>0/3/5 bar污泥；空白与纤维素对照；另有SMA实验</t>
+        </is>
+      </c>
       <c r="S89" s="2" t="inlineStr"/>
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr"/>
-      <c r="V89" s="2" t="inlineStr"/>
-      <c r="W89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>51页学位研究；完整第3章（PDF14–23页）为底物、接种、加压白水、AMPTS和GC产气、粒径与SMA；附录I–IV为TS/VS、粒径仪截图及AMPTS/SMA数值表，无目标测序。低文字页已查看原页缩略图，均为封面、装置照片、粒径或产气表。</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–51页定位；第3章PDF14–23页完整；附录PDF38–51页；低文字PDF1/23/39–48/51视觉核查</t>
+        </is>
+      </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04700/fulltext/fulltext__thesis__40ac0de29f75851c.pdf"]</t>
@@ -12160,13 +12240,21 @@
       <c r="AB89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>无独立SI；论文内附录I–IV已检查，非测序材料。</t>
+        </is>
+      </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE89" s="2" t="inlineStr"/>
+          <t>["R04700-E01", "R04700-E02"]</t>
+        </is>
+      </c>
+      <c r="AE89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:09:50.240337+00:00</t>
+        </is>
+      </c>
       <c r="AF89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="60" customHeight="1">
@@ -12321,22 +12409,58 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>细菌/古菌16S扩增子MiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr"/>
-      <c r="P91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>初沉污泥60%+剩余污泥40%</t>
+        </is>
+      </c>
       <c r="Q91" s="2" t="inlineStr"/>
       <c r="R91" s="2" t="inlineStr"/>
-      <c r="S91" s="2" t="inlineStr"/>
-      <c r="T91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S扩增子）</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>MA及Raw各1份污泥，共2份</t>
+        </is>
+      </c>
       <c r="U91" s="2" t="inlineStr"/>
-      <c r="V91" s="2" t="inlineStr"/>
-      <c r="W91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）已读：总DNA后细菌338F/806R和古菌Arch524F/958R扩增16S，纯化amplicons后MiSeq、97% OTU。酶活为ELISA；无shotgun或群落RNA测序。</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；方法PDF2–3页§2</t>
+        </is>
+      </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04786/fulltext/fulltext__published__ea18005b6cd10f40.pdf"]</t>
@@ -12360,13 +12484,21 @@
       <c r="AB91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE91" s="2" t="inlineStr"/>
+          <t>["R04786-E01"]</t>
+        </is>
+      </c>
+      <c r="AE91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:09:50.268655+00:00</t>
+        </is>
+      </c>
       <c r="AF91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="60" customHeight="1">
@@ -12417,22 +12549,58 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；农场脱硫监测及经济分析</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>奶牛粪与食物废物共消化</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>农场2顶空空气2.86 m3/h</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>农场1氧化铁/钢丝绒吸附；农场2生物微曝气脱硫</t>
+        </is>
+      </c>
       <c r="S92" s="2" t="inlineStr"/>
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr"/>
-      <c r="V92" s="2" t="inlineStr"/>
-      <c r="W92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF3–4页）为两厂装置、气体连续监测、维护成本、脱硫计算及统计；无核酸、建库、测序或组学复用。</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–13页定位；方法PDF3–4页§2</t>
+        </is>
+      </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04796/fulltext/fulltext__published__6844f12fe56c174d.pdf"]</t>
@@ -12456,13 +12624,21 @@
       <c r="AB92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE92" s="2" t="inlineStr"/>
+          <t>["R04796-E01"]</t>
+        </is>
+      </c>
+      <c r="AE92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:09:50.299325+00:00</t>
+        </is>
+      </c>
       <c r="AF92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="60" customHeight="1">
@@ -12513,22 +12689,58 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>PCR-DGGE群落指纹（非目标）</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr"/>
-      <c r="P93" s="2" t="inlineStr"/>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>乙醇合成废水及400 mg/L硫酸钠</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>0.1/0.3 mL/min；泥床内、泥床上方或顶空</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>R1先厌氧再泥床上微曝气；R2顶空/泥床微曝气</t>
+        </is>
+      </c>
       <c r="S93" s="2" t="inlineStr"/>
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr"/>
-      <c r="V93" s="2" t="inlineStr"/>
-      <c r="W93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1、2.3–2.6（PDF5–6页）为反应器、曝气策略、标准水质、PCR-DGGE及生态指数。无目标测序；PDF23低文字原页为DGGE胶图，PDF17为利益声明，已视觉核查。</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–27页定位；方法PDF5–6页§2；PDF21图注及23胶图；低文字PDF17/23原页核查</t>
+        </is>
+      </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04803/fulltext/fulltext__published__3e98d6cf0fefd5e7.pdf"]</t>
@@ -12552,13 +12764,21 @@
       <c r="AB93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>无独立SI；接受稿后部图表属于正文，DGGE胶图已核查。</t>
+        </is>
+      </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE93" s="2" t="inlineStr"/>
+          <t>["R04803-E01"]</t>
+        </is>
+      </c>
+      <c r="AE93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:09:50.328543+00:00</t>
+        </is>
+      </c>
       <c r="AF93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="60" customHeight="1">
@@ -12713,22 +12933,58 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；厌氧培养菌落计数及理化/GC</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr"/>
-      <c r="P95" s="2" t="inlineStr"/>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>棕榈油厂废水POME</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>产酸段每日注入相当工作液5%的空气，产甲烷段不曝气</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>牛粪与生物柴油废水来源接种物；产酸pH4/5</t>
+        </is>
+      </c>
       <c r="S95" s="2" t="inlineStr"/>
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr"/>
-      <c r="V95" s="2" t="inlineStr"/>
-      <c r="W95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>完整RESEARCH METHODOLOGY（PDF2–4页）包括材料、两段AD、sCOD/VFA/GC与厌氧总菌落计数CFU；未报告DNA/RNA提取、建库或测序。</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–8页定位；方法PDF2–4页</t>
+        </is>
+      </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04889/fulltext/fulltext__published__860a0532503787f8.pdf"]</t>
@@ -12752,13 +13008,21 @@
       <c r="AB95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE95" s="2" t="inlineStr"/>
+          <t>["R04889-E01", "R04889-E02"]</t>
+        </is>
+      </c>
+      <c r="AE95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:11:20.392454+00:00</t>
+        </is>
+      </c>
       <c r="AF95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="60" customHeight="1">
@@ -12809,22 +13073,66 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA及mcrA扩增子HiSeq（非目标）；宏转录组仅未来建议</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr"/>
-      <c r="P96" s="2" t="inlineStr"/>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Napier草</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>ORP控制间歇O2，1 mL/min，隔日开关</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>三次重复实验中厌氧与微曝气，ORP基线+25 mV</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>Illumina HiSeq2000（16S及mcrA靶基因）</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>三次重复各两时点，6份主分析样本；文中12个BioSample编号对应两个标记数据，未核实逐编号映射</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr"/>
-      <c r="V96" s="2" t="inlineStr"/>
-      <c r="W96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6（PDF2–3页）明确515F/806R扩增16S和mcrA3F/mcrA3R扩增mcrA后HiSeq、mothur/OTU；宏转录组在讨论为未来所需分析。DOCX补充方法为ORP、化学和热力学，不含额外shotgun/RNA建库。</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；方法PDF2–3页§2；PDF7–8页宏转录组建议；DOCX全部588段落/表格</t>
+        </is>
+      </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04899/fulltext/fulltext__published__92f0b2f1ad01522c.pdf"]</t>
@@ -12848,13 +13156,21 @@
       <c r="AB96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>题名/作者核实DOCX已读；补充ORP/化学/热力学，Table S2为扩增子OTU丰度，其余运行/理化表图，无目标测序。</t>
+        </is>
+      </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE96" s="2" t="inlineStr"/>
+          <t>["R04899-E01", "R04899-E02", "R04899-E03", "R04899-E04"]</t>
+        </is>
+      </c>
+      <c r="AE96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:11:20.426341+00:00</t>
+        </is>
+      </c>
       <c r="AF96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="60" customHeight="1">
@@ -12905,22 +13221,58 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；发酵产气与动力学模型</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr"/>
-      <c r="P97" s="2" t="inlineStr"/>
-      <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>模拟餐厨废物和污泥</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>空气0/5/10/15/20 mL组</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>五组厌氧/微曝气发酵，37°C、50天</t>
+        </is>
+      </c>
       <c r="S97" s="2" t="inlineStr"/>
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr"/>
-      <c r="V97" s="2" t="inlineStr"/>
-      <c r="W97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods及Model establishment（PDF2–6页）为模拟食物废物批次发酵、每日产气、Logistic/Gompertz/一阶模型拟合，无核酸、测序或组学复用。</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–13页定位；实验方法PDF2–3页；模型PDF3–6页</t>
+        </is>
+      </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04912/fulltext/fulltext__published__ba09ba8854601318.pdf"]</t>
@@ -12944,13 +13296,21 @@
       <c r="AB97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE97" s="2" t="inlineStr"/>
+          <t>["R04912-E01"]</t>
+        </is>
+      </c>
+      <c r="AE97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:11:20.456203+00:00</t>
+        </is>
+      </c>
       <c r="AF97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="60" customHeight="1">
@@ -13001,22 +13361,58 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；全规模脱硫运行监测</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr"/>
-      <c r="P98" s="2" t="inlineStr"/>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>高固体污泥90%与食物废物相关物10%共消化</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>三消化罐顶空空气，剩余O2设定0.2–2.0%</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>三台55°C全规模消化罐81周不同供氧阶段</t>
+        </is>
+      </c>
       <c r="S98" s="2" t="inlineStr"/>
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr"/>
-      <c r="V98" s="2" t="inlineStr"/>
-      <c r="W98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.3（PDF2页）为厂站、运行条件、气体流量/组分、固体/氨氮/碱度；未报告核酸或测序。</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–6页定位；方法PDF2页§2</t>
+        </is>
+      </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04922/fulltext/fulltext__published__d4f609c42961a5d2.pdf"]</t>
@@ -13040,13 +13436,21 @@
       <c r="AB98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE98" s="2" t="inlineStr"/>
+          <t>["R04922-E01"]</t>
+        </is>
+      </c>
+      <c r="AE98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:11:20.485837+00:00</t>
+        </is>
+      </c>
       <c r="AF98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="60" customHeight="1">
@@ -13097,22 +13501,58 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；UASB运行、VS/VFA和产气模型</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>酒糟废水vinasse，牛粪接种</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>每日取样后注气；DI无气/DII低气/DIII高气</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>三档空气投加及一阶降解模型</t>
+        </is>
+      </c>
       <c r="S99" s="2" t="inlineStr"/>
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr"/>
-      <c r="V99" s="2" t="inlineStr"/>
-      <c r="W99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.2（PDF4–5页）为接种活化、UASB再循环、VS/VFA/排水量气；其余定量产酸模型，不含DNA/RNA建库或测序。</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；方法PDF4–5页§2</t>
+        </is>
+      </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
           <t>["original_files/R04928/fulltext/fulltext__published__9d47028c02204ac0.pdf"]</t>
@@ -13136,13 +13576,21 @@
       <c r="AB99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE99" s="2" t="inlineStr"/>
+          <t>["R04928-E01"]</t>
+        </is>
+      </c>
+      <c r="AE99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:11:20.514509+00:00</t>
+        </is>
+      </c>
       <c r="AF99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="60" customHeight="1">
@@ -13293,22 +13741,58 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>16S V3–V4扩增子MiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O101" s="2" t="inlineStr"/>
-      <c r="P101" s="2" t="inlineStr"/>
-      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>2-丁烯醛生产废水</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>回流出水曝气，DO0.2–0.5 mg/L</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr"/>
-      <c r="S101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq</t>
+        </is>
+      </c>
       <c r="T101" s="2" t="inlineStr"/>
       <c r="U101" s="2" t="inlineStr"/>
-      <c r="V101" s="2" t="inlineStr"/>
-      <c r="W101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6（PDF2–3页）：EPS/核酸含量比色、EEM/PARAFAC及16S V3–V4 340F/805R扩增子测序；核酸定量不等同宏基因组。DOCX为装置/PCA、GCMS化合物表和16S多样性表，无额外目标流程。</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；方法PDF2–3页；DOCX全部349段落及表S1/S2</t>
+        </is>
+      </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05065/fulltext/fulltext__published__239adeaf9a5df55a.pdf"]</t>
@@ -13332,13 +13816,21 @@
       <c r="AB101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>题名/作者匹配DOCX全部文本和表格已读；无目标测序或编号。</t>
+        </is>
+      </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE101" s="2" t="inlineStr"/>
+          <t>["R05065-E01", "R05065-E02"]</t>
+        </is>
+      </c>
+      <c r="AE101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:12:59.723435+00:00</t>
+        </is>
+      </c>
       <c r="AF101" s="2" t="inlineStr"/>
     </row>
     <row r="102" ht="60" customHeight="1">
@@ -13493,22 +13985,62 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr"/>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA扩增子HiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O103" s="2" t="inlineStr"/>
-      <c r="P103" s="2" t="inlineStr"/>
-      <c r="Q103" s="2" t="inlineStr"/>
-      <c r="R103" s="2" t="inlineStr"/>
-      <c r="S103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>葡萄糖/三溴苯酚TBP合成废水</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>回流曝气；DO0.11/0.68/1.51 mg/L等阶段</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>R1活性污泥；R2加磁铁矿</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>Illumina HiSeq（16S）</t>
+        </is>
+      </c>
       <c r="T103" s="2" t="inlineStr"/>
       <c r="U103" s="2" t="inlineStr"/>
-      <c r="V103" s="2" t="inlineStr"/>
-      <c r="W103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and Methods（PDF2–3页）：物化/酶活/显微及明确16S 515F/806R PCR、HiSeq、97% OTU/QIIME。DOCX仅种泥理化表及COD/稀释曲线/铁效应图，无额外目标测序。</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；方法PDF2–3页；DOCX全部63段落</t>
+        </is>
+      </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05173/fulltext/fulltext__published__dedf2d646e952ba0.pdf"]</t>
@@ -13532,13 +14064,21 @@
       <c r="AB103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>DOCX缺独立题名/DOI，目录内容相符但保留唯一归属待核实；无可归属目标编号。</t>
+        </is>
+      </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE103" s="2" t="inlineStr"/>
+          <t>["R05173-E01", "R05173-E02", "R05173-E03"]</t>
+        </is>
+      </c>
+      <c r="AE103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:12:59.757033+00:00</t>
+        </is>
+      </c>
       <c r="AF103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="60" customHeight="1">
@@ -13693,22 +14233,58 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr"/>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；LPMO酶制剂、GC与HPAEC/NMR</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O105" s="2" t="inlineStr"/>
-      <c r="P105" s="2" t="inlineStr"/>
-      <c r="Q105" s="2" t="inlineStr"/>
-      <c r="R105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Avicel、云杉/桦木及富木质素残渣</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>厌氧/空气顶空及H2O2补加比较</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>酶/煮沸酶、NcLPMO9C、Celluclast及无酶/接种物对照</t>
+        </is>
+      </c>
       <c r="S105" s="2" t="inlineStr"/>
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr"/>
-      <c r="V105" s="2" t="inlineStr"/>
-      <c r="W105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>完整Methods（PDF10–12页）为底物/成分、酶制剂、接种物、产气GC和氧化产物HPAEC；NcLPMO9C表达纯化非群落RNA测序。现有DOCX为色谱/甲烷曲线。PDF13泛指additional data可索取，但无目标测序，不计相关reads可索取候选。</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–14页定位；Methods PDF10–12页；数据声明PDF13页；DOCX全部72段落</t>
+        </is>
+      </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05213/fulltext/fulltext__published__bcab84a15ce93062.pdf"]</t>
@@ -13732,13 +14308,21 @@
       <c r="AB105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>官方历史关联DOCX题名作者相符；全部图注为色谱与产气。</t>
+        </is>
+      </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE105" s="2" t="inlineStr"/>
+          <t>["R05213-E01", "R05213-E02", "R05213-E03", "R05213-E04"]</t>
+        </is>
+      </c>
+      <c r="AE105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:12:59.794409+00:00</t>
+        </is>
+      </c>
       <c r="AF105" s="2" t="inlineStr"/>
     </row>
     <row r="106" ht="60" customHeight="1">
@@ -13789,22 +14373,66 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>细菌/古菌16S扩增子MiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O106" s="2" t="inlineStr"/>
-      <c r="P106" s="2" t="inlineStr"/>
-      <c r="Q106" s="2" t="inlineStr"/>
-      <c r="R106" s="2" t="inlineStr"/>
-      <c r="S106" s="2" t="inlineStr"/>
-      <c r="T106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>鸡粪</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>1.4/2.8/4.2 mL O2/gVS，顶空载体连续/脉冲供气</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>R1厌氧；R2分四供气阶段，顶空尼龙载体</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S）</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>第120天R1/R2液相及R2载体；每类两份采样</t>
+        </is>
+      </c>
       <c r="U106" s="2" t="inlineStr"/>
-      <c r="V106" s="2" t="inlineStr"/>
-      <c r="W106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–4页）：化学/统计及338F/806R细菌、524F/958R古菌16S PCR、MiSeq、97% OTU。metagenome只出现在末页参考文献，不是本研究方法。</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；方法PDF2–4页§2；参考文献PDF10页</t>
+        </is>
+      </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05319/fulltext/fulltext__published__865dcb7f90757119.pdf"]</t>
@@ -13828,13 +14456,21 @@
       <c r="AB106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE106" s="2" t="inlineStr"/>
+          <t>["R05319-E01", "R05319-E02"]</t>
+        </is>
+      </c>
+      <c r="AE106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:13:19.954706+00:00</t>
+        </is>
+      </c>
       <c r="AF106" s="2" t="inlineStr"/>
     </row>
     <row r="107" ht="60" customHeight="1">
@@ -13885,22 +14521,62 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
-      <c r="P107" s="2" t="inlineStr"/>
-      <c r="Q107" s="2" t="inlineStr"/>
-      <c r="R107" s="2" t="inlineStr"/>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>待确认：菌群组成已报告但测序方法未说明</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>未说明；仅报告细菌门/真菌纲，不能确认是否目标测序</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>7 证据不足，待确认</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>正文§2.1报告16个细菌门和7个真菌纲，但完整§2.1–2.6未交代核酸提取、靶标/引物、建库/测序或数据来源。现有匹配题名DOCX只有显微、FTIR和XRD图，无法区分扩增子、目标组学或既有分析。不能仅按菌群分类层级判断阴性。</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>油菜秸秆及两相消化水解产酸发酵液</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>0/20/60/120 mL O2/gVS/d，预处理10天</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>发酵液、灭菌过滤液和去离子水对照</t>
+        </is>
+      </c>
       <c r="S107" s="2" t="inlineStr"/>
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr"/>
-      <c r="V107" s="2" t="inlineStr"/>
-      <c r="W107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>已完整阅读§2.1–2.6（PDF2–3页）及现有DOCX，主体为生物预处理、理化/GC/SEM/FTIR/XRD。预处理液菌群组成的分析来源和类型不明，保留待确认；全文及附件未定位编号或相关测序数据声明。</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–7页定位；方法PDF2–3页§2；DOCX全部22段落</t>
+        </is>
+      </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05396/fulltext/fulltext__published__0a746b3ef69be3a5.pdf"]</t>
@@ -13924,14 +14600,22 @@
       <c r="AB107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>题名/作者核实DOCX仅菌丝/SEM/FTIR/XRD图，未补充菌群方法/编号。</t>
+        </is>
+      </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["R05396-E01", "R05396-E02"]</t>
         </is>
       </c>
       <c r="AE107" s="2" t="inlineStr"/>
-      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:13:19.987967+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="60" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -13981,22 +14665,58 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；菌培养/显微/Gram染色及工程分析</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O108" s="2" t="inlineStr"/>
-      <c r="P108" s="2" t="inlineStr"/>
-      <c r="Q108" s="2" t="inlineStr"/>
-      <c r="R108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>猪粪沼气</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>每日顶空注入约2.08 L空气；1%储气袋体积</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>二重复微曝气储气袋与二重复氧化铁过滤</t>
+        </is>
+      </c>
       <c r="S108" s="2" t="inlineStr"/>
       <c r="T108" s="2" t="inlineStr"/>
       <c r="U108" s="2" t="inlineStr"/>
-      <c r="V108" s="2" t="inlineStr"/>
-      <c r="W108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF4–6页）为消化/微曝气/铁滤、SOB培养和Gram染色、气体/元素和统计；分离纯培养没有基因组或群落组学测序。</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–14页定位；方法PDF4–6页§2</t>
+        </is>
+      </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05472/fulltext/fulltext__published__a81227cda8f65dc0.pdf"]</t>
@@ -14020,13 +14740,21 @@
       <c r="AB108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE108" s="2" t="inlineStr"/>
+          <t>["R05472-E01"]</t>
+        </is>
+      </c>
+      <c r="AE108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:14:31.726362+00:00</t>
+        </is>
+      </c>
       <c r="AF108" s="2" t="inlineStr"/>
     </row>
     <row r="109" ht="60" customHeight="1">
@@ -14177,22 +14905,62 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>16S扩增子MiSeq + PICRUSt功能预测（非目标）</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O110" s="2" t="inlineStr"/>
-      <c r="P110" s="2" t="inlineStr"/>
-      <c r="Q110" s="2" t="inlineStr"/>
-      <c r="R110" s="2" t="inlineStr"/>
-      <c r="S110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>厕所黑水</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>0/5/10/50/150 mg O2/L反应器/周期</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>五个ASBR梯度氧，HRT5/4/3/2天</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S）</t>
+        </is>
+      </c>
       <c r="T110" s="2" t="inlineStr"/>
       <c r="U110" s="2" t="inlineStr"/>
-      <c r="V110" s="2" t="inlineStr"/>
-      <c r="W110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–3页）明确515F/806R扩增16S、MiSeq、QIIME2/DADA2，再用PICRUSt预测metagenome/functions；未实际shotgun/RNA测序。现有DOCX为黑水指标和pH/VFA/EEM图。</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–8页定位；方法PDF2–3页；预测说明PDF5–6页；DOCX全部42段落</t>
+        </is>
+      </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05511/fulltext/fulltext__published__f020eb6189063184.pdf"]</t>
@@ -14216,13 +14984,21 @@
       <c r="AB110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>题名/作者匹配SI仅1表3图，无额外组学流程或编号。</t>
+        </is>
+      </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE110" s="2" t="inlineStr"/>
+          <t>["R05511-E01", "R05511-E02", "R05511-E03"]</t>
+        </is>
+      </c>
+      <c r="AE110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:14:31.762956+00:00</t>
+        </is>
+      </c>
       <c r="AF110" s="2" t="inlineStr"/>
     </row>
     <row r="111" ht="60" customHeight="1">
@@ -14273,22 +15049,54 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；流式细胞术、ATP及理化</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O111" s="2" t="inlineStr"/>
-      <c r="P111" s="2" t="inlineStr"/>
-      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>70%浓缩生物污泥+30%初沉污泥</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>0.1–0.5 vvm预曝气，优化0.2 vvm、40h</t>
+        </is>
+      </c>
       <c r="R111" s="2" t="inlineStr"/>
       <c r="S111" s="2" t="inlineStr"/>
       <c r="T111" s="2" t="inlineStr"/>
       <c r="U111" s="2" t="inlineStr"/>
-      <c r="V111" s="2" t="inlineStr"/>
-      <c r="W111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4.3（PDF2–4页）为预处理/AD反应器、Annexin/PI流式细胞生死染色、ATP发光及标准水质/GC，非宏转录组或宏基因组。</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页定位；方法PDF2–4页§2</t>
+        </is>
+      </c>
       <c r="X111" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05542/fulltext/fulltext__published__735560cdb2769e25.pdf"]</t>
@@ -14312,13 +15120,21 @@
       <c r="AB111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE111" s="2" t="inlineStr"/>
+          <t>["R05542-E01", "R05542-E02"]</t>
+        </is>
+      </c>
+      <c r="AE111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:14:31.795500+00:00</t>
+        </is>
+      </c>
       <c r="AF111" s="2" t="inlineStr"/>
     </row>
     <row r="112" ht="60" customHeight="1">
@@ -14369,22 +15185,54 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；产气、水质和数学模型</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" s="2" t="inlineStr"/>
-      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>餐厨废物</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>0/5/10/15/20 mL氧</t>
+        </is>
+      </c>
       <c r="R112" s="2" t="inlineStr"/>
       <c r="S112" s="2" t="inlineStr"/>
       <c r="T112" s="2" t="inlineStr"/>
       <c r="U112" s="2" t="inlineStr"/>
-      <c r="V112" s="2" t="inlineStr"/>
-      <c r="W112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods（PDF2页）及Table2（PDF3页）为SBR发酵、产气、pH、COD、氨氮；sequencing batch指序批反应器，不是测序。未报告组学。</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–7页定位；方法PDF2页；Table2 PDF3页</t>
+        </is>
+      </c>
       <c r="X112" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05543/fulltext/fulltext__published__b9b6c6f484001832.pdf"]</t>
@@ -14408,13 +15256,21 @@
       <c r="AB112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE112" s="2" t="inlineStr"/>
+          <t>["R05543-E01"]</t>
+        </is>
+      </c>
+      <c r="AE112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:14:31.837445+00:00</t>
+        </is>
+      </c>
       <c r="AF112" s="2" t="inlineStr"/>
     </row>
     <row r="113" ht="60" customHeight="1">
@@ -14465,22 +15321,58 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；消化稳定性及理化分析</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
       <c r="O113" s="2" t="inlineStr"/>
-      <c r="P113" s="2" t="inlineStr"/>
-      <c r="Q113" s="2" t="inlineStr"/>
-      <c r="R113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>猪粪高固体AD</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>本研究纳米气泡水为CO2制备（原范围分类保留）</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>3/6/8/10%TS，NBW与去离子水对照</t>
+        </is>
+      </c>
       <c r="S113" s="2" t="inlineStr"/>
       <c r="T113" s="2" t="inlineStr"/>
       <c r="U113" s="2" t="inlineStr"/>
-      <c r="V113" s="2" t="inlineStr"/>
-      <c r="W113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–3页）为批次AD、CO2纳米气泡水、产气/固体/碱度/氨/VFA/蛋白糖和统计，无DNA/RNA建库或测序。不因气体为CO2改原研究范围。</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；方法PDF2–3页§2</t>
+        </is>
+      </c>
       <c r="X113" s="2" t="inlineStr">
         <is>
           <t>["original_files/R05544/fulltext/fulltext__published__24c76324a7cd3191.pdf"]</t>
@@ -14504,13 +15396,21 @@
       <c r="AB113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE113" s="2" t="inlineStr"/>
+          <t>["R05544-E01", "R05544-E02"]</t>
+        </is>
+      </c>
+      <c r="AE113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:14:50.414176+00:00</t>
+        </is>
+      </c>
       <c r="AF113" s="2" t="inlineStr"/>
     </row>
     <row r="114" ht="60" customHeight="1">
@@ -45329,7 +46229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L158"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -54080,8 +54980,2259 @@
         </is>
       </c>
     </row>
+    <row r="159" ht="90" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>R04646-E01</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>R04646</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Samples
+ taken
+ from
+ the
+ outlet
+ of
+ the
+ reactors
+ at
+ the
+ end
+ of
+the
+ cycle
+ time
+ were
+ analyzed
+ three
+ times
+ a
+ week
+ by
+ measuring
+pH,
+ alkalinity,
+ oxidation-reduction
+ potential
+ (ORP),
+ dissolved
+oxygen
+ (DO),
+ salinity,
+ COD,
+ DB22
+ concentration,
+ and
+ aromatic
+amines
+ (qualitatively).</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>完整方法为水质、染料/芳香胺光谱及GC，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04646/fulltext/fulltext__published__e1d4e0f3c97d519f.pdf</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>e1d4e0f3c97d519f1a419d98a6493eec88f5ce98834b86c2c0831c2c96908766</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical procedure</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="90" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>R04646-E02</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>R04646</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Acute
+ ecotoxicity
+ of
+ the
+ inﬂuent
+ and
+ efﬂuent
+ of
+ each
+ reac-
+tor
+ was evaluated
+ at
+ the
+ end
+ of
+ the
+ operational
+ period
+ by
+Microtox® (Microtox
+ Model
+ 500
+ analyzer,
+ Strategic
+ Diagnos-
+tics,
+ Inc.
+ SDIX,
+ Newark,
+ DE,
+ USA),
+ applying
+ the
+ bioluminescent
+bacterium
+ Vibrio
+ ﬁscheri
+ as
+ the
+ toxicity
+ indicator
+ (incubation
+time
+ of
+ 15
+ min).</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Microtox为生物发光毒性试验，不是组学测序。</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04646/fulltext/fulltext__published__e1d4e0f3c97d519f.pdf</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>e1d4e0f3c97d519f1a419d98a6493eec88f5ce98834b86c2c0831c2c96908766</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical procedure</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="90" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>R04700-E01</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>R04700</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Next, bio-methane potential (BMP) test, gas chromatography (GC)
+and particle size distribution analysis were carried out to estimate the methane potential
+and biogas composition of the aerated and non-aerated sludge.</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>完整方法为BMP、GC与粒径分析，无核酸/建库流程。</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04700/fulltext/fulltext__thesis__40ac0de29f75851c.pdf</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>[14]</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>3 Materials and Methodology</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="90" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>R04700-E02</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>R04700</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>The 0 bar, 5 bar aerated and 5 bar supernatant samples were tested to analyze the effect
+of aeration on particle size distribution. The Bluewave – Particle Size Analyzer (PSA) from
+Microtrac was used for this analysis. The procedure followed was based on the Bulewave
+particle size analyzer user manual (Microtrac, 2019).</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>粒径检测仪器，不是微生物组测序。</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04700/fulltext/fulltext__thesis__40ac0de29f75851c.pdf</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>[22]</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>3.5 Particle Size Distribution</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="90" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>R04786-E01</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>R04786</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA genes fragments were
+ampliﬁed from the obtained DNA using a primer set, 338F (5′-ACTCC
+TACGGGAGGCAGCAG-3′)
+and
+806R
+(5-’GGACTACHVGGGTWTCT-
+AAT-3′) for bacteria, and Arch524F (5-’TG YCAGCCGCCGCGGTAA-3′)
+and Arch958R (5-′YCCGGCGTTGAVTCCAATT-3′) for archaea. Puriﬁed
+amplicons were pooled in equimolar, and paired-end sequenced on an
+Illumina-MiSeq platform. Then 16S rRNA sequences were clustered into
+operational taxonomic units by setting a 3% distance limit.</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>靶基因/引物与amplicon池化明确，非宏基因组。</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04786/fulltext/fulltext__published__ea18005b6cd10f40.pdf</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>ea18005b6cd10f402de201443be02098d554b7564b6d6aa3cf6713b5c861946c</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>2.4.1 Bacterial and archaeal community</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="90" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>R04796-E01</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>R04796</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Untreated and treated biogas were analyzed to detect daily and
+seasonal diﬀerences using two portable continuous biogas testing and monitoring systems (Siemens
+Model #7MB2337-3CR13-5DR1, Siemens AG, Munich, Germany) for CH4 (0% to 100%), CO2 (0%
+to 100%), O2 (0% to 100%), and H2S (0–5000 ppm), with a Campbell Scientiﬁc CR1000 data logger
+and acquisition system, and gas meters (Model #9500, Thermal Instrument Co, Trevose, PA, USA;
+Model #FT2, Fox Thermal, Marina, CA, USA) and assembled as described in Shelford et al. 2019 [4].</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>测量为CH4/CO2/O2/H2S传感及气量，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04796/fulltext/fulltext__published__6844f12fe56c174d.pdf</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>6844f12fe56c174d2250e0a88bba570a3c94fd37dec91d66d805c2cec1c2c013</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Performance Monitoring and Cost Information</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="90" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>R04803-E01</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>R04803</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Bacterial and archaeal community structure was analyzed by PCR-
+DGGE (Ploymerase Chain Reaction Denaturing Gradient Gel Electrophoresis) 
+according to [9]. The obtained archaeal and bacterial DGGE gels were analyzed in order 
+to calculate the following ecological parameters: evenness/functional organization (Fo), 
+ranged weighted richness (Rr) and Shannon diversity index (H) according to [22].</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>微生物结构采用PCR-DGGE及其指纹指数，不是宏基因组/宏转录组。</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04803/fulltext/fulltext__published__3e98d6cf0fefd5e7.pdf</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>3e98d6cf0fefd5e7daae2600b11ecc00cdff35ca4f4dfd462e4c7ed25bb3c6c6</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>[6]</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="90" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>R04889-E01</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>R04889</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Measured variables reported in this 
+study included pH, sCOD, volatile fatty acid 
+(VFA), methane production, and anaerobic total 
+plate count.</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>菌量以培养平板计数，非宏基因组/宏转录组。</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04889/fulltext/fulltext__published__860a0532503787f8.pdf</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>860a0532503787f8bb84a599bdbf923f690615b05121c8a78c21249f8de911cb</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>RESEARCH METHODOLOGY – Anaerobic digestion</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="90" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>R04889-E02</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>R04889</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Analysis of sCOD and VFA were 
+conducted 
+by 
+following 
+APHA 
+procedures 
+(Clesceri, et.al., 2005). Methane concentration was 
+measured using Gas Chromatography Shimadzu 
+GC 8A.</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>完整检测为水质、VFA和产气GC。</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04889/fulltext/fulltext__published__860a0532503787f8.pdf</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>860a0532503787f8bb84a599bdbf923f690615b05121c8a78c21249f8de911cb</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>RESEARCH METHODOLOGY – Analysis</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="90" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>R04899-E01</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>R04899</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>The bacterial and methanogenic communities were investigated
+by targeting the 16S rRNA gene using 515F/806R primers and the
+mcrA gene using mcrA3F/mcrA3R primers, respectively (Caporaso
+et al., 2012; Luton et al., 2002).</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>靶标为16S及mcrA，非群落DNA随机建库。</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04899/fulltext/fulltext__published__92f0b2f1ad01522c.pdf</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>92f0b2f1ad01522ccc4e76595e3cd022e18db61eb7367bec31eeb097881b8329</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial analyses</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="90" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>R04899-E02</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>R04899</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>非目标编号排除</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>The raw sequence reads were
+deposited in the NCBI Sequence Read Archive (SRA; http://www.
+ncbi.nlm.nih.gov/sra) under accession numbers SAMN12752316 to
+SAMN12752321 and SAMN12752323 to SAMN12752328.</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>文中给出BioSample编号，属于上述标记基因数据，不计为目标组学项目。</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04899/fulltext/fulltext__published__92f0b2f1ad01522c.pdf</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>92f0b2f1ad01522ccc4e76595e3cd022e18db61eb7367bec31eeb097881b8329</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial analyses</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="90" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>R04899-E03</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>R04899</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>术语命中排除</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>How-
+ever, further metatranscriptomic analyses are needed to evaluate</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>明确未来需要宏转录组，不能视作实际开展。</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04899/fulltext/fulltext__published__92f0b2f1ad01522c.pdf</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>92f0b2f1ad01522ccc4e76595e3cd022e18db61eb7367bec31eeb097881b8329</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>[7]</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>4 Discussion</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="90" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>R04899-E04</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>R04899</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting materials and methods: </t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>补充方法列表为ORP/化学/热力学，现有附件无额外目标测序流程。</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04899/supplementary/supplementary__93e7e6da6f9fc16c.docx</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>93e7e6da6f9fc16c9535a4cfd721b7da589326e3314fb7eee286572c71da81eb</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落20–23、40–80；Table S2段落109–377</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="90" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>R04912-E01</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>R04912</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Five parallel groups were 
+set up. Group 1 was used as a control and it was carried out as a standard anaerobic 
+fermentation. Groups 2–5 were experimental groups, and 5 ml, 10 ml, 15 ml, and 20 ml 
+of air were respectively inflated to create different microaerobic conditions. The biogas 
+generation in each group was measured once a day, and the total amount of biogas 
+generation in each group was also calculated.</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>实验测量每日沼气体积，非测序；微生物生长模型不等同组学。</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04912/fulltext/fulltext__published__ba09ba8854601318.pdf</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>ba09ba8854601318e3af61c59c8980e8022ec2a668e0c1f925cc16502a53081b</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Experimental methods</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="90" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>R04922-E01</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>R04922</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Biogas composition (CH4, CO2,
+H2S and O2) in the three digesters and upstream of the CHP unit was
+monitored six times/day using an Optima 7 portable biogas analyzer
+(MRU GmbH, Germany).</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>测量气体组分，完整方法无目标测序。</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04922/fulltext/fulltext__published__d4f609c42961a5d2.pdf</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>d4f609c42961a5d25218af73e99fcc5ae1f02a5018337ec964fe076fc1addcbf</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Monitoring and analytical methods</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="90" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>R04928-E01</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>R04928</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Once daily, 300 ml samples were taken for VS and 
+VFA analysis through sampling valve. The VS and VFA 
+analysis was done in 3 series per day per digester and 
+followed by APHA (American Public Health Association - 
+APHA, 2005).</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>检测VS/VFA及沼气体积，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04928/fulltext/fulltext__published__9d47028c02204ac0.pdf</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>9d47028c02204ac08f73849bdf73af55c1e235aa3593b2b281d139b85d58607f</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Experimental</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="90" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>R05065-E01</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>R05065</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>The V3-V4 regions of the 16 s rDNA genes were am-
+plified with 340 F (CCTACGGGNBGCASCAG) and 805R (GACTACNV-
+GGGTATCTAATCC). All polymerase chain reaction (PCR) reaction
+mixture was purified with the MinElute Gel Extraction Kit (Qiagen,
+Germany). The Invitrogen™-Qubit fluorometer quantitative system
+(California, USA) was used to quantity the amplicons. Then high-
+throughput sequencing of 16S DNA amplicons were sequenced with the
+Illumina MiSeq platform at SinoGenoMax Co., Ltd (Beijing, China).</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>明确扩增16S并测amplicons，非宏基因组。</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05065/fulltext/fulltext__published__239adeaf9a5df55a.pdf</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>239adeaf9a5df55a383ba454cf2811563b710d89e446a0af02062140664e382e</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Microbial structure analysis</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="90" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>R05065-E02</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>R05065</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Table S2 Community richness and diversity indices of different samples</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>补充表是16S群落丰富度/多样性，不是shotgun库。</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05065/supplementary/supplementary__138834a73b710b94.docx</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>138834a73b710b94f194521b56815619a34161b6ccdb225f771fb58e8ede57bb</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>DOCX Table S2，段落290–346</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="90" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>R05173-E01</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>R05173</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA
+genes were ampliﬁed using the bacterial universal primers (515F
+and 806R) with speciﬁc barcode.</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>靶基因引物明确，非shotgun。</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05173/fulltext/fulltext__published__dedf2d646e952ba0.pdf</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>dedf2d646e952ba0f6c2e7326d6c8ceda5eac7f0c9485dba3a4a0d136a922526</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA amplicon sequencing and data processing</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="90" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>R05173-E02</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>R05173</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>PCR products were quantiﬁed, mixed, puriﬁed and
+sequenced on an Illumina HiSeq platform at Novogene (Beijing,
+China).</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>HiSeq用于PCR产物，不按平台判断宏基因组。</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05173/fulltext/fulltext__published__dedf2d646e952ba0.pdf</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>dedf2d646e952ba0f6c2e7326d6c8ceda5eac7f0c9485dba3a4a0d136a922526</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>16S rRNA amplicon sequencing and data processing</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="90" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>R05173-E03</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>R05173</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Physicochemical characteristics of seed sludge.</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>仅种泥理化表及相关图；保持唯一归属待核实。</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05173/supplementary/supplementary__63ce6947f3cf6519.docx</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>63ce6947f3cf65197f9c19d5a0ba14d1e8d45197745c67215e1350d8d6b586e6</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落1–23、41–45</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="90" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>R05213-E01</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>R05213</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>An LPMO from 
+Neurospora crassa (NcLPMO9C) was expressed and 
+purified as described by Müller et al. [21].</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>蛋白酶制剂表达纯化不构成宏转录组。</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05213/fulltext/fulltext__published__bcab84a15ce93062.pdf</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>[11]</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Methods – Enzyme preparations</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="90" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>R05213-E02</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>R05213</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>The biogas composition 
+was assessed using a gas chromatograph (3000 Micro 
+GC, Agilent Technologies, USA) equipped with a ther-
+mal conductivity detector (TCD), allowing detection of 
+methane, carbon-dioxide and nitrogen gas.</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>完整方法为酶/产物与产气分析，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05213/fulltext/fulltext__published__bcab84a15ce93062.pdf</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>[12]</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Methods – Biogas analysis and calculation</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="90" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>R05213-E03</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>R05213</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>非目标泛指索取声明</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Additional data are available from the corresponding author on reasonable 
+request.</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>泛指研究数据，不是相关原始测序数据声明；无目标测序，不计可索取命中。</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05213/fulltext/fulltext__published__bcab84a15ce93062.pdf</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>[13]</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Availability of data and materials</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="90" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>R05213-E04</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>R05213</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Figure S1. (A) Chromatogram of soluble fractions of anaerobic digestion reactions with Avicel supplemented with purified NcLPMO9C as well as H2O2. Samples were taken initially in reactions supplemented with purified NcLPMO9C, after addition of H2O2 or H2O. Shoulder peaks representing Glc4gemGlc, seen in reactions with NcLPMO9C only, are highlighted by the dashed lines. (B) Chromatogram of a standard sample (0,001 g/L) obtained after treating cellopentaose with NcLPMO9C, run together with other samples.</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>色谱及甲烷曲线，未包含测序方法或编号。</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05213/supplementary/supplementary__2a8184a309e33621.docx</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>2a8184a309e3362192b49457a6cae5f0da5f682d39e48fee2b3dcbfc67a87853</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>DOCX Figure S1–S7，段落23–71</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="90" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>R05319-E01</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>R05319</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Forward primers
+(338F and 524F) and reverse primers (806R and 958R) for bacterial
+and archaeal sequences, respectively, were performed for ampliﬁca-
+tions of 16S rDNA. The key characteristics of PCR thermal cycling
+were taken from a previous study.3 PCR products were then puriﬁed,
+quantitated, and paired-end-sequenced based on the platform of
+Illumina MiSeq</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>16S靶基因扩增及PCR产物测序，非宏基因组。</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05319/fulltext/fulltext__published__865dcb7f90757119.pdf</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>865dcb7f90757119fcc3c78c4e24b37817c7bf203a8727ab8e54a7d37304e19c</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial Community Analysis</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="90" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>R05319-E02</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>R05319</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>术语命中排除</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>The complete genome sequence for putative H2- and S-oxidizer
+candidatus Sulfuricurvum sp. assembled de novo from an aquifer-
+derived metagenome.</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>被引论文题名，不是本研究测序或公开数据复用。</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05319/fulltext/fulltext__published__865dcb7f90757119.pdf</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>865dcb7f90757119fcc3c78c4e24b37817c7bf203a8727ab8e54a7d37304e19c</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>[10]</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>References (43)</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="90" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>R05396-E01</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>R05396</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>The microbial community structure analysis of pretreatment liquid
+showed that there were a total of 16 identified bacterial phyla and a
+total of 7 identified fungal class. The most dominant bacterial phyla was
+Bacteroidetes (50.26%), and followed by Firmicutes (15.37%) and Pro-
+teobacteria (9.34%). The most dominant fungal class was Sordar-
+iomycetes (44.99%), and followed by Dothideomycetes (25.56%) and
+Eurotiomycetes (17.9%).</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>报告群落组成但未说明分析方法，不能推断目标或非目标测序。</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05396/fulltext/fulltext__published__0a746b3ef69be3a5.pdf</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>0a746b3ef69be3a5b775f72e10dc44c95fe93c381373a8c5ecae4eb65f83a4f5</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>2.1 Raw materials</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="90" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>R05396-E02</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>R05396</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Fig. A.1 Mycelium morphology of ORS surface in different pretreatment time.</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>现有附件为菌丝形态/显微与材料结构图，无核酸/建库证据。</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05396/supplementary/supplementary__5e7c6f02f21c479f.docx</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>5e7c6f02f21c479f48987d2f27f3c857f5a7f2605b6728de78ced29d7358a0be</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落14、17、19、21</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="90" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>R05472-E01</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>R05472</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>The criteria for identifying SOB-positive tubes
+were (1) visualization of the turbidity of the medium, (2) microscopic veriﬁcation of the growth of
+the microorganism in the medium liquid using an optical microscope, and (3) observation of the
+presence of colonies in the solids.</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>SOB鉴定为培养浊度、显微与菌落，不是序列测定。</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05472/fulltext/fulltext__published__a81227cda8f65dc0.pdf</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>a81227cda8f65dc0a1784d367c05e5848d87660afd9c7b9c1cb20770f1aa37b0</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Sulfur-Oxidizing Bacteria Observation and Isolation</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="90" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>R05511-E01</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>R05511</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>PCR was performed followed by
+sequencing on the Illumina MiSeq platform. The 16S rRNA genes
+were
+ampliﬁed
+using
+the
+universal
+primer
+pair
+515F
+(GTGCCAGCMGCCGCGG) and 806R (GGACTACHVGGGTWTCTAAT).</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>16S靶基因扩增，不是群落DNA随机测序。</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05511/fulltext/fulltext__published__f020eb6189063184.pdf</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>f020eb6189063184de1d86419290cfe595da970bbf395020168c0ce5a8349e91</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="90" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>R05511-E02</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>R05511</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>功能预测排除</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>The predicted metagenome and
+functional genes were determined using the Phylogenetic Investi-
+gation of Communities by Reconstruction of Unobserved States
+(PICRUSt) (Langille et al., 2013).</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>明确PICRUSt预测，不能计为实际宏基因组。</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05511/fulltext/fulltext__published__f020eb6189063184.pdf</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>f020eb6189063184de1d86419290cfe595da970bbf395020168c0ce5a8349e91</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial analysis</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="90" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>R05511-E03</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>R05511</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>补充材料核查</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Table S1. Characterization of conventional flush toilets blackwater</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>现有补充仅水质表与pH/VFA/EEM图，无额外目标测序。</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05511/supplementary/supplementary__b434b7fc5acd7ee0.docx</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>b434b7fc5acd7ee0b4792e0ca5a2017a4ed1991e88eee3baf94c1bfcde86721b</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落8–10、14–41</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="90" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>R05542-E01</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>R05542</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>To this end, the apoptosis
+evaluation kit containing specic Annexin and propidium
+iodide were used.</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>流式细胞荧光染色，不是测序。</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05542/fulltext/fulltext__published__735560cdb2769e25.pdf</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>735560cdb2769e2517355c073dd51a95ac90b015a5b36f90dcc0dff360ae182b</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>2.4.1 Flow cytometry assay</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="90" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>R05542-E02</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>R05542</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>ATP biolog-
+ical measurement was performed to determine the quantify
+the metabolic activity in the biological medium using the ATP
+kit (AquaSnap™Total (Hygiena)).</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>ATP为生化发光测量，不是RNA测序。</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05542/fulltext/fulltext__published__735560cdb2769e25.pdf</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>735560cdb2769e2517355c073dd51a95ac90b015a5b36f90dcc0dff360ae182b</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>2.4.2 ATP measurement</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="90" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>R05543-E01</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>R05543</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>The variation patterns of primary parameters such as 
+daily gas production, cumulative gas production, pH, COD, 
+and ammonia nitrogen were evaluated. The detection meth-
+ods, instrument models, and measurement accuracy of these 
+parameters are shown in Table 2.</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>检测指标为产气/pH/COD/氨氮，表2仪器亦为水质与气体仪，无测序。</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05543/fulltext/fulltext__published__b9b6c6f484001832.pdf</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>b9b6c6f4840018324ed13892f9b0e35390e8ddbad76f3aab938611304261daed</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Experimental methods</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="90" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>R05544-E01</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>R05544</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>In-
+troduced carbon dioxide gas into deionized water (DW) through this
+generator at 20 ± 2 °C for 20 min to get NBW used throughout the AD
+process in this research.</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>气泡气体明示CO2；保持原分类，仅记录方法。</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05544/fulltext/fulltext__published__24c76324a7cd3191.pdf</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>24c76324a7cd319136713fab50e62f23646cac5f5f6a8abb0a4ca9560a4173f8</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Preparation of NBW</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="90" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>R05544-E02</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>R05544</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Soluble carbohydrates and proteins were determined by
+using the phenol–sulfuric method and Lowry method, respectively.</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>理化/比色及GC方法，无目标测序。</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05544/fulltext/fulltext__published__24c76324a7cd3191.pdf</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>24c76324a7cd319136713fab50e62f23646cac5f5f6a8abb0a4ca9560a4173f8</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L158"/>
+  <autoFilter ref="A1:L196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54092,7 +57243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P106"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -58521,8 +61672,158 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr"/>
     </row>
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>R04646</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>正文提及SI但当前无原件</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04646/fulltext/fulltext__published__e1d4e0f3c97d519f.pdf</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>e1d4e0f3c97d519f1a419d98a6493eec88f5ce98834b86c2c0831c2c96908766</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>§2.1/2.4称SI含染料NMR纯度及动力学计算，现无原件。</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>保留缺口；正文方法无目标测序，不追下载。</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>R04899</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>非目标扩增子BioSample编号</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R04899/fulltext/fulltext__published__92f0b2f1ad01522c.pdf</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>92f0b2f1ad01522ccc4e76595e3cd022e18db61eb7367bec31eeb097881b8329</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>SAMN12752316 to SAMN12752321 and SAMN12752323 to SAMN12752328</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>SAMN12752316–SAMN12752321; SAMN12752323–SAMN12752328</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>BioSample样本（非项目）</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>NCBI BioSample/SRA</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/biosample/?term=SAMN12752316</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>正文§2.5对应16S及mcrA扩增子，不是宏基因组/宏转录组；未逐个官方核验，也未将12个编号计为12项目。</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>保留非目标线索，不计目标项目。</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>R05396</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>测序类型待确认</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R05396/fulltext/fulltext__published__0a746b3ef69be3a5.pdf</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>0a746b3ef69be3a5b775f72e10dc44c95fe93c381373a8c5ecae4eb65f83a4f5</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>菌群组成已报告但核酸/测序方法及数据来源缺失；现有正文/匹配SI无法区分目标组学和标记基因。</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>独立复核队列；需要菌群分析的靶标/建库说明，不计阳性或阴性。</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P106"/>
+  <autoFilter ref="A1:P109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -58533,7 +61834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -58619,7 +61920,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -58635,7 +61936,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -58767,7 +62068,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -58783,7 +62084,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -58848,7 +62149,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>R04646</t>
+          <t>R05550</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -59746,8 +63047,226 @@
       </c>
       <c r="D72" s="2" t="inlineStr"/>
     </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>R04646, R04700, R04786, R04796, R04803, R04889, R04899, R04912, R04922, R04928, R05065, R05173, R05213, R05319, R05472, R05511, R05542, R05543, R05544</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。 未解决项保留待确认，未标记完成或阴性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>research_screened_count</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>pending_count</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>pending_ids</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>["R05396"]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>processed_record_count</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>target_articles</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>metagenomics_only</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>metatranscriptomics_only</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>explicit_request_articles</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D72"/>
+  <autoFilter ref="A1:D85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
+++ b/results/ad-oxygen-literature-20261006/omics_screening/omics_screening_cumulative.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'筛查总表'!$A$1:$AF$427</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'目标测序研究'!$A$1:$AF$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据项目与样本'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$247</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$W$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'口径与字段说明'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'目标测序研究'!$A$1:$AF$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据项目与样本'!$A$1:$W$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'证据记录'!$A$1:$L$274</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待确认与相关线索'!$A$1:$W$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'批次进度与统计'!$A$1:$D$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'口径与字段说明'!$A$1:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20105,22 +20105,54 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr"/>
-      <c r="M148" s="2" t="inlineStr"/>
-      <c r="N148" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>16S PCR-DGGE切带再扩增测序（非目标）</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O148" s="2" t="inlineStr"/>
-      <c r="P148" s="2" t="inlineStr"/>
-      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>污泥＋混合有机底物＋PDMS硅氧烷</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>气相O2分压0/1/3/5%，每周补充</t>
+        </is>
+      </c>
       <c r="R148" s="2" t="inlineStr"/>
       <c r="S148" s="2" t="inlineStr"/>
       <c r="T148" s="2" t="inlineStr"/>
       <c r="U148" s="2" t="inlineStr"/>
-      <c r="V148" s="2" t="inlineStr"/>
-      <c r="W148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>完整方法PDF3–5页为BMP、硅氧烷GCMS及群落16S PCR-DGGE切带、再次PCR与16S BLAST。虽使用shotgun sequencing措辞，测序对象明确是DGGE条带16S PCR产物，非群落DNA shotgun。</t>
+        </is>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–16页定位；完整方法PDF3–5页；参考文献PDF13–16页</t>
+        </is>
+      </c>
       <c r="X148" s="2" t="inlineStr">
         <is>
           <t>["original_files/R06897/fulltext/fulltext__published__676de58881645f6f.pdf"]</t>
@@ -20144,13 +20176,21 @@
       <c r="AB148" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr">
+        <is>
+          <t>正文提及ESI MM1/MM2等，当前无独立原件；保留缺口，正文16S方法明确。</t>
+        </is>
+      </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE148" s="2" t="inlineStr"/>
+          <t>["R06897-E01", "R06897-E02"]</t>
+        </is>
+      </c>
+      <c r="AE148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:32:30.529706+00:00</t>
+        </is>
+      </c>
       <c r="AF148" s="2" t="inlineStr"/>
     </row>
     <row r="149" ht="60" customHeight="1">
@@ -20305,22 +20345,58 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="inlineStr"/>
-      <c r="M150" s="2" t="inlineStr"/>
-      <c r="N150" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；GC/理化与Gompertz模型</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O150" s="2" t="inlineStr"/>
-      <c r="P150" s="2" t="inlineStr"/>
-      <c r="Q150" s="2" t="inlineStr"/>
-      <c r="R150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>猪粪</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>空气纳米气泡水，与DW对照</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>初始pH5.5/6.0/6.5，35°C 40天，三重复</t>
+        </is>
+      </c>
       <c r="S150" s="2" t="inlineStr"/>
       <c r="T150" s="2" t="inlineStr"/>
       <c r="U150" s="2" t="inlineStr"/>
-      <c r="V150" s="2" t="inlineStr"/>
-      <c r="W150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–4页）为NBW制备、批次发酵、气体GC、固体/碱度/TOC/蛋白糖、模型及统计，无DNA/RNA测序。</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–8页定位；完整方法PDF2–4页</t>
+        </is>
+      </c>
       <c r="X150" s="2" t="inlineStr">
         <is>
           <t>["original_files/R06979/fulltext/fulltext__published__3f34cd9cf2890e4e.pdf"]</t>
@@ -20344,13 +20420,21 @@
       <c r="AB150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE150" s="2" t="inlineStr"/>
+          <t>["R06979-E01"]</t>
+        </is>
+      </c>
+      <c r="AE150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.024017+00:00</t>
+        </is>
+      </c>
       <c r="AF150" s="2" t="inlineStr"/>
     </row>
     <row r="151" ht="60" customHeight="1">
@@ -20505,22 +20589,58 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="inlineStr"/>
-      <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>16S rDNA扩增子HiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O152" s="2" t="inlineStr"/>
-      <c r="P152" s="2" t="inlineStr"/>
-      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5/1/2 mL O2/gVS，55°C干式AD</t>
+        </is>
+      </c>
       <c r="R152" s="2" t="inlineStr"/>
-      <c r="S152" s="2" t="inlineStr"/>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>Illumina HiSeq2000（16S）</t>
+        </is>
+      </c>
       <c r="T152" s="2" t="inlineStr"/>
       <c r="U152" s="2" t="inlineStr"/>
-      <c r="V152" s="2" t="inlineStr"/>
-      <c r="W152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6（PDF2–3页）明确515F/806R扩增细菌16S后HiSeq、OTU/RDP。总群落DNA提取不等于shotgun，未见群落RNA。</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–7页定位；完整方法PDF2–3页</t>
+        </is>
+      </c>
       <c r="X152" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07039/fulltext/fulltext__published__443aa78550adec48.pdf"]</t>
@@ -20544,13 +20664,21 @@
       <c r="AB152" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE152" s="2" t="inlineStr"/>
+          <t>["R07039-E01"]</t>
+        </is>
+      </c>
+      <c r="AE152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.054923+00:00</t>
+        </is>
+      </c>
       <c r="AF152" s="2" t="inlineStr"/>
     </row>
     <row r="153" ht="60" customHeight="1">
@@ -20705,22 +20833,54 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；H2S/GC监测及AQUASIM模型</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O154" s="2" t="inlineStr"/>
-      <c r="P154" s="2" t="inlineStr"/>
-      <c r="Q154" s="2" t="inlineStr"/>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>乳清配制底物＋硫酸钾</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>头空间纯氧4 mL/h，44°C SBR</t>
+        </is>
+      </c>
       <c r="R154" s="2" t="inlineStr"/>
       <c r="S154" s="2" t="inlineStr"/>
       <c r="T154" s="2" t="inlineStr"/>
       <c r="U154" s="2" t="inlineStr"/>
-      <c r="V154" s="2" t="inlineStr"/>
-      <c r="W154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）包括搅拌/硫化物、VFA/GC、AQUASIM硫转化过程模型与统计，无核酸建库或组学复用。</t>
+        </is>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–7页定位；完整方法PDF2–3页</t>
+        </is>
+      </c>
       <c r="X154" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07184/fulltext/fulltext__published__dbc19544004625c7.pdf"]</t>
@@ -20744,13 +20904,21 @@
       <c r="AB154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE154" s="2" t="inlineStr"/>
+          <t>["R07184-E01"]</t>
+        </is>
+      </c>
+      <c r="AE154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.086547+00:00</t>
+        </is>
+      </c>
       <c r="AF154" s="2" t="inlineStr"/>
     </row>
     <row r="155" ht="60" customHeight="1">
@@ -20801,22 +20969,70 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K155" s="2" t="inlineStr"/>
-      <c r="L155" s="2" t="inlineStr"/>
-      <c r="M155" s="2" t="inlineStr"/>
-      <c r="N155" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>确认宏基因组</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>群落DNA shotgun宏基因组（新产生）；无实际宏转录组</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O155" s="2" t="inlineStr"/>
-      <c r="P155" s="2" t="inlineStr"/>
-      <c r="Q155" s="2" t="inlineStr"/>
-      <c r="R155" s="2" t="inlineStr"/>
-      <c r="S155" s="2" t="inlineStr"/>
-      <c r="T155" s="2" t="inlineStr"/>
-      <c r="U155" s="2" t="inlineStr"/>
-      <c r="V155" s="2" t="inlineStr"/>
-      <c r="W155" s="2" t="inlineStr"/>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>Napier grass（象草，木质纤维素）</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>ORP基线以上+25 mV间歇供氧，每隔一天；Rep1 −470 mV、Rep2 −450 mV</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>同底物/接种/运行的3次独立重复；仅Rep1/Rep2微氧稳态样本用于宏基因组；Rep3 DNA降解未测；本篇无厌氧对照宏基因组</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>文中HiSeq2000 PE125；官方HiSeq2000但标SINGLE，布局/长度差异待核对</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>2个微氧稳态样本（Rep1、Rep2）；文中3次独立反应器重复，仅2个通过DNA质量标准</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>反应器三次独立重复；宏基因组两次重复各1样本，Rep3未测</t>
+        </is>
+      </c>
+      <c r="V155" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）：群落DNA建库、HiSeq2000 PE125、Trimmomatic/SPAdes组装、MaxBin分箱、CheckM、Prokka/KEGG/CAZy，确认新产生宏基因组。前篇16S/mcrA与单菌参考基因组比较分开；宏转录组仅未来建议。两个BioSample官方对应公开WGS/RANDOM、bioreactor metagenome，项目PRJNA565588。</t>
+        </is>
+      </c>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页；完整方法PDF2–3；Table1 PDF4；讨论/展望PDF9–10；DOCX全部114段落；XLSX表头、功能表及全部编号/数据声明定位</t>
+        </is>
+      </c>
       <c r="X155" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07202/fulltext/fulltext__published__7663ffc3d7b30f70.pdf"]</t>
@@ -20840,13 +21056,21 @@
       <c r="AB155" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr">
+        <is>
+          <t>DOCX的两个BioSample、两组reads/contigs与正文TableS1引用逐项相同，已在筛查层核实唯一关联（非凭目录）；TableS1给出Rep1_D149→SAMN13634953，Rep2_D192→SAMN13634954。XLSX仅功能注释，缺唯一身份仍保留原限制。官方文库名B147_meta/A190_meta及SINGLE布局与论文表述存在差异，保留复核。</t>
+        </is>
+      </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE155" s="2" t="inlineStr"/>
+          <t>["R07202-E01", "R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="AE155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:34:58.851653+00:00</t>
+        </is>
+      </c>
       <c r="AF155" s="2" t="inlineStr"/>
     </row>
     <row r="156" ht="60" customHeight="1">
@@ -20897,22 +21121,54 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="inlineStr"/>
-      <c r="M156" s="2" t="inlineStr"/>
-      <c r="N156" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；流式细胞术/ATP/脂肪酶及理化</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O156" s="2" t="inlineStr"/>
-      <c r="P156" s="2" t="inlineStr"/>
-      <c r="Q156" s="2" t="inlineStr"/>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>剩余/初沉污泥70:30</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>超声20 kHz及0.1–0.5 VVM空气微氧预处理，38°C</t>
+        </is>
+      </c>
       <c r="R156" s="2" t="inlineStr"/>
       <c r="S156" s="2" t="inlineStr"/>
       <c r="T156" s="2" t="inlineStr"/>
       <c r="U156" s="2" t="inlineStr"/>
-      <c r="V156" s="2" t="inlineStr"/>
-      <c r="W156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.8（PDF2–4页）为超声/微曝气、BMP、Annexin/PI流式、ATP发光、油醇乳液脂肪酶活、能量平衡及sCOD，无核酸或测序。</t>
+        </is>
+      </c>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页定位；完整方法PDF2–4页；DOCX15段落和ZIP成员清单</t>
+        </is>
+      </c>
       <c r="X156" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07238/fulltext/fulltext__published__26c38d1631747ddc.pdf"]</t>
@@ -20936,13 +21192,21 @@
       <c r="AB156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr">
+        <is>
+          <t>官方来源DOCX为FigS1混合速率/脂肪酶图；ZIP唯一g a.skp为装置CAD模型，原ZIP保留，无测序方法或数据表，不计额外原件。</t>
+        </is>
+      </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE156" s="2" t="inlineStr"/>
+          <t>["R07238-E01"]</t>
+        </is>
+      </c>
+      <c r="AE156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:35:46.464704+00:00</t>
+        </is>
+      </c>
       <c r="AF156" s="2" t="inlineStr"/>
     </row>
     <row r="157" ht="60" customHeight="1">
@@ -21301,22 +21565,54 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；气量/GC及理化</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O160" s="2" t="inlineStr"/>
-      <c r="P160" s="2" t="inlineStr"/>
-      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>酸白菜</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0/0.58/0.87/1.4 mL O2/h，pH6，38±2°C</t>
+        </is>
+      </c>
       <c r="R160" s="2" t="inlineStr"/>
       <c r="S160" s="2" t="inlineStr"/>
       <c r="T160" s="2" t="inlineStr"/>
       <c r="U160" s="2" t="inlineStr"/>
-      <c r="V160" s="2" t="inlineStr"/>
-      <c r="W160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.3（PDF3–5页）为微氧暗发酵、Owen气量、GC-TCD及归一化/硫质量计算，无核酸或测序。</t>
+        </is>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–13页定位；完整方法PDF3–5页</t>
+        </is>
+      </c>
       <c r="X160" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07455/fulltext/fulltext__published__789dcf37303b566b.pdf"]</t>
@@ -21340,13 +21636,21 @@
       <c r="AB160" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE160" s="2" t="inlineStr"/>
+          <t>["R07455-E01"]</t>
+        </is>
+      </c>
+      <c r="AE160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:35:46.508797+00:00</t>
+        </is>
+      </c>
       <c r="AF160" s="2" t="inlineStr"/>
     </row>
     <row r="161" ht="60" customHeight="1">
@@ -21501,22 +21805,54 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr"/>
-      <c r="M162" s="2" t="inlineStr"/>
-      <c r="N162" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；AMPTS/BMP及元素/固体分析</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O162" s="2" t="inlineStr"/>
-      <c r="P162" s="2" t="inlineStr"/>
-      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>食物废物</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>静态好氧储存4/7天或强制曝气1.7 L/min 4天</t>
+        </is>
+      </c>
       <c r="R162" s="2" t="inlineStr"/>
       <c r="S162" s="2" t="inlineStr"/>
       <c r="T162" s="2" t="inlineStr"/>
       <c r="U162" s="2" t="inlineStr"/>
-      <c r="V162" s="2" t="inlineStr"/>
-      <c r="W162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr">
+        <is>
+          <t>完整Material and methods（PDF2–3页）为储存/曝气预处理、pH/TS/TVS、元素分析和AMPTS II BMP，无核酸/建库或组学。</t>
+        </is>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页定位；完整方法PDF2–3页</t>
+        </is>
+      </c>
       <c r="X162" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07641/fulltext/fulltext__published__1d41d189d5d994e9.pdf"]</t>
@@ -21540,13 +21876,21 @@
       <c r="AB162" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE162" s="2" t="inlineStr"/>
+          <t>["R07641-E01"]</t>
+        </is>
+      </c>
+      <c r="AE162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:35:46.548819+00:00</t>
+        </is>
+      </c>
       <c r="AF162" s="2" t="inlineStr"/>
     </row>
     <row r="163" ht="60" customHeight="1">
@@ -21597,22 +21941,54 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="2" t="inlineStr"/>
-      <c r="M163" s="2" t="inlineStr"/>
-      <c r="N163" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；组分/HPLC/GC分析</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O163" s="2" t="inlineStr"/>
-      <c r="P163" s="2" t="inlineStr"/>
-      <c r="Q163" s="2" t="inlineStr"/>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>脱水消化污泥</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>湿式氧化/蒸汽爆破，160–185°C、0/5%VS氧</t>
+        </is>
+      </c>
       <c r="R163" s="2" t="inlineStr"/>
       <c r="S163" s="2" t="inlineStr"/>
       <c r="T163" s="2" t="inlineStr"/>
       <c r="U163" s="2" t="inlineStr"/>
-      <c r="V163" s="2" t="inlineStr"/>
-      <c r="W163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6（PDF2–4页）为AWOEx、二段AD、NREL组分/Lowry/脂质、HPLC及气体分析，无目标测序。原研究范围保留。</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–8页定位；完整方法PDF2–4页</t>
+        </is>
+      </c>
       <c r="X163" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07903/fulltext/fulltext__published__840af1bcba2461da.pdf"]</t>
@@ -21636,13 +22012,21 @@
       <c r="AB163" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE163" s="2" t="inlineStr"/>
+          <t>["R07903-E01"]</t>
+        </is>
+      </c>
+      <c r="AE163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:35:46.580307+00:00</t>
+        </is>
+      </c>
       <c r="AF163" s="2" t="inlineStr"/>
     </row>
     <row r="164" ht="60" customHeight="1">
@@ -21693,22 +22077,54 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="inlineStr"/>
-      <c r="M164" s="2" t="inlineStr"/>
-      <c r="N164" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；GC/ICP-OES/HPLC及运行分析</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O164" s="2" t="inlineStr"/>
-      <c r="P164" s="2" t="inlineStr"/>
-      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>酿酒及蒸馏酒糟</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>硅膜循环空气或N2；厌氧无循环对照</t>
+        </is>
+      </c>
       <c r="R164" s="2" t="inlineStr"/>
       <c r="S164" s="2" t="inlineStr"/>
       <c r="T164" s="2" t="inlineStr"/>
       <c r="U164" s="2" t="inlineStr"/>
-      <c r="V164" s="2" t="inlineStr"/>
-      <c r="W164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF3–5页）为两段反应器/循环、气体GC、金属ICP-OES、VFA HPLC及ANOVA，无核酸/测序。</t>
+        </is>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–14页定位；完整方法PDF3–5页</t>
+        </is>
+      </c>
       <c r="X164" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07908/fulltext/fulltext__published__508bae4b9d86cb53.pdf"]</t>
@@ -21732,13 +22148,21 @@
       <c r="AB164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE164" s="2" t="inlineStr"/>
+          <t>["R07908-E01"]</t>
+        </is>
+      </c>
+      <c r="AE164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:35:46.611178+00:00</t>
+        </is>
+      </c>
       <c r="AF164" s="2" t="inlineStr"/>
     </row>
     <row r="165" ht="60" customHeight="1">
@@ -21789,22 +22213,54 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K165" s="2" t="inlineStr"/>
-      <c r="L165" s="2" t="inlineStr"/>
-      <c r="M165" s="2" t="inlineStr"/>
-      <c r="N165" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；木质素/产气及动力学</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O165" s="2" t="inlineStr"/>
-      <c r="P165" s="2" t="inlineStr"/>
-      <c r="Q165" s="2" t="inlineStr"/>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>水牛粪</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>5.3/7.3/9.3 mL O2/gVS筛选，7.3单次12h后AD</t>
+        </is>
+      </c>
       <c r="R165" s="2" t="inlineStr"/>
       <c r="S165" s="2" t="inlineStr"/>
       <c r="T165" s="2" t="inlineStr"/>
       <c r="U165" s="2" t="inlineStr"/>
-      <c r="V165" s="2" t="inlineStr"/>
-      <c r="W165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–4页）为微氧预处理、NREL木质素/总酚、水质、产气及Gompertz，无核酸或测序。</t>
+        </is>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–8页定位；完整方法PDF2–4页</t>
+        </is>
+      </c>
       <c r="X165" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07919/fulltext/fulltext__published__d4adef397549abc7.pdf"]</t>
@@ -21828,13 +22284,21 @@
       <c r="AB165" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE165" s="2" t="inlineStr"/>
+          <t>["R07919-E01"]</t>
+        </is>
+      </c>
+      <c r="AE165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:36:40.547707+00:00</t>
+        </is>
+      </c>
       <c r="AF165" s="2" t="inlineStr"/>
     </row>
     <row r="166" ht="60" customHeight="1">
@@ -21885,22 +22349,58 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>16S扩增子MiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O166" s="2" t="inlineStr"/>
-      <c r="P166" s="2" t="inlineStr"/>
-      <c r="Q166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>生活污水颗粒有机物</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.3 vvm，10 min/6 h，30°C</t>
+        </is>
+      </c>
       <c r="R166" s="2" t="inlineStr"/>
-      <c r="S166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S）</t>
+        </is>
+      </c>
       <c r="T166" s="2" t="inlineStr"/>
       <c r="U166" s="2" t="inlineStr"/>
-      <c r="V166" s="2" t="inlineStr"/>
-      <c r="W166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）明确16S V3–V4及细菌341F/805R、古菌524F10extF/Arch958RmodR PCR产物MiSeq；无shotgun/RNA。</t>
+        </is>
+      </c>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–13页定位；完整方法PDF2–3页</t>
+        </is>
+      </c>
       <c r="X166" s="2" t="inlineStr">
         <is>
           <t>["original_files/R07952/fulltext/fulltext__published__f934152c4b018bed.pdf"]</t>
@@ -21924,13 +22424,21 @@
       <c r="AB166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE166" s="2" t="inlineStr"/>
+          <t>["R07952-E01"]</t>
+        </is>
+      </c>
+      <c r="AE166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:36:40.579755+00:00</t>
+        </is>
+      </c>
       <c r="AF166" s="2" t="inlineStr"/>
     </row>
     <row r="167" ht="60" customHeight="1">
@@ -21981,22 +22489,54 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="2" t="inlineStr"/>
-      <c r="M167" s="2" t="inlineStr"/>
-      <c r="N167" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；固体/水质/产气与能耗</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O167" s="2" t="inlineStr"/>
-      <c r="P167" s="2" t="inlineStr"/>
-      <c r="Q167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>初沉＋剩余污泥</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>0.35 vvm空气48h、35°C；与热处理对比</t>
+        </is>
+      </c>
       <c r="R167" s="2" t="inlineStr"/>
       <c r="S167" s="2" t="inlineStr"/>
       <c r="T167" s="2" t="inlineStr"/>
       <c r="U167" s="2" t="inlineStr"/>
-      <c r="V167" s="2" t="inlineStr"/>
-      <c r="W167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–5页）为预处理、半连续AD、APHA/Lowry/排水甲烷与设备能耗。未报告核酸/测序。SI引用是能量与设备表/水质图，当前未取得。</t>
+        </is>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–14页定位；完整方法PDF2–5页；SI目录PDF12页</t>
+        </is>
+      </c>
       <c r="X167" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08016/fulltext/fulltext__published__50ed49bc2c646167.pdf"]</t>
@@ -22020,13 +22560,21 @@
       <c r="AB167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE167" s="2" t="inlineStr"/>
+          <t>["R08016-E01"]</t>
+        </is>
+      </c>
+      <c r="AE167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:36:40.611288+00:00</t>
+        </is>
+      </c>
       <c r="AF167" s="2" t="inlineStr"/>
     </row>
     <row r="168" ht="60" customHeight="1">
@@ -22077,22 +22625,58 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr"/>
-      <c r="N168" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>16S细菌/古菌扩增子＋PICRUSt预测（非目标）</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O168" s="2" t="inlineStr"/>
-      <c r="P168" s="2" t="inlineStr"/>
-      <c r="Q168" s="2" t="inlineStr"/>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>猪粪</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>1000 mL/L/d，空气/O2/N2/无气对照，pH10、35°C</t>
+        </is>
+      </c>
       <c r="R168" s="2" t="inlineStr"/>
-      <c r="S168" s="2" t="inlineStr"/>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S）</t>
+        </is>
+      </c>
       <c r="T168" s="2" t="inlineStr"/>
       <c r="U168" s="2" t="inlineStr"/>
-      <c r="V168" s="2" t="inlineStr"/>
-      <c r="W168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>完整Materials and methods（PDF2–3页）明确338F/806R细菌和344F/806R古菌16S PCR，MiSeq及PICRUSt/KEGG预测，无实际shotgun或RNA。DOCX按近同题名/完整作者机构核实关联，内容仅装置/ORP/群落和气体表。</t>
+        </is>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；完整方法PDF2–3；DOCX全部132段落/表格</t>
+        </is>
+      </c>
       <c r="X168" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08280/fulltext/fulltext__published__e2022315e2e0cead.pdf"]</t>
@@ -22116,13 +22700,21 @@
       <c r="AB168" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr">
+        <is>
+          <t>DOCX标题“Revealing mechanism...”及Qitao Cao等作者/机构与正文相符，已在筛查层核实唯一身份；无附加目标测序。</t>
+        </is>
+      </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE168" s="2" t="inlineStr"/>
+          <t>["R08280-E01", "R08280-E02"]</t>
+        </is>
+      </c>
+      <c r="AE168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:36:40.664710+00:00</t>
+        </is>
+      </c>
       <c r="AF168" s="2" t="inlineStr"/>
     </row>
     <row r="169" ht="60" customHeight="1">
@@ -22173,22 +22765,58 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="2" t="inlineStr"/>
-      <c r="M169" s="2" t="inlineStr"/>
-      <c r="N169" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>16S及真菌ITS扩增子MiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O169" s="2" t="inlineStr"/>
-      <c r="P169" s="2" t="inlineStr"/>
-      <c r="Q169" s="2" t="inlineStr"/>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>DDGS＋甘蔗髓，固态共发酵</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>好氧/封闭厌氧条件</t>
+        </is>
+      </c>
       <c r="R169" s="2" t="inlineStr"/>
-      <c r="S169" s="2" t="inlineStr"/>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq PE300（16S/ITS）</t>
+        </is>
+      </c>
       <c r="T169" s="2" t="inlineStr"/>
       <c r="U169" s="2" t="inlineStr"/>
-      <c r="V169" s="2" t="inlineStr"/>
-      <c r="W169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.6（PDF2–3页）明确细菌16S V3–V4 338F/806R和真菌ITS1F/ITS2R扩增产物MiSeq，DOM/FTIR及理化分析；不是目标组学。原范围分类保留。</t>
+        </is>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–9页定位；完整方法PDF2–3页</t>
+        </is>
+      </c>
       <c r="X169" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08308/fulltext/fulltext__published__3f8b05cbd2ac3f87.pdf"]</t>
@@ -22212,13 +22840,21 @@
       <c r="AB169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE169" s="2" t="inlineStr"/>
+          <t>["R08308-E01"]</t>
+        </is>
+      </c>
+      <c r="AE169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:36:40.700212+00:00</t>
+        </is>
+      </c>
       <c r="AF169" s="2" t="inlineStr"/>
     </row>
     <row r="170" ht="60" customHeight="1">
@@ -22269,22 +22905,54 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
-      <c r="N170" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>未报告测序；ETS生化活性及理化/GC</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O170" s="2" t="inlineStr"/>
-      <c r="P170" s="2" t="inlineStr"/>
-      <c r="Q170" s="2" t="inlineStr"/>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>高盐食物废物（20 g NaCl/L）</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>空气NBW预驯化，KOH/NaOH调节</t>
+        </is>
+      </c>
       <c r="R170" s="2" t="inlineStr"/>
       <c r="S170" s="2" t="inlineStr"/>
       <c r="T170" s="2" t="inlineStr"/>
       <c r="U170" s="2" t="inlineStr"/>
-      <c r="V170" s="2" t="inlineStr"/>
-      <c r="W170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）为NBW预驯化、两段AD、GC/离子色谱、理化及INT-ETS活性；没有DNA/RNA测序。</t>
+        </is>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；完整方法PDF2–3页</t>
+        </is>
+      </c>
       <c r="X170" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08346/fulltext/fulltext__published__8fbfd9ecf913a34e.pdf"]</t>
@@ -22308,13 +22976,21 @@
       <c r="AB170" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr">
+        <is>
+          <t>当前无独立补充原件；不据此认定不存在SI。</t>
+        </is>
+      </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE170" s="2" t="inlineStr"/>
+          <t>["R08346-E01"]</t>
+        </is>
+      </c>
+      <c r="AE170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:37:36.607715+00:00</t>
+        </is>
+      </c>
       <c r="AF170" s="2" t="inlineStr"/>
     </row>
     <row r="171" ht="60" customHeight="1">
@@ -22469,22 +23145,58 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="inlineStr"/>
-      <c r="M172" s="2" t="inlineStr"/>
-      <c r="N172" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>16S与真菌ITS扩增子MiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="inlineStr"/>
-      <c r="P172" s="2" t="inlineStr"/>
-      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>稻草＋猪粪＋沼液</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>好氧/微氧及好氧后微氧D1–D8，14天</t>
+        </is>
+      </c>
       <c r="R172" s="2" t="inlineStr"/>
-      <c r="S172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S/ITS）</t>
+        </is>
+      </c>
       <c r="T172" s="2" t="inlineStr"/>
       <c r="U172" s="2" t="inlineStr"/>
-      <c r="V172" s="2" t="inlineStr"/>
-      <c r="W172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–3页）明确ITS1F/ITS2R真菌、515FmodF/806RmodR细菌古菌16S PCR后MiSeq和OTU，无shotgun/RNA。题名匹配SI为水解理化表、供氧/粒径/OTU图。</t>
+        </is>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；完整方法PDF2–3；DOCX917段落含TableS1数据/所有方法与图注</t>
+        </is>
+      </c>
       <c r="X172" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08387/fulltext/fulltext__published__b7a8776d6654a870.pdf"]</t>
@@ -22508,13 +23220,21 @@
       <c r="AB172" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr">
+        <is>
+          <t>题名作者已匹配DOCX，无附加测序方法/编号，表S1为理化值。</t>
+        </is>
+      </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE172" s="2" t="inlineStr"/>
+          <t>["R08387-E01"]</t>
+        </is>
+      </c>
+      <c r="AE172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:37:36.649620+00:00</t>
+        </is>
+      </c>
       <c r="AF172" s="2" t="inlineStr"/>
     </row>
     <row r="173" ht="60" customHeight="1">
@@ -22565,22 +23285,58 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="inlineStr"/>
-      <c r="M173" s="2" t="inlineStr"/>
-      <c r="N173" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>16S扩增子MiSeq＋PICRUSt预测（非目标）</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="inlineStr"/>
-      <c r="P173" s="2" t="inlineStr"/>
-      <c r="Q173" s="2" t="inlineStr"/>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.2 mL O2/gVS，逐步提高OLR半连续AD</t>
+        </is>
+      </c>
       <c r="R173" s="2" t="inlineStr"/>
-      <c r="S173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S）</t>
+        </is>
+      </c>
       <c r="T173" s="2" t="inlineStr"/>
       <c r="U173" s="2" t="inlineStr"/>
-      <c r="V173" s="2" t="inlineStr"/>
-      <c r="W173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）为16S细菌V3–V4/古菌V4–V5引物PCR、MiSeq，水解酶丰度为PICRUSt预测；SI补方法仅Gompertz、SHAs/EEM与CV。未实际宏基因组或转录组。</t>
+        </is>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–8页定位；完整方法PDF2–3；DOCX63段落的补方法/图注/参考文献</t>
+        </is>
+      </c>
       <c r="X173" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08393/fulltext/fulltext__published__8783bc9ab4738cb6.pdf"]</t>
@@ -22604,13 +23360,21 @@
       <c r="AB173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr">
+        <is>
+          <t>候选DOCX内容吻合，仍保留唯一身份待核实；正文自身已明确16S/PICRUSt。</t>
+        </is>
+      </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE173" s="2" t="inlineStr"/>
+          <t>["R08393-E01"]</t>
+        </is>
+      </c>
+      <c r="AE173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:37:36.688319+00:00</t>
+        </is>
+      </c>
       <c r="AF173" s="2" t="inlineStr"/>
     </row>
     <row r="174" ht="60" customHeight="1">
@@ -22661,22 +23425,58 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr"/>
-      <c r="M174" s="2" t="inlineStr"/>
-      <c r="N174" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>未使用目标测序</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>细菌/古菌16S扩增子MiSeq（非目标）</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>不适用（未使用目标测序）</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O174" s="2" t="inlineStr"/>
-      <c r="P174" s="2" t="inlineStr"/>
-      <c r="Q174" s="2" t="inlineStr"/>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>玉米秸秆</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>0–1.6 mL O2/gVS/d，37°C BMP</t>
+        </is>
+      </c>
       <c r="R174" s="2" t="inlineStr"/>
-      <c r="S174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>Illumina MiSeq（16S）</t>
+        </is>
+      </c>
       <c r="T174" s="2" t="inlineStr"/>
       <c r="U174" s="2" t="inlineStr"/>
-      <c r="V174" s="2" t="inlineStr"/>
-      <c r="W174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5.6（PDF2–3页）明确细菌338F/806R、古菌524F/958R扩增16S，pool amplicons后MiSeq，OTU/SILVA16S。其余理化、SHAs、CV和酶活，无shotgun/RNA。</t>
+        </is>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–10页定位；完整方法PDF2–3；题名匹配DOCX19段落/全部图注</t>
+        </is>
+      </c>
       <c r="X174" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08456/fulltext/fulltext__published__66cfb1c0f06eb3d6.pdf"]</t>
@@ -22700,13 +23500,21 @@
       <c r="AB174" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr">
+        <is>
+          <t>SI为腐殖化/FTIR/16S Shannon四图，无额外组学。</t>
+        </is>
+      </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE174" s="2" t="inlineStr"/>
+          <t>["R08456-E01"]</t>
+        </is>
+      </c>
+      <c r="AE174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:37:36.725190+00:00</t>
+        </is>
+      </c>
       <c r="AF174" s="2" t="inlineStr"/>
     </row>
     <row r="175" ht="60" customHeight="1">
@@ -22757,22 +23565,70 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="inlineStr"/>
-      <c r="M175" s="2" t="inlineStr"/>
-      <c r="N175" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>确认宏基因组</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>群落DNA shotgun宏基因组＋16S扩增子/qPCR（分别标记）</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>5 仅有泛指性的数据可索取声明，是否包含原始测序数据不明确</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="inlineStr"/>
-      <c r="P175" s="2" t="inlineStr"/>
-      <c r="Q175" s="2" t="inlineStr"/>
-      <c r="R175" s="2" t="inlineStr"/>
-      <c r="S175" s="2" t="inlineStr"/>
-      <c r="T175" s="2" t="inlineStr"/>
-      <c r="U175" s="2" t="inlineStr"/>
-      <c r="V175" s="2" t="inlineStr"/>
-      <c r="W175" s="2" t="inlineStr"/>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>模拟食物废物（米饭/白菜/猪肉/豆腐）</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>旁流反应器0.7 L，20 mL空气/d（0.03 L/L/d），35±1°C</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>SMA、无曝气SD及直接曝气DMA；组学关注SMA stageIII供氧前与IV供氧后，OLR5.0 gVS/L/d</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>文中Illumina NovaSeq/Hiseq Xten；具体型号未唯一明确</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>SMA供氧前/后两个时间条件；具体独立测序样本总数未报告</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>反应器及实验三重复；宏基因组独立生物重复未明确</t>
+        </is>
+      </c>
+      <c r="V175" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–3页），其中§2.3.2为16S/qPCR，§2.3.3另行对群落DNA超声打断约400bp、NEXTflex Rapid DNA-Seq建库及NovaSeq/Hiseq Xten测序，确认新产生宏基因组。全文/SI未定位存储编号；PDF12仅泛指数据可索取，不能认定包括reads。</t>
+        </is>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–13页全部相关方法/数据位置；方法PDF2–3；组学结果PDF9–11；数据声明PDF12；题名匹配DOCX181段落；候选XLSX6工作表全部编号/数据声明定位及表头</t>
+        </is>
+      </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
           <t>["original_files/R08462/fulltext/fulltext__published__d5f9765b6923adab.pdf"]</t>
@@ -22796,13 +23652,21 @@
       <c r="AB175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr">
+        <is>
+          <t>DOCX题名作者匹配，TableS2a及段落142说明SMA供氧前/后组学。候选XLSX为stageIII/IV功能丰度S3–S8，无编号/数据声明；仍缺唯一题名身份，不从文件夹分配编号。</t>
+        </is>
+      </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE175" s="2" t="inlineStr"/>
+          <t>["R08462-E01", "R08462-E02", "R08462-E03"]</t>
+        </is>
+      </c>
+      <c r="AE175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:38:33.466962+00:00</t>
+        </is>
+      </c>
       <c r="AF175" s="2" t="inlineStr"/>
     </row>
     <row r="176" ht="60" customHeight="1">
@@ -47209,7 +48073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -47408,8 +48272,312 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Synergistic association between cytochrome bd-encoded Proteiniphilum and reactive oxygen species (ROS)-scavenging methanogens in microaerobic-anaerobic digestion of lignocellulosic biomass</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>WATER RESEARCH</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2020.116721</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1 直接向 AD 反应器或内部循环系统供氧</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>研究类</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>已取得核验全文</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>确认宏基因组</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>群落DNA shotgun宏基因组（新产生）；无实际宏转录组</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Napier grass（象草，木质纤维素）</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>ORP基线以上+25 mV间歇供氧，每隔一天；Rep1 −470 mV、Rep2 −450 mV</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>同底物/接种/运行的3次独立重复；仅Rep1/Rep2微氧稳态样本用于宏基因组；Rep3 DNA降解未测；本篇无厌氧对照宏基因组</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>文中HiSeq2000 PE125；官方HiSeq2000但标SINGLE，布局/长度差异待核对</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>2个微氧稳态样本（Rep1、Rep2）；文中3次独立反应器重复，仅2个通过DNA质量标准</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>反应器三次独立重复；宏基因组两次重复各1样本，Rep3未测</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.5（PDF2–3页）：群落DNA建库、HiSeq2000 PE125、Trimmomatic/SPAdes组装、MaxBin分箱、CheckM、Prokka/KEGG/CAZy，确认新产生宏基因组。前篇16S/mcrA与单菌参考基因组比较分开；宏转录组仅未来建议。两个BioSample官方对应公开WGS/RANDOM、bioreactor metagenome，项目PRJNA565588。</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–11页；完整方法PDF2–3；Table1 PDF4；讨论/展望PDF9–10；DOCX全部114段落；XLSX表头、功能表及全部编号/数据声明定位</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>["original_files/R07202/fulltext/fulltext__published__7663ffc3d7b30f70.pdf"]</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>["7663ffc3d7b30f701edee0fd4bfd7908d2eace9e7365540d6c9402e8b9b9e10a"]</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>已取得2件原格式补充材料；其中2件唯一关联待核实；完整性未确认</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>["original_files/R07202/supplementary/supplementary__0fe7ac23fd51cc3e.xlsx", "original_files/R07202/supplementary/supplementary__3e34694c8a7c6ad9.docx"]</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>DOCX的两个BioSample、两组reads/contigs与正文TableS1引用逐项相同，已在筛查层核实唯一关联（非凭目录）；TableS1给出Rep1_D149→SAMN13634953，Rep2_D192→SAMN13634954。XLSX仅功能注释，缺唯一身份仍保留原限制。官方文库名B147_meta/A190_meta及SINGLE布局与论文表述存在差异，保留复核。</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E01", "R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:34:58.851653+00:00</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>R08462</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Upgrade the high-load anaerobic digestion and relieve acid stress through the strategy of side-stream micro-aeration: biochemical performances, microbial response and intrinsic mechanisms</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>WATER RESEARCH</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2022.118850</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1 直接向 AD 反应器或内部循环系统供氧</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>期刊论文</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>研究类</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>已取得核验全文</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>确认宏基因组</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>群落DNA shotgun宏基因组＋16S扩增子/qPCR（分别标记）</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5 仅有泛指性的数据可索取声明，是否包含原始测序数据不明确</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>模拟食物废物（米饭/白菜/猪肉/豆腐）</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>旁流反应器0.7 L，20 mL空气/d（0.03 L/L/d），35±1°C</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>SMA、无曝气SD及直接曝气DMA；组学关注SMA stageIII供氧前与IV供氧后，OLR5.0 gVS/L/d</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>文中Illumina NovaSeq/Hiseq Xten；具体型号未唯一明确</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>SMA供氧前/后两个时间条件；具体独立测序样本总数未报告</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>反应器及实验三重复；宏基因组独立生物重复未明确</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>完整§2.1–2.4（PDF2–3页），其中§2.3.2为16S/qPCR，§2.3.3另行对群落DNA超声打断约400bp、NEXTflex Rapid DNA-Seq建库及NovaSeq/Hiseq Xten测序，确认新产生宏基因组。全文/SI未定位存储编号；PDF12仅泛指数据可索取，不能认定包括reads。</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>全文PDF1–13页全部相关方法/数据位置；方法PDF2–3；组学结果PDF9–11；数据声明PDF12；题名匹配DOCX181段落；候选XLSX6工作表全部编号/数据声明定位及表头</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>["original_files/R08462/fulltext/fulltext__published__d5f9765b6923adab.pdf"]</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>["d5f9765b6923adabfda081bf961d137fce46a2bf28f96d02a6a243341fe01e1c"]</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>已取得2件原格式补充材料；其中1件唯一关联待核实；完整性未确认</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>["original_files/R08462/supplementary/supplementary__5e2e3579320c0218.docx", "original_files/R08462/supplementary/supplementary__dc9b581bc0cb167a.xlsx"]</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>DOCX题名作者匹配，TableS2a及段落142说明SMA供氧前/后组学。候选XLSX为stageIII/IV功能丰度S3–S8，无编号/数据声明；仍缺唯一题名身份，不从文件夹分配编号。</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>["R08462-E01", "R08462-E02", "R08462-E03"]</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:38:33.466962+00:00</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AF1"/>
+  <autoFilter ref="A1:AF3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47420,7 +48588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -47565,8 +48733,1535 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634953</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634953</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>BioSample样本</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/biosample/SAMN13634953</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.157299+00:00</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>metagenomic seq</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634953</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418072</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742654</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Rep1_D149（作者SI），微氧稳态，官方B147_meta</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>BioSample/run/实验官方关联明确；作者分组映射来自身份核实SI，日标签差异待核对</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>官方由SAMN13634953关联：SRX7418072</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418072</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>SRA实验</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/sra/SRX7418072</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.157299+00:00</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>metagenomic seq</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634953</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418072</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742654</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Rep1_D149（作者SI），微氧稳态，官方B147_meta</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>BioSample/run/实验官方关联明确；作者分组映射来自身份核实SI，日标签差异待核对</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>官方由SAMN13634953关联：SRR10742654</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742654</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>SRA run</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/sra/SRR10742654</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.157299+00:00</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>metagenomic seq</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634953</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418072</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742654</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Rep1_D149（作者SI），微氧稳态，官方B147_meta</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>BioSample/run/实验官方关联明确；作者分组映射来自身份核实SI，日标签差异待核对</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634954</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634954</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BioSample样本</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/biosample/SAMN13634954</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.157691+00:00</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>metagenomic seq</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634954</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418073</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742653</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Rep2_D192（作者SI），微氧稳态，官方A190_meta</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>BioSample/run/实验官方关联明确；作者分组映射来自身份核实SI，日标签差异待核对</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>官方由SAMN13634954关联：SRX7418073</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418073</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>SRA实验</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/sra/SRX7418073</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.157691+00:00</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>metagenomic seq</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634954</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418073</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742653</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Rep2_D192（作者SI），微氧稳态，官方A190_meta</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>BioSample/run/实验官方关联明确；作者分组映射来自身份核实SI，日标签差异待核对</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>官方由SAMN13634954关联：SRR10742653</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742653</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>SRA run</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/sra/SRR10742653</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:33:32.157691+00:00</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>metagenomic seq</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SAMN13634954</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>SRX7418073</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>SRR10742653</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Rep2_D192（作者SI），微氧稳态，官方A190_meta</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>BioSample/run/实验官方关联明确；作者分组映射来自身份核实SI，日标签差异待核对</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>官方由SAMN13634953/954关联：PRJNA565588</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>PRJNA565588</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BioProject项目</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/bioproject/PRJNA565588</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>本篇核实的2个微氧样本；不将项目内其余16S或其他样本计入本文</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>BioSample官方链接确认</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NCBI:PRJNA565588</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>官方由SAMN13634953/954关联：SRP222288</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SRP222288</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>SRA Study</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>NCBI SRA/BioProject</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/sra/?term=SRP222288</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>公开（官方实验及run元数据）</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1 已定位编号，官方确认公开</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>本篇核实的2个微氧样本；不将项目内其余16S或其他样本计入本文</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>BioSample官方链接确认</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E02", "R07202-E03", "R07202-E04"]</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>方法与官方WGS/bioreactor metagenome一致；官方SINGLE与论文PE125不同，文库名时间标签也不同，保留差异。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000 to JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>WGS master（MAG组装）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>NCBI WGS/GenBank</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组组装MAG</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/JADLKJ000000000</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>文中提交；单条组装公开状态尚未独立核实</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>文中连续范围展开为7个WGS master；不是7个独立原始reads项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000 to JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>JADLKK000000000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>WGS master（MAG组装）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>NCBI WGS/GenBank</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组组装MAG</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/JADLKK000000000</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>文中提交；单条组装公开状态尚未独立核实</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>文中连续范围展开为7个WGS master；不是7个独立原始reads项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000 to JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>JADLKL000000000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>WGS master（MAG组装）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>NCBI WGS/GenBank</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组组装MAG</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/JADLKL000000000</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>文中提交；单条组装公开状态尚未独立核实</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>文中连续范围展开为7个WGS master；不是7个独立原始reads项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000 to JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>JADLKM000000000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>WGS master（MAG组装）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>NCBI WGS/GenBank</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组组装MAG</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/JADLKM000000000</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>文中提交；单条组装公开状态尚未独立核实</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>文中连续范围展开为7个WGS master；不是7个独立原始reads项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000 to JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>JADLKN000000000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>WGS master（MAG组装）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>NCBI WGS/GenBank</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组组装MAG</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/JADLKN000000000</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>文中提交；单条组装公开状态尚未独立核实</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>文中连续范围展开为7个WGS master；不是7个独立原始reads项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000 to JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>JADLKO000000000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>WGS master（MAG组装）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>NCBI WGS/GenBank</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组组装MAG</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/JADLKO000000000</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>文中提交；单条组装公开状态尚未独立核实</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>文中连续范围展开为7个WGS master；不是7个独立原始reads项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>JADLKJ000000000 to JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>WGS master（MAG组装）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>NCBI WGS/GenBank</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组组装MAG</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/nuccore/JADLKP000000000</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>文中提交；单条组装公开状态尚未独立核实</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>文中连续范围展开为7个WGS master；不是7个独立原始reads项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://figshare.com/articles/dataset/Microaerobic_digestion_genome_annotation/13270487</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13270487</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Figshare功能注释数据集</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Figshare</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组MAG功能注释</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>https://figshare.com/articles/dataset/Microaerobic_digestion_genome_annotation/13270487</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>文中提供；访问尚未核实</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2 文中给出编号，但访问或公开状态未核实</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>["R07202-E03"]</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>功能注释不等于原始reads，不额外计独立测序项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>R08462</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>未定位编号</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>宏基因组</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>本研究产生</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>未定位项目/公开状态未知</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5 仅有泛指性的数据可索取声明，是否包含原始测序数据不明确</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>SMA stageIII供氧前→stageIV供氧后；OLR5.0 gVS/L/d</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>文中及题名匹配SI说明条件；独立样本/run对应未报告</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>["R08462-E01", "R08462-E02", "R08462-E03"]</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>明确使用目标测序；Data will be made available on request未限定相关原始测序数据；没有编号不影响目标研究纳入。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47577,7 +50272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L247"/>
+  <dimension ref="A1:L274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -61559,8 +64254,1614 @@
         </is>
       </c>
     </row>
+    <row r="248" ht="90" customHeight="1">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>R06897-E01</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>R06897</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>using universal bacterial primers 358F-GC and
+907R.</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>明确16S靶向PCR。</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R06897/fulltext/fulltext__published__676de58881645f6f.pdf</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>676de58881645f6f5d29193925ae9b89d9b9fbcfde669defbed25d10cca145b0</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Characterisation of bacterial community dynamics</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="90" customHeight="1">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>R06897-E02</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>R06897</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Most-intensive, visible
+prole bands were excised from the DGGE gel, considering the
+assumption of each band represented a diﬀerent bacterial
+population. The 16S rRNA gene from DNA in each band was
+amplied using the same previously described primers without
+the 40 bp GC clamp.62 PCR products were conrmed by 1%
+electrophoresis on an agarose gel prior shotgun sequencing
+(Macrogen Inc.). DGGE band sequences were compared to the
+16S ribosomal RNA sequences (Archaea and Bacteria) database
+(NCBI) using BLASTN (Megablast program, default parame-</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>切胶后再次16S PCR才进入作者称shotgun的测序；不能按单词归宏基因组。</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R06897/fulltext/fulltext__published__676de58881645f6f.pdf</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>676de58881645f6f5d29193925ae9b89d9b9fbcfde669defbed25d10cca145b0</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Characterisation of bacterial community dynamics</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="90" customHeight="1">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>R06979-E01</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>R06979</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>The biogas produced from each reactor was determined every two 
+days using a gas-tight 60 mL syringe. Gas compositions (CH4 + CO2 +
+H2) were measured by a gas chromatograph (GC-8A/TCD, SHIMADZU 
+CO., Japan). Volatile solids (VS), TS and total ammonia nitrogen (TAN) 
+were measured according to the standard method (APHA, 2012).</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>GC与常规理化，完整方法没有测序流程。</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R06979/fulltext/fulltext__published__3f34cd9cf2890e4e.pdf</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>3f34cd9cf2890e4eb87cb72c78f09fa6ec28f4ab2736a8c6417799694a7d06e2</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>2.2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="90" customHeight="1">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>R07039-E01</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>R07039</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>The bacterial 16S rDNA sequence fragment was amplified by uni­
+versal primers (515 F and 806R, 5`-GTGCCAGCMGCCGCGGTAA-3` and 
+5`-GGACTACHVGGGTWTCTAAT-3`), and then the polymerase chain 
+reaction (PCR) assays were performed on each sample. Sequencing was 
+performed on an Illumina HiSeq 2000 (Illumina, San Diego, USA).</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>靶标、引物与PCR确认16S扩增子。</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07039/fulltext/fulltext__published__443aa78550adec48.pdf</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>443aa78550adec48cf8d1f71374d6f1bd8c485ac696bee07bb4054a46ce2ce24</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>2.4.2 PCR amplification and Sequencing for bioinformatics analysis</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="90" customHeight="1">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>R07184-E01</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>R07184</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Every two weeks, the COD concentration of the sludge and effluent 
+was measured according to the standard methods [4] and total sus­
+pended solids and volatile suspended solids were measured 
+gravimetrically.</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>常规水质/固体监测；结合全方法无目标测序。</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07184/fulltext/fulltext__published__dbc19544004625c7.pdf</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>dbc19544004625c74ae56e1a0e5cf2c352f53cd05d0e3fa37543a4df564ab891</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="90" customHeight="1">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>R07202-E01</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>In this study, only samples in 
+Rep 1 and Rep 2 met the sequence criteria for metagenomic anal- 
+ysis, whereas samples in Rep 3 were discarded due to severe DNA 
+degradation.</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>两个混合群落样本来自微氧稳态，Rep3排除，不把三反应器误写为3个测序样本。</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07202/fulltext/fulltext__published__7663ffc3d7b30f70.pdf</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>7663ffc3d7b30f701edee0fd4bfd7908d2eace9e7365540d6c9402e8b9b9e10a</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>2.1 Bioreactor operation and microbial sampling</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="90" customHeight="1">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>R07202-E02</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Genomic DNA was extracted using the PowerSoil DNA Isola- 
+tion Kit (Mo Bio Laboratories, Carlsbad, CA, USA) according to the 
+manufacturers’ protocols. The quality and the quantity of the ex- 
+tracted DNA were determined using NanoDrop (ThermoFisher Sci- 
+entiﬁc, Waltham, MA, USA) and Qubit ﬂuorometer (Life Technolo- 
+gies, Carlsbad, CA, USA). Genomic DNA was sent to BGI (Shenzhen, 
+China) for paired-end library construction. The prepared libraries 
+were sequenced on an Illumina HiSeq 20 0 0 platform (Illumina, San 
+Diego, CA, USA) to generate 125 bp paired-end sequencing reads. 
+2.3. Metagenomic assembly and binning 
+Raw paired-end reads from the Illumina HiSeq 20 0 0 platform 
+were initially ﬁltered using Trimmomatic (version 0.36) based on a 
+minimum quality score of 30, a minimum sequence length of 76 
+bp and allowing for less than three ambiguous nucleotides (Ns) 
+(Bolger et al., 2014 ). For each sample, the trimmed clean paired- 
+end reads were further de novo assembled into long sequence con-</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>群落DNA随机建库、全reads组装，与标记基因PCR区分。</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07202/fulltext/fulltext__published__7663ffc3d7b30f70.pdf</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>7663ffc3d7b30f701edee0fd4bfd7908d2eace9e7365540d6c9402e8b9b9e10a</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>2.2 DNA extraction and sequencing；2.3 Metagenomic assembly</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="90" customHeight="1">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>R07202-E03</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>数据声明</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>The metagenome sequencing reads have been submitted to 
+the NCBI’s Sequence Read Archive under accession numbers 
+SAMN13634953 to SAMN13634954. Draft genomes obtained 
+in this study have been deposited in NCBI’s Whole Genome 
+Shotgun database under accession numbers JADLKJ0 0 0 0 0 0 0 0 0 
+to JADLKP0 0 0 0 0 0 0 0 0. Their functional annotations have fur- 
+ther been deposited at the FigShare Online Database ( https:// 
+ﬁgshare.com/articles/dataset/Microaerobic _ digestion _ genome _ 
+annotation/13270487 ). All other relevant data are available in the 
+supporting information.</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>SAMN为BioSample不是项目号；另有7个MAG WGS主记录及Figshare功能注释。</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07202/fulltext/fulltext__published__7663ffc3d7b30f70.pdf</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>7663ffc3d7b30f701edee0fd4bfd7908d2eace9e7365540d6c9402e8b9b9e10a</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Data availability</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="90" customHeight="1">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>R07202-E04</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>附件身份及样本映射</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary Table 1. Metagenomic sequencing statistics.
+Sample
+Rep1_D149
+Rep2_D192
+Filtered reads
+87,089,214
+91,305,190
+Assembled Contigs 
+237,059
+58,704
+Total length (bp)
+387,711,802
+99,948,144
+Description
+HiSeq metagenome
+HiSeq metagenome
+BioSample No. 
+SAMN13634953
+SAMN13634954</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>两个BioSample及两组reads/contigs与正文完全一致并被正文TableS1引用，建立唯一关联及作者样本映射。</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07202/supplementary/supplementary__3e34694c8a7c6ad9.docx</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>3e34694c8a7c6ad91a6b67a08fd70f365028f3ca08f9f4c125c1e68af30eed68</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>DOCX Table S1，段落1–19</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="90" customHeight="1">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>R07238-E01</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>R07238</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>The oil-alcohol emulsion method was used to measure the lipase 
+activity of bacteria.</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>微生物活性是酶学滴定，不是转录组。</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07238/fulltext/fulltext__published__26c38d1631747ddc.pdf</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>26c38d1631747ddcb443b8d80d0070145f1968ff0f4b8e86dc2f69cc2bb968d8</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>2.6 Microbial lipase enzyme</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="90" customHeight="1">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>R07455-E01</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>R07455</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>The biogas production was determined
+using the Owen method [62]. All of the experiments were carried out, in triplicate, in
+12 reactors, the mean values for biogas measurements were reported.</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>气体测量和反应器重复，完整方法无目标组学。</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07455/fulltext/fulltext__published__789dcf37303b566b.pdf</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>789dcf37303b566b8a55345e94e04ea76e617d87cea956e5b22823e04359b55e</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>2.2 Analytical Methods</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="90" customHeight="1">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>R07641-E01</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>R07641</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>The BMP was performed on the Automatic Methane 
+Potential Test System – AMPTS II (Bioprocess®) equipment 
+according to the conditions of VDI 4630.</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>BMP装置测甲烷，不是测序。</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07641/fulltext/fulltext__published__1d41d189d5d994e9.pdf</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>1d41d189d5d994e9fbaa3e3fd20bcf623611e343c26a562734b64ffd5c8a138b</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Biochemical methane potential</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="90" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>R07903-E01</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>R07903</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>The moisture contents (MC), total solids (TS), volatile solids (VS), 
+carbohydrates (cellulose and hemicellulose), lignin, and lipid content of 
+all samples before and after AWOEx of DSS, DSS and AD were measured 
+following the National Renewable Energy Laboratory (NREL) methods</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>组分理化检测；完整方法无DNA/RNA测序。</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07903/fulltext/fulltext__published__840af1bcba2461da.pdf</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>840af1bcba2461daaa8b7f8e0623d1f7729bd8176515cd6b4ced4b6e59d4f259</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Composition analysis</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="90" customHeight="1">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>R07908-E01</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>R07908</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Metals were determined by inductively coupled plasma spectroscopy-optical emission
+spectroscopy (ICP-OES), using EPA Methods [19].</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>金属测量是ICP-OES；结合完整方法无目标组学。</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07908/fulltext/fulltext__published__508bae4b9d86cb53.pdf</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>508bae4b9d86cb53fd905fe1ae4e5455f1eb6c23e8e4099ec488d6843b0c9b86</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analyses</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="90" customHeight="1">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>R07919-E01</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>R07919</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Total solids, volatile solids, chemical oxygen demand, pH, and
+NH4eN of the substrate and inoculum were measured according to
+the standard methods (APHA, 1998).</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>理化与木质素检测，完整方法无组学。</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07919/fulltext/fulltext__published__d4adef397549abc7.pdf</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>d4adef397549abc715c77847c836f185f92b3b6403243cf29f80be138eb3efdd</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical methods</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="90" customHeight="1">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>R07952-E01</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>R07952</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>The hypervariable region V3-V4 of
+the bacterial 16S rRNA gene was then ampliﬁed with the bacterial (i.e., 341F and 805R)-
+and archaea (i.e., 524F10extF and Arch958RmodR)-fused primers by an ABI GeneAmp®
+9700 PCR thermocycler (ABI, Vernon, CA, USA). The genomic DNA and PCR products
+were analysed through electrophoresis in 1% agarose gel. Finally, qualiﬁed samples were
+sequenced on an Illumina MiSeq platform at Majorbio Bio-Pharm Technology Co., Ltd.
+(Shanghai, China).</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>靶区/引物和PCR产品明确，为标记基因扩增子。</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07952/fulltext/fulltext__published__f934152c4b018bed.pdf</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>f934152c4b018bedada50e6fd06a3d81ff026bbe989e5ad05d93cdbb14706a5e</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial Analyses</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="90" customHeight="1">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>R08016-E01</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>R08016</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Total solids (TS), volatile solids (VS), ﬁxed solids (FS), total suspended solids (TSS),
+volatile suspended solids (VSS), total ammonia nitrogen (TAN), total and soluble COD
+were measured by the methods described in APHA [25].</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>常规水质与固体；完整方法无目标测序。</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08016/fulltext/fulltext__published__50ed49bc2c646167.pdf</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>50ed49bc2c646167efb9fd14f44c6ac482f1e8581341292393f406414575960f</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>2.3 Analytical Methods and Statistical Analysis</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="90" customHeight="1">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>R08280-E01</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>R08280</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>To analyze the structure of microbial communities, approximately 5 
+mL of samples were obtained from each reactor every 6 days. High- 
+throughput sequencing was performed by Allwegene Technology Co. 
+Ltd (Beijing, China) using an Illumina MiSeq platform (Illumina Lnc., 
+CA, USA). The primer pairs 338F-806R and 344F-806R were used to 
+amplify bacterial 16S rRNA and archaeal 16S rRNA genes, allowing the 
+original sequence data to be generated. The functional characteristics of 
+the microbial communities were analyzed by phylogenetic investigation 
+of communities by reconstruction of unobserved states (PICRUSt), and 
+the metabolic pathways were classified and generated based on the 
+Kyoto Encyclopedia of Genes and Genomes (KEGG) database.</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>16S扩增和PICRUSt推断，不是宏基因组实测。</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08280/fulltext/fulltext__published__e2022315e2e0cead.pdf</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>e2022315e2e0ceada0079592a77726b5ed7c3b3d92448cb162dab8f634f4f456</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>1.3 Analytical methods – microbial community analysis</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="90" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>R08280-E02</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>R08280</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>附件身份核实</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary information
+Revealing mechanism of micro-aeration for enhancing volatile fatty acids from swine manure 
+Qitao Caoa,1, Wanqin Zhanga,1, Tianjing Liana,b, Shunli Wanga, Fubin Yina, Tanlong Zhoua, Xiaoman Weia, Hongmin Donga,*
+a Institute of Environment and Sustainable Development in Agriculture, Chinese Academy of Agricultural Sciences, Beijing 100081, PR China
+b College of Natural Resources and Environment, Northwest A&amp;F University, Yangling 712100, China</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>近同题名、相同作者及机构核实附件关联；完整附件已读。</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08280/supplementary/supplementary__a1191a34988b74dd.docx</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>a1191a34988b74dd742a54b3e62f1cc11145c1bc723963d3e0d3bbe991e13a0d</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>DOCX段落1–5</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="90" customHeight="1">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>R08308-E01</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>R08308</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>The V3-V4 hypervariable region of 16S 
+rRNA was amplified by bacterial universal primers 338F(ACTCC­
+TACGGGAGGCAGCAG) and 806R (GGACTACHVGGGTWTCTAAT). 
+Fungal ITS amplicon sequencing used the ITS1F (CTTGGTCATTTA­
+GAGGAAGTAA) and ITS2R (GCTGCGTTCTTCATCGATGC) universal 
+primers. Then, amplified products were sent to Majorbio Bio-Pharm 
+Technology Co., Ltd. (Shanghai, China) for sequencing using Miseq 
+PE300 platform (Illumina, San Diego, CA, USA).</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>细菌16S及真菌ITS均为靶向扩增子。</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08308/fulltext/fulltext__published__3f8b05cbd2ac3f87.pdf</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>3f8b05cbd2ac3f875fe3051d24b6faeea370be9e4e3ad3c696d1a8fa59bf73c2</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>2.5 Microbial sequencing</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="90" customHeight="1">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>R08346-E01</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>R08346</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>The microbial activities during the two-stage AD were reflected by 
+the electron transport rate, i.e., ETS activity. The 2-(p-iodophenyl)-3-(p- 
+nitrophenyl)-5-phenyltetrazolium chloride-electron transport system 
+(INT-ETS) reduction method was used.</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>酶/电子传递活性由化学还原法测得，非组学。</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08346/fulltext/fulltext__published__8fbfd9ecf913a34e.pdf</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>8fbfd9ecf913a34e5b72d4b5d3fe693d1d6621ac8961b0f0b1a5886fa3f9d903</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Analytical methods and calculations</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="90" customHeight="1">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>R08387-E01</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>R08387</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>The ITS1 region of 
+Fungus ITF genes was amplified with ITS1F (5′-CTTGGTCATTTA­
+GAGGAAGTAA-3′) and ITS2R (5′-GCTGCGTTCTTCATCGATGC-3′), and 
+the V4 region of archaea and bacterial 16S rRNA was amplified with 
+515FmodF (5′-GTGYCAGCMGCCGCGGTAA-3′) and 806RmodR (5′- 
+GGACTACNVGGGTWTCTAAT-3′). Amplification was completed by an 
+ABI GeneAmp® 9700 PCR thermocycler (ABI, CA, USA) with the 
+following parameters; 3 min at 95 ◦C, followed by 35 cycles (fungus) and 
+27 cycles (bacteria and archaea) of 30 s at 95 ◦C, 30 s at 55 ◦C, and 45 s at 
+72 ◦C. The Illumina Miseq sequencing service was provided by Majorbio 
+Bio-Pharm Technology Co. Ltd. (Shanghai, China). Finally, all sequences 
+were clustered into operational taxonomic units (OTU)</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>靶区/引物/扩增循环明确，不算宏基因组。</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08387/fulltext/fulltext__published__b7a8776d6654a870.pdf</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>b7a8776d6654a8704d5a796535689116767503d82a6169a81e7a2deea2a5730e</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>2.3.3 Microbial community structure</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="90" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>R08393-E01</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>R08393</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>The primer set for the V3eV4 region ampliﬁcation of the bacterial
+16S rRNA gene was 338F (ACTCCTACGGGAGGCAGCAG) and 806R
+(GGACTACHVGGGTWTCTAAT), while the primer set for the V4eV5
+region ampliﬁcation archaeal 16S rRNA gene was 524F (TGY-
+CAGCCGCCGCGGTAA) and 958R (YCCGGCGTTGAVTCCAATT). The
+gene data was processed on Illumina Miseq sequencing platform
+(Majorbio, Shanghai, China) for the microbial diversity analysis. In
+order to investigate the effects of micro-aeration on the extracel-
+lular enzymes during AD process, PICRUSt, a software for the pre-
+diction of genome functions, was used to predict the abundances of
+hydrolytic enzymes by the online platform (Majorbio, Shanghai,
+China) as described in a previous study [20].</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>16S扩增子与功能推断明确，不能把预测酶丰度当宏基因组。</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08393/fulltext/fulltext__published__8783bc9ab4738cb6.pdf</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>8783bc9ab4738cb6844675bc527754d45c2a8a5e3def2f6d17ff3068177b2f02</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial community structure analysis</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="90" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>R08456-E01</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>R08456</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>In order to run the polymerase chain reaction (PCR), a primer 
+set of 338F (ACTCCTACGGGAGGCAGCAG) and 806R (GGAC­
+TACHVGGGTWTCTAAT) was used to amplify the V3-V4 region of the 
+bacterial 16S rRNA gene, and a primer set of 524F (TGY­
+CAGCCGCCGCGGTAA) and 958R (YCCGGCGTTGAVTCCAATT) was 
+used to amplify the V4-V5 region of the archaeal 16S rRNA gene [23]. 
+The quantification of the PCR products was performed with the Quan­
+tiFluor™-ST blue fluorescence quantitative system (Promega Inc., 
+China). The Illumina MiSeq platform was used to pool the obtained 
+amplicons from the PCR reactions in equimolar and paired-end 
+sequenced.</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>16S PCR产物池化测序，不是shotgun。</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08456/fulltext/fulltext__published__66cfb1c0f06eb3d6.pdf</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>66cfb1c0f06eb3d6ea590df4b6f1bd2f704c850c73f84e247f34e770bb3d6f65</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>[2]</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>2.4 Microbial community structure analysis</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="90" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>R08462-E01</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>R08462</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>方法判断</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>The DNA was broken 
+into fragments of approximately 400 bp using ultrasound (Covaris 
+M220, USA). Sequencing library was constructed using the NEXTflexTM
+Rapid DNA-Seq. Subsequently, Majorbio Bio-Pharm Technology Co., 
+Ltd. (Shanghai, China) used the Illumina NovaSeq/Hiseq Xten(Illumina 
+Inc., San Diego, CA, USA) for sequencing. The raw reads from meta­
+genome sequencing were processed on the free online platform of 
+Majorbio Cloud Platform (cloud.majorbio.com).</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>超声打断全群落DNA＋DNA-Seq建库，全reads分析，与前节16S扩增子分开。</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08462/fulltext/fulltext__published__d5f9765b6923adab.pdf</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>d5f9765b6923adabfda081bf961d137fce46a2bf28f96d02a6a243341fe01e1c</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>[2, 3]</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>2.3.3 Metagenomic sequencing and analysis</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="90" customHeight="1">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>R08462-E02</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>R08462</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>数据声明</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Data will be made available on request.</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>泛指数据可索取；没有明确raw reads/metagenomic data，不标状态4。</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08462/fulltext/fulltext__published__d5f9765b6923adab.pdf</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>d5f9765b6923adabfda081bf961d137fce46a2bf28f96d02a6a243341fe01e1c</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>[12]</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>Data availability</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="90" customHeight="1">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>R08462-E03</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>R08462</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>处理组对应</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Table S2a describes the experimental design and analysis of the three groups of reactors. First, three groups of reactors were used as controls for structures and micro-aeration to explore the role of micro-aeration in the side-stream reactor. In addition, enzymes, C-blance, CLSM, microbial and microbial and metagenomic analysis were performed before and after the introduction of micro-aeration to further explore the intrinsic mechanisms of SMA.</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>题名已匹配附件说明供氧前/后组学，对应SMA阶段；具体测序独立样本数未写明。</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08462/supplementary/supplementary__5e2e3579320c0218.docx</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>5e2e3579320c021854d91feafeffc531850e6b9ad0ec645a8e5606f4cb064e32</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>DOCX TableS2a说明，段落142</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L247"/>
+  <autoFilter ref="A1:L274"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -61571,7 +65872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W119"/>
+  <dimension ref="A1:W124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -63856,10 +68157,26 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
-      <c r="T50" s="2" t="inlineStr"/>
-      <c r="U50" s="2" t="inlineStr"/>
-      <c r="V50" s="2" t="inlineStr"/>
-      <c r="W50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>已解决</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>正文数据声明SAMN13634953/954及TableS1的两组reads/contigs逐项相同，DOCX表S1含同一BioSample与统计，唯一关联核实；原清单角色/路径保留。</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>R07202-E04</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -65032,10 +69349,26 @@
           <t>不得仅凭目录将测序编号归给文章；待题名/DOI/正文引用核实</t>
         </is>
       </c>
-      <c r="T74" s="2" t="inlineStr"/>
-      <c r="U74" s="2" t="inlineStr"/>
-      <c r="V74" s="2" t="inlineStr"/>
-      <c r="W74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>已解决</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>近同题名、Qitao Cao/Wanqin Zhang等完整作者及CAAS机构与正文PDF1一致。</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>R08280-E02</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -67626,8 +71959,265 @@
       <c r="V119" s="2" t="inlineStr"/>
       <c r="W119" s="2" t="inlineStr"/>
     </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>R06897</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>正文提及SI但当前无原件</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R06897/fulltext/fulltext__published__676de58881645f6f.pdf</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>676de58881645f6f5d29193925ae9b89d9b9fbcfde669defbed25d10cca145b0</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>ESI MM1/MM2为供氧与分析QA/QC等，当前无独立SI原件。</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>保留缺口，不追下载。</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>官方元数据与论文方法差异</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07202/fulltext/fulltext__published__7663ffc3d7b30f70.pdf</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>7663ffc3d7b30f701edee0fd4bfd7908d2eace9e7365540d6c9402e8b9b9e10a</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>文中HiSeq2000 PE125；SRA标SINGLE、每spot300 bases。SI写Rep1_D149/Rep2_D192，但官方文库名B147_meta/A190_meta。两个BioSample和bioreactor metagenome/WGS身份明确，保留布局与时间标签差异。</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr"/>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>公开状态已确认；下游下载/分析前复核文库布局和实际采样日，不据此改写作者映射。</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>R07202</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>非目标单菌参考序列</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R07202/fulltext/fulltext__published__7663ffc3d7b30f70.pdf</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>7663ffc3d7b30f701edee0fd4bfd7908d2eace9e7365540d6c9402e8b9b9e10a</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>LT605205；CP006933；CP014265</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>GenBank单菌基因组序列</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>PDF3–4为MAG注释/比较使用的参考菌株基因组，非本研究新测序群落样本，也不计复用宏基因组项目。</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr"/>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>与本研究群落WGS分开。</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>R08016</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>正文提及SI但当前无原件</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08016/fulltext/fulltext__published__50ed49bc2c646167.pdf</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>50ed49bc2c646167efb9fd14f44c6ac482f1e8581341292393f406414575960f</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>[12]</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>SI S1–S3为Energy相关分析，S4为过程图，当前无独立附件。</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr"/>
+      <c r="R123" s="2" t="inlineStr"/>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>保留缺口，不追下载。</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>R08462</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>目标宏基因组数据获取待明确</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>original_files/R08462/fulltext/fulltext__published__d5f9765b6923adab.pdf</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>d5f9765b6923adabfda081bf961d137fce46a2bf28f96d02a6a243341fe01e1c</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>未找到编号，PDF12只写Data will be made available on request；是否包含原始宏基因组reads不明。</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>列入目标研究候选；不标公开下载，不代联系作者。</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W119"/>
+  <autoFilter ref="A1:W124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -67638,7 +72228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -67724,7 +72314,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -67740,7 +72330,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -67756,7 +72346,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -67765,7 +72355,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>未完成、待确认、缺正文及综述不计阴性；本批零命中不代表剩余队列没有目标测序。</t>
+          <t>未完成、待确认、缺正文及综述不计阴性；对后续记录逐篇阅读全文方法，不以前批命中数量推断。</t>
         </is>
       </c>
     </row>
@@ -67776,7 +72366,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -67824,7 +72414,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -67852,11 +72442,11 @@
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>独立目标项目数（按dataset_key去重）</t>
+          <t>泛指数据可索取但是否含reads不明</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -67868,11 +72458,11 @@
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>待确认研究</t>
+          <t>确认目标测序但无编号/声明</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -67884,11 +72474,11 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>未开始研究</t>
+          <t>独立目标项目数（按dataset_key去重）</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>226</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -67900,11 +72490,11 @@
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>缺正文跳过（研究）</t>
+          <t>待确认研究</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -67916,11 +72506,11 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>综述不适用（含4条缺正文综述）</t>
+          <t>未开始研究</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>51</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -67932,11 +72522,11 @@
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>附件唯一归属待核实件数</t>
+          <t>缺正文跳过（研究）</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -67948,13 +72538,11 @@
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>下一批起点</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>R06897</t>
-        </is>
+          <t>综述不适用（含4条缺正文综述）</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -67966,11 +72554,11 @@
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>下一批默认篇数</t>
+          <t>附件唯一归属待核实件数</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -67982,37 +72570,33 @@
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>本批完成ID</t>
+          <t>下一批起点</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>R00273, R00313, R00379, R00430, R00608</t>
+          <t>R08552</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>B001</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。</t>
-        </is>
-      </c>
+          <t>累计</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>research_screened_count</t>
+          <t>下一批默认篇数</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>累计</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -68020,27 +72604,33 @@
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>5</v>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>R00273, R00313, R00379, R00430, R00608</t>
+        </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>B001</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>pending_count</t>
+          <t>research_screened_count</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -68052,13 +72642,11 @@
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>pending_ids</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -68070,11 +72658,11 @@
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>processed_record_count</t>
+          <t>pending_count</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -68086,7 +72674,7 @@
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>review_not_applicable_ids</t>
+          <t>pending_ids</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -68104,11 +72692,11 @@
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -68120,11 +72708,13 @@
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>0</v>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -68136,7 +72726,7 @@
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
+          <t>target_articles</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -68152,7 +72742,7 @@
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>metagenomics_only</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -68168,7 +72758,7 @@
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>metatranscriptomics_only</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -68184,7 +72774,7 @@
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>explicit_request_articles</t>
+          <t>both</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -68200,37 +72790,31 @@
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>本批完成ID</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>R00651, R00677, R00795, R00888, R01050, R01126, R01212, R01238, R01297, R01347, R01349, R01350, R01362, R01410, R01414, R01505, R01556, R01654, R01727, R01785</t>
-        </is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>B002</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>按稳定ID顺序，逐篇阅读方法；实际综述单列后顺延补足研究篇数。</t>
-        </is>
-      </c>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>research_screened_count</t>
+          <t>explicit_request_articles</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -68238,27 +72822,33 @@
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>20</v>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>R00651, R00677, R00795, R00888, R01050, R01126, R01212, R01238, R01297, R01347, R01349, R01350, R01362, R01410, R01414, R01505, R01556, R01654, R01727, R01785</t>
+        </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>B002</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；实际综述单列后顺延补足研究篇数。</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>pending_count</t>
+          <t>research_screened_count</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -68270,13 +72860,11 @@
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>pending_ids</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -68288,11 +72876,11 @@
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>processed_record_count</t>
+          <t>pending_count</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -68304,12 +72892,12 @@
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>review_not_applicable_ids</t>
+          <t>pending_ids</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>["R00915"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -68322,11 +72910,11 @@
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -68338,11 +72926,13 @@
     <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>0</v>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>["R00915"]</t>
+        </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -68354,7 +72944,7 @@
     <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
+          <t>target_articles</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -68370,7 +72960,7 @@
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>metagenomics_only</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -68386,7 +72976,7 @@
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>metatranscriptomics_only</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -68402,7 +72992,7 @@
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>explicit_request_articles</t>
+          <t>both</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -68418,37 +73008,31 @@
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>本批完成ID</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>R02094, R02115, R02176, R02188, R02199, R02239, R02274, R02319, R02340, R02370, R02386, R02444, R02454, R02578, R02585, R02719, R02819, R02946, R03161</t>
-        </is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>B003</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。 未解决项保留待确认，未标记完成或阴性。</t>
-        </is>
-      </c>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>research_screened_count</t>
+          <t>explicit_request_articles</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>B003</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -68456,27 +73040,33 @@
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>19</v>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>R02094, R02115, R02176, R02188, R02199, R02239, R02274, R02319, R02340, R02370, R02386, R02444, R02454, R02578, R02585, R02719, R02819, R02946, R03161</t>
+        </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>B003</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。 未解决项保留待确认，未标记完成或阴性。</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>pending_count</t>
+          <t>research_screened_count</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -68488,13 +73078,11 @@
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>pending_ids</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>["R01917"]</t>
-        </is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -68506,11 +73094,11 @@
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>processed_record_count</t>
+          <t>pending_count</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -68522,12 +73110,12 @@
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>review_not_applicable_ids</t>
+          <t>pending_ids</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["R01917"]</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -68540,11 +73128,11 @@
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
@@ -68556,11 +73144,13 @@
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>0</v>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -68572,7 +73162,7 @@
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
+          <t>target_articles</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -68588,7 +73178,7 @@
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>metagenomics_only</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -68604,7 +73194,7 @@
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>metatranscriptomics_only</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -68620,7 +73210,7 @@
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>explicit_request_articles</t>
+          <t>both</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -68636,37 +73226,31 @@
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>本批完成ID</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>R03164, R03220, R03400, R03455, R03475, R03497, R03518, R03522, R03564, R03575, R03737, R03900, R04028, R04060, R04092, R04111, R04177, R04324, R04477, R04510</t>
-        </is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>B004</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。</t>
-        </is>
-      </c>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>research_screened_count</t>
+          <t>explicit_request_articles</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>B004</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -68674,27 +73258,33 @@
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>20</v>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>R03164, R03220, R03400, R03455, R03475, R03497, R03518, R03522, R03564, R03575, R03737, R03900, R04028, R04060, R04092, R04111, R04177, R04324, R04477, R04510</t>
+        </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>B004</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="60" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>pending_count</t>
+          <t>research_screened_count</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
@@ -68706,13 +73296,11 @@
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>pending_ids</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
@@ -68724,11 +73312,11 @@
     <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>processed_record_count</t>
+          <t>pending_count</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -68740,7 +73328,7 @@
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>review_not_applicable_ids</t>
+          <t>pending_ids</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -68758,11 +73346,11 @@
     <row r="67" ht="60" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
@@ -68774,11 +73362,13 @@
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>0</v>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
@@ -68790,7 +73380,7 @@
     <row r="69" ht="60" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
+          <t>target_articles</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -68806,7 +73396,7 @@
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>metagenomics_only</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -68822,7 +73412,7 @@
     <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>metatranscriptomics_only</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -68838,7 +73428,7 @@
     <row r="72" ht="60" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>explicit_request_articles</t>
+          <t>both</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -68854,37 +73444,31 @@
     <row r="73" ht="60" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>本批完成ID</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>R04646, R04700, R04786, R04796, R04803, R04889, R04899, R04912, R04922, R04928, R05065, R05173, R05213, R05319, R05472, R05511, R05542, R05543, R05544, R05550, R05611, R05626, R05638, R05728, R05732, R05823, R05828, R05839, R06034, R06036, R06092, R06129, R06152, R06196, R06227, R06294, R06325, R06587, R06588, R06597, R06611, R06626, R06665, R06667, R06674, R06681, R06833, R06895</t>
-        </is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>B005</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。 未解决项保留待确认，未标记完成或阴性。</t>
-        </is>
-      </c>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
     </row>
     <row r="74" ht="60" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>research_screened_count</t>
+          <t>explicit_request_articles</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>B005</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -68892,27 +73476,33 @@
     <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>completed_count</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n">
-        <v>48</v>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>R04646, R04700, R04786, R04796, R04803, R04889, R04899, R04912, R04922, R04928, R05065, R05173, R05213, R05319, R05472, R05511, R05542, R05543, R05544, R05550, R05611, R05626, R05638, R05728, R05732, R05823, R05828, R05839, R06034, R06036, R06092, R06129, R06152, R06196, R06227, R06294, R06325, R06587, R06588, R06597, R06611, R06626, R06665, R06667, R06674, R06681, R06833, R06895</t>
+        </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>B005</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。 未解决项保留待确认，未标记完成或阴性。</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="60" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>pending_count</t>
+          <t>research_screened_count</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
@@ -68924,13 +73514,11 @@
     <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>pending_ids</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>["R05396", "R06623"]</t>
-        </is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>48</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
@@ -68942,11 +73530,11 @@
     <row r="78" ht="60" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>processed_record_count</t>
+          <t>pending_count</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -68958,12 +73546,12 @@
     <row r="79" ht="60" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>review_not_applicable_ids</t>
+          <t>pending_ids</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["R05396", "R06623"]</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -68976,11 +73564,11 @@
     <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>target_articles</t>
+          <t>processed_record_count</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
@@ -68992,11 +73580,13 @@
     <row r="81" ht="60" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>metagenomics_only</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="n">
-        <v>0</v>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -69008,7 +73598,7 @@
     <row r="82" ht="60" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>metatranscriptomics_only</t>
+          <t>target_articles</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -69024,7 +73614,7 @@
     <row r="83" ht="60" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>metagenomics_only</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -69040,7 +73630,7 @@
     <row r="84" ht="60" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>public_data_articles</t>
+          <t>metatranscriptomics_only</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -69056,7 +73646,7 @@
     <row r="85" ht="60" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>explicit_request_articles</t>
+          <t>both</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -69069,8 +73659,258 @@
       </c>
       <c r="D85" s="2" t="inlineStr"/>
     </row>
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>explicit_request_articles</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>本批完成ID</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>R06897, R06979, R07039, R07184, R07202, R07238, R07455, R07641, R07903, R07908, R07919, R07952, R08016, R08280, R08308, R08346, R08387, R08393, R08456, R08462</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>按稳定ID顺序，逐篇阅读方法；扫描件按需OCR/原页核查。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>research_screened_count</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>completed_count</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>pending_count</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>pending_ids</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>processed_record_count</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>review_not_applicable_ids</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>target_articles</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>metagenomics_only</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>metatranscriptomics_only</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>public_data_articles</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>explicit_request_articles</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D85"/>
+  <autoFilter ref="A1:D100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -69081,7 +73921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -69103,185 +73943,197 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B005批次与待确认</t>
+          <t>数据来源与布局</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>本批按用户要求顺序筛查50篇：48完成、R05396/R06623待确认，不计阴性。后续默认20篇。R05396未说明分类数据获取方法；R06623菌群方法依赖尚未唯一关联SI。</t>
+          <t>B006发现R07202/R08462真实宏基因组。R07202两个BioSample官方WGS公开，项目PRJNA565588；论文PE125与官方SINGLE、样本日标签差异保留。R08462仅泛指数据可索取，不标明确reads可索取。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>B005扫描稿与证据</t>
+          <t>B005批次与待确认</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>R06611 PDF2–48逐页OCR，完整方法PDF7–17阅读；PDF12–13原页视觉确认16S/PCR/MiSeq，人工转录证据及衍生图SHA独立标记，避免OCR将16S误识为165/168。其他低文字页按需查看原页。</t>
+          <t>本批按用户要求顺序筛查50篇：48完成、R05396/R06623待确认，不计阴性。后续默认20篇。R05396未说明分类数据获取方法；R06623菌群方法依赖尚未唯一关联SI。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>筛查口径</t>
+          <t>B005扫描稿与证据</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>范围按现行完整分类名；不限制期刊/JCR；学位和其他研究如有核验正文也进入队列。综述引用不当作自身测序。</t>
+          <t>R06611 PDF2–48逐页OCR，完整方法PDF7–17阅读；PDF12–13原页视觉确认16S/PCR/MiSeq，人工转录证据及衍生图SHA独立标记，避免OCR将16S误识为165/168。其他低文字页按需查看原页。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>零命中</t>
+          <t>筛查口径</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>目标测序研究/项目表仅列真实阳性；零记录表表示累计已完成研究没有确认阳性；未完成记录不作阴性。</t>
+          <t>范围按现行完整分类名；不限制期刊/JCR；学位和其他研究如有核验正文也进入队列。综述引用不当作自身测序。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>正文覆盖</t>
+          <t>零命中</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>全范围426条含388有核验正文、38无核验正文；基线综述50条（4条缺正文），B002按原件新增识别R00915为综述，当前51条；34条研究缺正文跳过。</t>
+          <t>目标测序研究/项目表仅列真实阳性；零记录表表示累计已完成研究没有确认阳性；未完成记录不作阴性。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>目标测序</t>
+          <t>正文覆盖</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>群落DNA shotgun宏基因组或明确群落RNA宏转录组；既有公开数据复用单列；仅16S/DGGE/功能预测/单菌/引用不纳入；仅病毒组作线索。</t>
+          <t>全范围426条含388有核验正文、38无核验正文；基线综述50条（4条缺正文），B002按原件新增识别R00915为综述，当前51条；34条研究缺正文跳过。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>数据状态1–3</t>
+          <t>目标测序</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1 已定位编号，官方确认公开；2 文中给出编号，但访问或公开状态未核实；3 已定位项目，但数据未公开、受限或处于保留状态。</t>
+          <t>群落DNA shotgun宏基因组或明确群落RNA宏转录组；既有公开数据复用单列；仅16S/DGGE/功能预测/单菌/引用不纳入；仅病毒组作线索。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>数据状态4–7</t>
+          <t>数据状态1–3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4 明确声明相关测序数据可向作者索取；5 仅泛指数据可索取，是否含原始测序数据不明确；6 确认使用目标测序但未找到编号或相关声明；7 证据不足，待确认。</t>
+          <t>1 已定位编号，官方确认公开；2 文中给出编号，但访问或公开状态未核实；3 已定位项目，但数据未公开、受限或处于保留状态。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>阴性数据状态</t>
+          <t>数据状态4–7</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>阴性用不适用，不冒用状态6；缺正文或身份冲突不能标未使用目标测序。</t>
+          <t>4 明确声明相关测序数据可向作者索取；5 仅泛指数据可索取，是否含原始测序数据不明确；6 确认使用目标测序但未找到编号或相关声明；7 证据不足，待确认。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>官方核验</t>
+          <t>阴性数据状态</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>仅对目标或疑似目标项目读取官方数据库元数据，检查题名、样本、library strategy、公开状态和分组；不下载原始reads。不成功保留文中编号且标未核实。仅对已知文章做官方元数据核对；无编号或无结果不证明无数据，见各批次查询记录。</t>
+          <t>阴性用不适用，不冒用状态6；缺正文或身份冲突不能标未使用目标测序。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>项目层级</t>
+          <t>官方核验</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>项目/样本/实验/run/单条核酸记录分开；独立项目以数据库+规范项目号dataset_key跨文章去重，无项目号不推定为独立项目。</t>
+          <t>仅对目标或疑似目标项目读取官方数据库元数据，检查题名、样本、library strategy、公开状态和分组；不下载原始reads。不成功保留文中编号且标未核实。仅对已知文章做官方元数据核对；无编号或无结果不证明无数据，见各批次查询记录。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>页码和OCR</t>
+          <t>项目层级</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PDF页从1起；原印刷页另记section。R00608全5页OCR与当前PDF渲染图逐像素一致，p2–3方法原页视觉复核；科学判断经上下文阅读。</t>
+          <t>项目/样本/实验/run/单条核酸记录分开；独立项目以数据库+规范项目号dataset_key跨文章去重，无项目号不推定为独立项目。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>附件归属</t>
+          <t>页码和OCR</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>B002的R01727已核实为同文接受稿；B004的R03475 DOCX以题名、两位作者和机构核实关联，剩59件唯一归属待核实。不据目录分配编号；其余现有附件有内容吻合者仍保留归属限制，不追下载缺件。</t>
+          <t>PDF页从1起；原印刷页另记section。R00608全5页OCR与当前PDF渲染图逐像素一致，p2–3方法原页视觉复核；科学判断经上下文阅读。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>B001附件说明</t>
+          <t>附件归属</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>首批5篇均无独立补充材料原件；R00273正文内附录I–V已读，R00313正文提及Supplement Tables 1–2但未取得，方法证据明确为16S。</t>
+          <t>B002的R01727已核实为同文接受稿；B004的R03475 DOCX以题名、两位作者和机构核实关联，剩59件唯一归属待核实。不据目录分配编号；其余现有附件有内容吻合者仍保留归属限制，不追下载缺件。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>B001附件说明</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>首批5篇均无独立补充材料原件；R00273正文内附录I–V已读，R00313正文提及Supplement Tables 1–2但未取得，方法证据明确为16S。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>续跑</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>读取已提交screening_records.json，取未开始项按稳定ID顺序20篇；待确认独立复核；逐篇写入evidence/进度后再生成本表。勿运行初始化覆盖累计结果。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B16"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>